--- a/docs/test-cases/SPM-87_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-87_Test_Cases.xlsx
@@ -4,18 +4,19 @@
   <workbookPr/>
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="TC01" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="TC02" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="TC03" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="TC04" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="TC05" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="TC06" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TC07" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="TC08" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="TC09" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="TC10" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="TC11" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="TC12" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Open Questions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="TC01" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="TC02" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="TC03" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="TC04" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="TC05" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TC06" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="TC07" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="TC08" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="TC09" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="TC10" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="TC11" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="TC12" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -136,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -184,6 +185,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -475,12 +482,12 @@
   </cols>
   <sheetData>
     <row r="1" ht="30.75" customHeight="1" s="19">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="22" t="inlineStr">
         <is>
           <t>SPM-87: As a Safety Officer, I want to review an event's operational safety and record my decision so that only events with safe arrangements proceed</t>
         </is>
@@ -492,32 +499,32 @@
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="22" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" s="22" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" s="22" t="inlineStr">
         <is>
           <t>Linked AC</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="F3" s="22" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -544,27 +551,27 @@
           <t>TC01</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>SPM-87-TC01</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t>The Safety Checks list shows events awaiting a check, earliest event date first</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="23" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E4" s="17" t="inlineStr">
+      <c r="E4" s="23" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -583,27 +590,27 @@
           <t>TC02</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>SPM-87-TC02</t>
         </is>
       </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>The review shows attendance, each venue with its capacity, layout, opening hours and unavailable periods, accessibility needs and equipment</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="E5" s="17" t="inlineStr">
+      <c r="E5" s="23" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -622,27 +629,27 @@
           <t>TC03</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>SPM-87-TC03</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>The Safety Officer approves an event, which becomes Safety approved with the decision recorded</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>AC3, AC7, AC10, AC11</t>
         </is>
       </c>
-      <c r="E6" s="17" t="inlineStr">
+      <c r="E6" s="23" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -661,27 +668,27 @@
           <t>TC04</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>SPM-87-TC04</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>After approval the assigned Coordinator sees the decision and can go on to confirm the event</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>AC7, AC10</t>
         </is>
       </c>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -700,27 +707,27 @@
           <t>TC05</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>SPM-87-TC05</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>The Event Organiser sees that their event is Safety approved but not the safety details</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>AC7</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E8" s="23" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -739,27 +746,27 @@
           <t>TC06</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>SPM-87-TC06</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>Requesting changes returns the event to Planning with the changes required recorded for the Coordinator</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t>AC5, AC8, AC10</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -778,27 +785,27 @@
           <t>TC07</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>SPM-87-TC07</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>Rejecting the safety arrangement returns the event to Planning with the reason recorded for the Coordinator</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>AC4, AC8, AC10</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -817,27 +824,27 @@
           <t>TC08</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>SPM-87-TC08</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>Rejecting or requesting changes without a reason is not saved and a reason is asked for</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t>AC6</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E11" s="23" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -856,27 +863,27 @@
           <t>TC09</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>SPM-87-TC09</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>A second decision on the same submission, from a page opened before the first, is refused</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t>AC11</t>
         </is>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="E12" s="23" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -895,27 +902,27 @@
           <t>TC10</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>SPM-87-TC10</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>No decision can be recorded for an event that is not in Safety review</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>AC11</t>
         </is>
       </c>
-      <c r="E13" s="17" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -934,27 +941,27 @@
           <t>TC11</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>SPM-87-TC11</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>The assigned Coordinator and the Operations Manager cannot record a safety decision</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>AC12</t>
         </is>
       </c>
-      <c r="E14" s="17" t="inlineStr">
+      <c r="E14" s="23" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -973,27 +980,27 @@
           <t>TC12</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>SPM-87-TC12</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>[BLOCKED by SPM-71] The assigned Coordinator is notified of the decision with the changes required</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t>AC9</t>
         </is>
       </c>
-      <c r="E15" s="17" t="inlineStr">
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="F15" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1007,20 +1014,21 @@
       <c r="I15" s="23" t="n"/>
     </row>
     <row r="16"/>
+    <row r="17"/>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" s="22" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="B18" s="1" t="inlineStr">
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>Acceptance Criterion</t>
         </is>
       </c>
       <c r="C18" s="20" t="n"/>
       <c r="D18" s="21" t="n"/>
-      <c r="E18" s="1" t="inlineStr">
+      <c r="E18" s="22" t="inlineStr">
         <is>
           <t>Covered by</t>
         </is>
@@ -1028,19 +1036,19 @@
       <c r="F18" s="21" t="n"/>
     </row>
     <row r="19" ht="30.75" customHeight="1" s="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="23" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>The Safety Officer can view a list of events awaiting an Operational Safety Check, earliest event date first.</t>
         </is>
       </c>
       <c r="C19" s="20" t="n"/>
       <c r="D19" s="21" t="n"/>
-      <c r="E19" s="17" t="inlineStr">
+      <c r="E19" s="23" t="inlineStr">
         <is>
           <t>SPM-87-TC01</t>
         </is>
@@ -1048,19 +1056,19 @@
       <c r="F19" s="21" t="n"/>
     </row>
     <row r="20" ht="57.75" customHeight="1" s="19">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="A20" s="23" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>For each event, the review shows expected attendance, each venue booking with its capacity and layout, accessibility requirements, equipment arrangements, and any recorded venue restrictions or unavailable periods.</t>
         </is>
       </c>
       <c r="C20" s="20" t="n"/>
       <c r="D20" s="21" t="n"/>
-      <c r="E20" s="17" t="inlineStr">
+      <c r="E20" s="23" t="inlineStr">
         <is>
           <t>SPM-87-TC02</t>
         </is>
@@ -1068,19 +1076,19 @@
       <c r="F20" s="21" t="n"/>
     </row>
     <row r="21" ht="17.25" customHeight="1" s="19">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="23" t="inlineStr">
         <is>
           <t>AC3</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>The Safety Officer can approve the event.</t>
         </is>
       </c>
       <c r="C21" s="20" t="n"/>
       <c r="D21" s="21" t="n"/>
-      <c r="E21" s="17" t="inlineStr">
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>SPM-87-TC03</t>
         </is>
@@ -1088,19 +1096,19 @@
       <c r="F21" s="21" t="n"/>
     </row>
     <row r="22" ht="30.75" customHeight="1" s="19">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="23" t="inlineStr">
         <is>
           <t>AC4</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B22" s="23" t="inlineStr">
         <is>
           <t>The Safety Officer can reject the safety arrangement, and must give a reason.</t>
         </is>
       </c>
       <c r="C22" s="20" t="n"/>
       <c r="D22" s="21" t="n"/>
-      <c r="E22" s="17" t="inlineStr">
+      <c r="E22" s="23" t="inlineStr">
         <is>
           <t>SPM-87-TC07</t>
         </is>
@@ -1108,19 +1116,19 @@
       <c r="F22" s="21" t="n"/>
     </row>
     <row r="23" ht="30.75" customHeight="1" s="19">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="23" t="inlineStr">
         <is>
           <t>AC5</t>
         </is>
       </c>
-      <c r="B23" s="17" t="inlineStr">
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t>The Safety Officer can request changes, and must describe the changes required.</t>
         </is>
       </c>
       <c r="C23" s="20" t="n"/>
       <c r="D23" s="21" t="n"/>
-      <c r="E23" s="17" t="inlineStr">
+      <c r="E23" s="23" t="inlineStr">
         <is>
           <t>SPM-87-TC06</t>
         </is>
@@ -1128,19 +1136,19 @@
       <c r="F23" s="21" t="n"/>
     </row>
     <row r="24" ht="44.25" customHeight="1" s="19">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="A24" s="23" t="inlineStr">
         <is>
           <t>AC6</t>
         </is>
       </c>
-      <c r="B24" s="17" t="inlineStr">
+      <c r="B24" s="23" t="inlineStr">
         <is>
           <t>Given the Safety Officer attempts to reject or request changes without a reason, when they submit, then the decision is not saved and a reason is asked for.</t>
         </is>
       </c>
       <c r="C24" s="20" t="n"/>
       <c r="D24" s="21" t="n"/>
-      <c r="E24" s="17" t="inlineStr">
+      <c r="E24" s="23" t="inlineStr">
         <is>
           <t>SPM-87-TC08</t>
         </is>
@@ -1148,19 +1156,19 @@
       <c r="F24" s="21" t="n"/>
     </row>
     <row r="25" ht="44.25" customHeight="1" s="19">
-      <c r="A25" s="17" t="inlineStr">
+      <c r="A25" s="23" t="inlineStr">
         <is>
           <t>AC7</t>
         </is>
       </c>
-      <c r="B25" s="17" t="inlineStr">
+      <c r="B25" s="23" t="inlineStr">
         <is>
           <t>Approving records the event as safety-approved and returns it to the Coordinator to proceed.</t>
         </is>
       </c>
       <c r="C25" s="20" t="n"/>
       <c r="D25" s="21" t="n"/>
-      <c r="E25" s="17" t="inlineStr">
+      <c r="E25" s="23" t="inlineStr">
         <is>
           <t>SPM-87-TC03
 SPM-87-TC04
@@ -1170,19 +1178,19 @@
       <c r="F25" s="21" t="n"/>
     </row>
     <row r="26" ht="30.75" customHeight="1" s="19">
-      <c r="A26" s="17" t="inlineStr">
+      <c r="A26" s="23" t="inlineStr">
         <is>
           <t>AC8</t>
         </is>
       </c>
-      <c r="B26" s="17" t="inlineStr">
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>Rejecting or requesting changes returns the event to Planning (see: Resolve Safety Check Outcome).</t>
         </is>
       </c>
       <c r="C26" s="20" t="n"/>
       <c r="D26" s="21" t="n"/>
-      <c r="E26" s="17" t="inlineStr">
+      <c r="E26" s="23" t="inlineStr">
         <is>
           <t>SPM-87-TC06
 SPM-87-TC07</t>
@@ -1191,19 +1199,19 @@
       <c r="F26" s="21" t="n"/>
     </row>
     <row r="27" ht="30.75" customHeight="1" s="19">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="23" t="inlineStr">
         <is>
           <t>AC9</t>
         </is>
       </c>
-      <c r="B27" s="17" t="inlineStr">
+      <c r="B27" s="23" t="inlineStr">
         <is>
           <t>The assigned Event Coordinator is notified of the decision, with the reason or the changes required.</t>
         </is>
       </c>
       <c r="C27" s="20" t="n"/>
       <c r="D27" s="21" t="n"/>
-      <c r="E27" s="17" t="inlineStr">
+      <c r="E27" s="23" t="inlineStr">
         <is>
           <t>SPM-87-TC12</t>
         </is>
@@ -1211,19 +1219,19 @@
       <c r="F27" s="21" t="n"/>
     </row>
     <row r="28" ht="57.75" customHeight="1" s="19">
-      <c r="A28" s="17" t="inlineStr">
+      <c r="A28" s="23" t="inlineStr">
         <is>
           <t>AC10</t>
         </is>
       </c>
-      <c r="B28" s="17" t="inlineStr">
+      <c r="B28" s="23" t="inlineStr">
         <is>
           <t>The decision, the Safety Officer who made it, and the date and time are recorded against the event.</t>
         </is>
       </c>
       <c r="C28" s="20" t="n"/>
       <c r="D28" s="21" t="n"/>
-      <c r="E28" s="17" t="inlineStr">
+      <c r="E28" s="23" t="inlineStr">
         <is>
           <t>SPM-87-TC03
 SPM-87-TC04
@@ -1234,19 +1242,19 @@
       <c r="F28" s="21" t="n"/>
     </row>
     <row r="29" ht="44.25" customHeight="1" s="19">
-      <c r="A29" s="17" t="inlineStr">
+      <c r="A29" s="23" t="inlineStr">
         <is>
           <t>AC11</t>
         </is>
       </c>
-      <c r="B29" s="17" t="inlineStr">
+      <c r="B29" s="23" t="inlineStr">
         <is>
           <t>A decision can only be recorded for an event in Safety Review, and only once per submission.</t>
         </is>
       </c>
       <c r="C29" s="20" t="n"/>
       <c r="D29" s="21" t="n"/>
-      <c r="E29" s="17" t="inlineStr">
+      <c r="E29" s="23" t="inlineStr">
         <is>
           <t>SPM-87-TC03
 SPM-87-TC09
@@ -1256,19 +1264,19 @@
       <c r="F29" s="21" t="n"/>
     </row>
     <row r="30" ht="17.25" customHeight="1" s="19">
-      <c r="A30" s="17" t="inlineStr">
+      <c r="A30" s="23" t="inlineStr">
         <is>
           <t>AC12</t>
         </is>
       </c>
-      <c r="B30" s="17" t="inlineStr">
+      <c r="B30" s="23" t="inlineStr">
         <is>
           <t>Only a Safety Officer can record a safety decision.</t>
         </is>
       </c>
       <c r="C30" s="20" t="n"/>
       <c r="D30" s="21" t="n"/>
-      <c r="E30" s="17" t="inlineStr">
+      <c r="E30" s="23" t="inlineStr">
         <is>
           <t>SPM-87-TC11</t>
         </is>
@@ -1277,12 +1285,12 @@
     </row>
     <row r="31" ht="15.75" customHeight="1" s="19"/>
     <row r="32" ht="152.25" customHeight="1" s="19">
-      <c r="A32" s="1" t="inlineStr">
+      <c r="A32" s="22" t="inlineStr">
         <is>
           <t>Code reviewed</t>
         </is>
       </c>
-      <c r="B32" s="17" t="inlineStr">
+      <c r="B32" s="23" t="inlineStr">
         <is>
           <t>src/app/api/events/[id]/safety-decision/route.ts
 src/lib/safetyDecision.ts
@@ -2348,9 +2356,9 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
-        <is>
-          <t>SPM-87-TC09</t>
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>SPM-87-TC08</t>
         </is>
       </c>
     </row>
@@ -2360,21 +2368,21 @@
           <t>Summary</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
-        <is>
-          <t>A second decision on the same submission, from a page opened before the first, is refused</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="57.75" customHeight="1" s="19">
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>Rejecting or requesting changes without a reason is not saved and a reason is asked for</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="44.25" customHeight="1" s="19">
       <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
-        <is>
-          <t>npm run fixtures:spm87 has been run. 'SPM87 Twin Tab Briefing' is in Safety review. Logged in as Hana Yusof (hana.yusof@connectsphere.com / password123). This case changes the event - run npm run fixtures:spm87 afterwards.</t>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>npm run fixtures:spm87 has been run. 'SPM87 Hillside Workshop' is in Safety review. Logged in as Hana Yusof (hana.yusof@connectsphere.com / password123).</t>
         </is>
       </c>
     </row>
@@ -2384,27 +2392,31 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>1. Click 'Safety Checks' in the sidebar
-2. Click 'SPM87 Twin Tab Briefing' in the list
-3. Copy the address from the browser address bar, open a new tab, paste it and press Enter
-4. In the second tab, click 'Record safety decision', choose 'Approve' and click 'Record decision'
-5. Switch back to the first tab without reloading it
-6. Click 'Record safety decision', choose 'Reject', type 'Too crowded' in 'Reason for rejecting' and click 'Record decision'</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="54" customHeight="1" s="19">
+2. Click 'SPM87 Hillside Workshop' in the list
+3. Click 'Record safety decision'
+4. Choose 'Reject'
+5. Leave 'Reason for rejecting' empty
+6. Click 'Record decision'
+7. Choose 'Request changes'
+8. Type three spaces in 'Changes required'
+9. Click 'Record decision'
+10. Click 'Cancel' in the dialog</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30.75" customHeight="1" s="19">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>Event: SPM87 Twin Tab Briefing (Safety review)
-Two browser tabs on the same event</t>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Event: SPM87 Hillside Workshop (Safety review)
+Reject with no reason; Request changes with only spaces</t>
         </is>
       </c>
     </row>
@@ -2414,10 +2426,11 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>Step 4: The second tab shows 'Safety check approved. The coordinator has been notified.' and the status 'Safety approved'.
-Step 6: The first tab shows 'This safety check has already been decided.' The rejection is not saved, upon reloading the event changes to Safety approved.</t>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>Step 6: Nothing is saved. 'Give a reason for rejecting.' is shown under the reason box and the dialog stays open.
+Step 9: Nothing is saved. 'Describe the changes required.' is shown under the box and the dialog stays open.
+Step 10: The status is still 'Safety review' and the 'Record safety decision' button is still there.</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2440,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -2459,10 +2472,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>Step 4: The second tab shows 'Safety check approved. The coordinator has been notified.' and the status 'Safety approved'.
-Step 6: The first tab shows 'This safety check has already been decided.' The rejection is not saved, upon reloading the event changes to Safety approved.</t>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>Step 6: Nothing is saved. 'Give a reason for rejecting.' is shown under the reason box and the dialog stays open.
+Step 9: Nothing is saved. 'Describe the changes required.' is shown under the box and the dialog stays open.
+Step 10: The status is still 'Safety review' and the 'Record safety decision' button is still there.</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2510,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -2526,10 +2540,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>Step 4: The second tab shows 'Safety check approved. The coordinator has been notified.' and the status 'Safety approved'.
-Step 6: The first tab shows 'This safety check has already been decided.' The rejection is not saved, upon reloading the event changes to Safety approved.</t>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>Step 6: Nothing is saved. 'Give a reason for rejecting.' is shown under the reason box and the dialog stays open.
+Step 9: Nothing is saved. 'Describe the changes required.' is shown under the box and the dialog stays open.
+Step 10: The status is still 'Safety review' and the 'Record safety decision' button is still there.</t>
         </is>
       </c>
     </row>
@@ -2563,7 +2578,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>Kayalvizhi</t>
         </is>
@@ -3591,9 +3606,9 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
-        <is>
-          <t>SPM-87-TC10</t>
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>SPM-87-TC09</t>
         </is>
       </c>
     </row>
@@ -3603,9 +3618,9 @@
           <t>Summary</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
-        <is>
-          <t>No decision can be recorded for an event that is not in Safety review</t>
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>A second decision on the same submission, from a page opened before the first, is refused</t>
         </is>
       </c>
     </row>
@@ -3615,46 +3630,52 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
-        <is>
-          <t>npm run fixtures:spm87 has been run. 'SPM87 Unsubmitted Planning Day' is in Planning and has never been submitted for a safety check. Logged in as Hana Yusof (hana.yusof@connectsphere.com / password123).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30.75" customHeight="1" s="19">
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>npm run fixtures:spm87 has been run. 'SPM87 Twin Tab Briefing' is in Safety review. Logged in as Hana Yusof (hana.yusof@connectsphere.com / password123). This case changes the event - run npm run fixtures:spm87 afterwards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="138.75" customHeight="1" s="19">
       <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t>1. Click 'All Events' in the sidebar
-2. Click 'SPM87 Unsubmitted Planning Day' in the list</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="17.25" customHeight="1" s="19">
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>1. Click 'Safety Checks' in the sidebar
+2. Click 'SPM87 Twin Tab Briefing' in the list
+3. Copy the address from the browser address bar, open a new tab, paste it and press Enter
+4. In the second tab, click 'Record safety decision', choose 'Approve' and click 'Record decision'
+5. Switch back to the first tab without reloading it
+6. Click 'Record safety decision', choose 'Reject', type 'Too crowded' in 'Reason for rejecting' and click 'Record decision'</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="54" customHeight="1" s="19">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>Event: SPM87 Unsubmitted Planning Day (Planning)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30.75" customHeight="1" s="19">
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Event: SPM87 Twin Tab Briefing (Safety review)
+Two browser tabs on the same event</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="84.75" customHeight="1" s="19">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>Step 2: The event opens with the status 'Planning' and there is no 'Record safety decision' button.</t>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>Step 4: The second tab shows 'Safety check approved. The coordinator has been notified.' and the status 'Safety approved'.
+Step 6: The first tab shows 'This safety check has already been decided.' The rejection is not saved, upon reloading the event changes to Safety approved.</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3685,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -3696,9 +3717,10 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>Step 2: The event opens with the status 'Planning' and there is no 'Record safety decision' button.</t>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>Step 4: The second tab shows 'Safety check approved. The coordinator has been notified.' and the status 'Safety approved'.
+Step 6: The first tab shows 'This safety check has already been decided.' The rejection is not saved, upon reloading the event changes to Safety approved.</t>
         </is>
       </c>
     </row>
@@ -3732,7 +3754,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -3762,9 +3784,10 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>Step 2: The event opens with the status 'Planning' and there is no 'Record safety decision' button.</t>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>Step 4: The second tab shows 'Safety check approved. The coordinator has been notified.' and the status 'Safety approved'.
+Step 6: The first tab shows 'This safety check has already been decided.' The rejection is not saved, upon reloading the event changes to Safety approved.</t>
         </is>
       </c>
     </row>
@@ -3798,7 +3821,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>Kayalvizhi</t>
         </is>
@@ -4826,9 +4849,9 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
-        <is>
-          <t>SPM-87-TC11</t>
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>SPM-87-TC10</t>
         </is>
       </c>
     </row>
@@ -4838,65 +4861,58 @@
           <t>Summary</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
-        <is>
-          <t>The assigned Coordinator and the Operations Manager cannot record a safety decision</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30.75" customHeight="1" s="19">
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>No decision can be recorded for an event that is not in Safety review</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="57.75" customHeight="1" s="19">
       <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
-        <is>
-          <t>npm run fixtures:spm87 has been run. 'SPM87 Hillside Workshop' is in Safety review, assigned to Daniel Tan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="98.25" customHeight="1" s="19">
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>npm run fixtures:spm87 has been run. 'SPM87 Unsubmitted Planning Day' is in Planning and has never been submitted for a safety check. Logged in as Hana Yusof (hana.yusof@connectsphere.com / password123).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30.75" customHeight="1" s="19">
       <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t>1. Log in as daniel.tan@connectsphere.com with password123
-2. Click 'All Events' in the sidebar
-3. Click 'SPM87 Hillside Workshop' in the list
-4. Click 'Log out' in the top bar
-5. Log in as grace.lim@connectsphere.com with password123
-6. Click 'All Events' in the sidebar
-7. Click 'SPM87 Hillside Workshop' in the list</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30.75" customHeight="1" s="19">
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>1. Click 'All Events' in the sidebar
+2. Click 'SPM87 Unsubmitted Planning Day' in the list</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="17.25" customHeight="1" s="19">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>Coordinator: daniel.tan@connectsphere.com (assigned)
-Operations Manager: grace.lim@connectsphere.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="71.25" customHeight="1" s="19">
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Event: SPM87 Unsubmitted Planning Day (Planning)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30.75" customHeight="1" s="19">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>Step 3: Daniel Tan sees the event in 'Safety review' with no 'Record safety decision' button - only the Safety Officer decides.
-Step 7: Grace Lim sees the event with no 'Record safety decision' button either.</t>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>Step 2: The event opens with the status 'Planning' and there is no 'Record safety decision' button.</t>
         </is>
       </c>
     </row>
@@ -4906,7 +4922,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -4938,10 +4954,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>Step 3: Daniel Tan sees the event in 'Safety review' with no 'Record safety decision' button - only the Safety Officer decides.
-Step 7: Grace Lim sees the event with no 'Record safety decision' button either.</t>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>Step 2: The event opens with the status 'Planning' and there is no 'Record safety decision' button.</t>
         </is>
       </c>
     </row>
@@ -4975,7 +4990,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -5005,10 +5020,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>Step 3: Daniel Tan sees the event in 'Safety review' with no 'Record safety decision' button - only the Safety Officer decides.
-Step 7: Grace Lim sees the event with no 'Record safety decision' button either.</t>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>Step 2: The event opens with the status 'Planning' and there is no 'Record safety decision' button.</t>
         </is>
       </c>
     </row>
@@ -5042,7 +5056,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>Kayalvizhi</t>
         </is>
@@ -6070,9 +6084,9 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
-        <is>
-          <t>SPM-87-TC12</t>
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>SPM-87-TC11</t>
         </is>
       </c>
     </row>
@@ -6082,7 +6096,1251 @@
           <t>Summary</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>The assigned Coordinator and the Operations Manager cannot record a safety decision</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30.75" customHeight="1" s="19">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Pre-conditions</t>
+        </is>
+      </c>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>npm run fixtures:spm87 has been run. 'SPM87 Hillside Workshop' is in Safety review, assigned to Daniel Tan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="98.25" customHeight="1" s="19">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>1. Log in as daniel.tan@connectsphere.com with password123
+2. Click 'All Events' in the sidebar
+3. Click 'SPM87 Hillside Workshop' in the list
+4. Click 'Log out' in the top bar
+5. Log in as grace.lim@connectsphere.com with password123
+6. Click 'All Events' in the sidebar
+7. Click 'SPM87 Hillside Workshop' in the list</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30.75" customHeight="1" s="19">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Coordinator: daniel.tan@connectsphere.com (assigned)
+Operations Manager: grace.lim@connectsphere.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="71.25" customHeight="1" s="19">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>Step 3: Daniel Tan sees the event in 'Safety review' with no 'Record safety decision' button - only the Safety Officer decides.
+Step 7: Grace Lim sees the event with no 'Record safety decision' button either.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="17.25" customHeight="1" s="19">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>Janelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" s="19">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Creation Date</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="n">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="10" ht="15.75" customHeight="1" s="19"/>
+    <row r="11" ht="15.75" customHeight="1" s="19">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="14" t="n"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1" s="19">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>Step 3: Daniel Tan sees the event in 'Safety review' with no 'Record safety decision' button - only the Safety Officer decides.
+Step 7: Grace Lim sees the event with no 'Record safety decision' button either.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15.75" customHeight="1" s="19">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1" s="19">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15.75" customHeight="1" s="19">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>Janelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" s="19">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>Date of Execution</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="n">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1" s="19">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="n"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1" s="19">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>Step 3: Daniel Tan sees the event in 'Safety review' with no 'Record safety decision' button - only the Safety Officer decides.
+Step 7: Grace Lim sees the event with no 'Record safety decision' button either.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15.75" customHeight="1" s="19">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15.75" customHeight="1" s="19">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1" s="19">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>Kayalvizhi</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1" s="19">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>Date of Execution</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" s="19"/>
+    <row r="24" ht="15.75" customHeight="1" s="19"/>
+    <row r="25" ht="15.75" customHeight="1" s="19"/>
+    <row r="26" ht="15.75" customHeight="1" s="19"/>
+    <row r="27" ht="15.75" customHeight="1" s="19"/>
+    <row r="28" ht="15.75" customHeight="1" s="19"/>
+    <row r="29" ht="15.75" customHeight="1" s="19"/>
+    <row r="30" ht="15.75" customHeight="1" s="19"/>
+    <row r="31" ht="15.75" customHeight="1" s="19"/>
+    <row r="32" ht="15.75" customHeight="1" s="19"/>
+    <row r="33" ht="15.75" customHeight="1" s="19"/>
+    <row r="34" ht="15.75" customHeight="1" s="19"/>
+    <row r="35" ht="15.75" customHeight="1" s="19"/>
+    <row r="36" ht="15.75" customHeight="1" s="19"/>
+    <row r="37" ht="15.75" customHeight="1" s="19"/>
+    <row r="38" ht="15.75" customHeight="1" s="19"/>
+    <row r="39" ht="15.75" customHeight="1" s="19"/>
+    <row r="40" ht="15.75" customHeight="1" s="19"/>
+    <row r="41" ht="15.75" customHeight="1" s="19"/>
+    <row r="42" ht="15.75" customHeight="1" s="19"/>
+    <row r="43" ht="15.75" customHeight="1" s="19"/>
+    <row r="44" ht="15.75" customHeight="1" s="19"/>
+    <row r="45" ht="15.75" customHeight="1" s="19"/>
+    <row r="46" ht="15.75" customHeight="1" s="19"/>
+    <row r="47" ht="15.75" customHeight="1" s="19"/>
+    <row r="48" ht="15.75" customHeight="1" s="19"/>
+    <row r="49" ht="15.75" customHeight="1" s="19"/>
+    <row r="50" ht="15.75" customHeight="1" s="19"/>
+    <row r="51" ht="15.75" customHeight="1" s="19"/>
+    <row r="52" ht="15.75" customHeight="1" s="19"/>
+    <row r="53" ht="15.75" customHeight="1" s="19"/>
+    <row r="54" ht="15.75" customHeight="1" s="19"/>
+    <row r="55" ht="15.75" customHeight="1" s="19"/>
+    <row r="56" ht="15.75" customHeight="1" s="19"/>
+    <row r="57" ht="15.75" customHeight="1" s="19"/>
+    <row r="58" ht="15.75" customHeight="1" s="19"/>
+    <row r="59" ht="15.75" customHeight="1" s="19"/>
+    <row r="60" ht="15.75" customHeight="1" s="19"/>
+    <row r="61" ht="15.75" customHeight="1" s="19"/>
+    <row r="62" ht="15.75" customHeight="1" s="19"/>
+    <row r="63" ht="15.75" customHeight="1" s="19"/>
+    <row r="64" ht="15.75" customHeight="1" s="19"/>
+    <row r="65" ht="15.75" customHeight="1" s="19"/>
+    <row r="66" ht="15.75" customHeight="1" s="19"/>
+    <row r="67" ht="15.75" customHeight="1" s="19"/>
+    <row r="68" ht="15.75" customHeight="1" s="19"/>
+    <row r="69" ht="15.75" customHeight="1" s="19"/>
+    <row r="70" ht="15.75" customHeight="1" s="19"/>
+    <row r="71" ht="15.75" customHeight="1" s="19"/>
+    <row r="72" ht="15.75" customHeight="1" s="19"/>
+    <row r="73" ht="15.75" customHeight="1" s="19"/>
+    <row r="74" ht="15.75" customHeight="1" s="19"/>
+    <row r="75" ht="15.75" customHeight="1" s="19"/>
+    <row r="76" ht="15.75" customHeight="1" s="19"/>
+    <row r="77" ht="15.75" customHeight="1" s="19"/>
+    <row r="78" ht="15.75" customHeight="1" s="19"/>
+    <row r="79" ht="15.75" customHeight="1" s="19"/>
+    <row r="80" ht="15.75" customHeight="1" s="19"/>
+    <row r="81" ht="15.75" customHeight="1" s="19"/>
+    <row r="82" ht="15.75" customHeight="1" s="19"/>
+    <row r="83" ht="15.75" customHeight="1" s="19"/>
+    <row r="84" ht="15.75" customHeight="1" s="19"/>
+    <row r="85" ht="15.75" customHeight="1" s="19"/>
+    <row r="86" ht="15.75" customHeight="1" s="19"/>
+    <row r="87" ht="15.75" customHeight="1" s="19"/>
+    <row r="88" ht="15.75" customHeight="1" s="19"/>
+    <row r="89" ht="15.75" customHeight="1" s="19"/>
+    <row r="90" ht="15.75" customHeight="1" s="19"/>
+    <row r="91" ht="15.75" customHeight="1" s="19"/>
+    <row r="92" ht="15.75" customHeight="1" s="19"/>
+    <row r="93" ht="15.75" customHeight="1" s="19"/>
+    <row r="94" ht="15.75" customHeight="1" s="19"/>
+    <row r="95" ht="15.75" customHeight="1" s="19"/>
+    <row r="96" ht="15.75" customHeight="1" s="19"/>
+    <row r="97" ht="15.75" customHeight="1" s="19"/>
+    <row r="98" ht="15.75" customHeight="1" s="19"/>
+    <row r="99" ht="15.75" customHeight="1" s="19"/>
+    <row r="100" ht="15.75" customHeight="1" s="19"/>
+    <row r="101" ht="15.75" customHeight="1" s="19"/>
+    <row r="102" ht="15.75" customHeight="1" s="19"/>
+    <row r="103" ht="15.75" customHeight="1" s="19"/>
+    <row r="104" ht="15.75" customHeight="1" s="19"/>
+    <row r="105" ht="15.75" customHeight="1" s="19"/>
+    <row r="106" ht="15.75" customHeight="1" s="19"/>
+    <row r="107" ht="15.75" customHeight="1" s="19"/>
+    <row r="108" ht="15.75" customHeight="1" s="19"/>
+    <row r="109" ht="15.75" customHeight="1" s="19"/>
+    <row r="110" ht="15.75" customHeight="1" s="19"/>
+    <row r="111" ht="15.75" customHeight="1" s="19"/>
+    <row r="112" ht="15.75" customHeight="1" s="19"/>
+    <row r="113" ht="15.75" customHeight="1" s="19"/>
+    <row r="114" ht="15.75" customHeight="1" s="19"/>
+    <row r="115" ht="15.75" customHeight="1" s="19"/>
+    <row r="116" ht="15.75" customHeight="1" s="19"/>
+    <row r="117" ht="15.75" customHeight="1" s="19"/>
+    <row r="118" ht="15.75" customHeight="1" s="19"/>
+    <row r="119" ht="15.75" customHeight="1" s="19"/>
+    <row r="120" ht="15.75" customHeight="1" s="19"/>
+    <row r="121" ht="15.75" customHeight="1" s="19"/>
+    <row r="122" ht="15.75" customHeight="1" s="19"/>
+    <row r="123" ht="15.75" customHeight="1" s="19"/>
+    <row r="124" ht="15.75" customHeight="1" s="19"/>
+    <row r="125" ht="15.75" customHeight="1" s="19"/>
+    <row r="126" ht="15.75" customHeight="1" s="19"/>
+    <row r="127" ht="15.75" customHeight="1" s="19"/>
+    <row r="128" ht="15.75" customHeight="1" s="19"/>
+    <row r="129" ht="15.75" customHeight="1" s="19"/>
+    <row r="130" ht="15.75" customHeight="1" s="19"/>
+    <row r="131" ht="15.75" customHeight="1" s="19"/>
+    <row r="132" ht="15.75" customHeight="1" s="19"/>
+    <row r="133" ht="15.75" customHeight="1" s="19"/>
+    <row r="134" ht="15.75" customHeight="1" s="19"/>
+    <row r="135" ht="15.75" customHeight="1" s="19"/>
+    <row r="136" ht="15.75" customHeight="1" s="19"/>
+    <row r="137" ht="15.75" customHeight="1" s="19"/>
+    <row r="138" ht="15.75" customHeight="1" s="19"/>
+    <row r="139" ht="15.75" customHeight="1" s="19"/>
+    <row r="140" ht="15.75" customHeight="1" s="19"/>
+    <row r="141" ht="15.75" customHeight="1" s="19"/>
+    <row r="142" ht="15.75" customHeight="1" s="19"/>
+    <row r="143" ht="15.75" customHeight="1" s="19"/>
+    <row r="144" ht="15.75" customHeight="1" s="19"/>
+    <row r="145" ht="15.75" customHeight="1" s="19"/>
+    <row r="146" ht="15.75" customHeight="1" s="19"/>
+    <row r="147" ht="15.75" customHeight="1" s="19"/>
+    <row r="148" ht="15.75" customHeight="1" s="19"/>
+    <row r="149" ht="15.75" customHeight="1" s="19"/>
+    <row r="150" ht="15.75" customHeight="1" s="19"/>
+    <row r="151" ht="15.75" customHeight="1" s="19"/>
+    <row r="152" ht="15.75" customHeight="1" s="19"/>
+    <row r="153" ht="15.75" customHeight="1" s="19"/>
+    <row r="154" ht="15.75" customHeight="1" s="19"/>
+    <row r="155" ht="15.75" customHeight="1" s="19"/>
+    <row r="156" ht="15.75" customHeight="1" s="19"/>
+    <row r="157" ht="15.75" customHeight="1" s="19"/>
+    <row r="158" ht="15.75" customHeight="1" s="19"/>
+    <row r="159" ht="15.75" customHeight="1" s="19"/>
+    <row r="160" ht="15.75" customHeight="1" s="19"/>
+    <row r="161" ht="15.75" customHeight="1" s="19"/>
+    <row r="162" ht="15.75" customHeight="1" s="19"/>
+    <row r="163" ht="15.75" customHeight="1" s="19"/>
+    <row r="164" ht="15.75" customHeight="1" s="19"/>
+    <row r="165" ht="15.75" customHeight="1" s="19"/>
+    <row r="166" ht="15.75" customHeight="1" s="19"/>
+    <row r="167" ht="15.75" customHeight="1" s="19"/>
+    <row r="168" ht="15.75" customHeight="1" s="19"/>
+    <row r="169" ht="15.75" customHeight="1" s="19"/>
+    <row r="170" ht="15.75" customHeight="1" s="19"/>
+    <row r="171" ht="15.75" customHeight="1" s="19"/>
+    <row r="172" ht="15.75" customHeight="1" s="19"/>
+    <row r="173" ht="15.75" customHeight="1" s="19"/>
+    <row r="174" ht="15.75" customHeight="1" s="19"/>
+    <row r="175" ht="15.75" customHeight="1" s="19"/>
+    <row r="176" ht="15.75" customHeight="1" s="19"/>
+    <row r="177" ht="15.75" customHeight="1" s="19"/>
+    <row r="178" ht="15.75" customHeight="1" s="19"/>
+    <row r="179" ht="15.75" customHeight="1" s="19"/>
+    <row r="180" ht="15.75" customHeight="1" s="19"/>
+    <row r="181" ht="15.75" customHeight="1" s="19"/>
+    <row r="182" ht="15.75" customHeight="1" s="19"/>
+    <row r="183" ht="15.75" customHeight="1" s="19"/>
+    <row r="184" ht="15.75" customHeight="1" s="19"/>
+    <row r="185" ht="15.75" customHeight="1" s="19"/>
+    <row r="186" ht="15.75" customHeight="1" s="19"/>
+    <row r="187" ht="15.75" customHeight="1" s="19"/>
+    <row r="188" ht="15.75" customHeight="1" s="19"/>
+    <row r="189" ht="15.75" customHeight="1" s="19"/>
+    <row r="190" ht="15.75" customHeight="1" s="19"/>
+    <row r="191" ht="15.75" customHeight="1" s="19"/>
+    <row r="192" ht="15.75" customHeight="1" s="19"/>
+    <row r="193" ht="15.75" customHeight="1" s="19"/>
+    <row r="194" ht="15.75" customHeight="1" s="19"/>
+    <row r="195" ht="15.75" customHeight="1" s="19"/>
+    <row r="196" ht="15.75" customHeight="1" s="19"/>
+    <row r="197" ht="15.75" customHeight="1" s="19"/>
+    <row r="198" ht="15.75" customHeight="1" s="19"/>
+    <row r="199" ht="15.75" customHeight="1" s="19"/>
+    <row r="200" ht="15.75" customHeight="1" s="19"/>
+    <row r="201" ht="15.75" customHeight="1" s="19"/>
+    <row r="202" ht="15.75" customHeight="1" s="19"/>
+    <row r="203" ht="15.75" customHeight="1" s="19"/>
+    <row r="204" ht="15.75" customHeight="1" s="19"/>
+    <row r="205" ht="15.75" customHeight="1" s="19"/>
+    <row r="206" ht="15.75" customHeight="1" s="19"/>
+    <row r="207" ht="15.75" customHeight="1" s="19"/>
+    <row r="208" ht="15.75" customHeight="1" s="19"/>
+    <row r="209" ht="15.75" customHeight="1" s="19"/>
+    <row r="210" ht="15.75" customHeight="1" s="19"/>
+    <row r="211" ht="15.75" customHeight="1" s="19"/>
+    <row r="212" ht="15.75" customHeight="1" s="19"/>
+    <row r="213" ht="15.75" customHeight="1" s="19"/>
+    <row r="214" ht="15.75" customHeight="1" s="19"/>
+    <row r="215" ht="15.75" customHeight="1" s="19"/>
+    <row r="216" ht="15.75" customHeight="1" s="19"/>
+    <row r="217" ht="15.75" customHeight="1" s="19"/>
+    <row r="218" ht="15.75" customHeight="1" s="19"/>
+    <row r="219" ht="15.75" customHeight="1" s="19"/>
+    <row r="220" ht="15.75" customHeight="1" s="19"/>
+    <row r="221" ht="15.75" customHeight="1" s="19"/>
+    <row r="222" ht="15.75" customHeight="1" s="19"/>
+    <row r="223" ht="15.75" customHeight="1" s="19"/>
+    <row r="224" ht="15.75" customHeight="1" s="19"/>
+    <row r="225" ht="15.75" customHeight="1" s="19"/>
+    <row r="226" ht="15.75" customHeight="1" s="19"/>
+    <row r="227" ht="15.75" customHeight="1" s="19"/>
+    <row r="228" ht="15.75" customHeight="1" s="19"/>
+    <row r="229" ht="15.75" customHeight="1" s="19"/>
+    <row r="230" ht="15.75" customHeight="1" s="19"/>
+    <row r="231" ht="15.75" customHeight="1" s="19"/>
+    <row r="232" ht="15.75" customHeight="1" s="19"/>
+    <row r="233" ht="15.75" customHeight="1" s="19"/>
+    <row r="234" ht="15.75" customHeight="1" s="19"/>
+    <row r="235" ht="15.75" customHeight="1" s="19"/>
+    <row r="236" ht="15.75" customHeight="1" s="19"/>
+    <row r="237" ht="15.75" customHeight="1" s="19"/>
+    <row r="238" ht="15.75" customHeight="1" s="19"/>
+    <row r="239" ht="15.75" customHeight="1" s="19"/>
+    <row r="240" ht="15.75" customHeight="1" s="19"/>
+    <row r="241" ht="15.75" customHeight="1" s="19"/>
+    <row r="242" ht="15.75" customHeight="1" s="19"/>
+    <row r="243" ht="15.75" customHeight="1" s="19"/>
+    <row r="244" ht="15.75" customHeight="1" s="19"/>
+    <row r="245" ht="15.75" customHeight="1" s="19"/>
+    <row r="246" ht="15.75" customHeight="1" s="19"/>
+    <row r="247" ht="15.75" customHeight="1" s="19"/>
+    <row r="248" ht="15.75" customHeight="1" s="19"/>
+    <row r="249" ht="15.75" customHeight="1" s="19"/>
+    <row r="250" ht="15.75" customHeight="1" s="19"/>
+    <row r="251" ht="15.75" customHeight="1" s="19"/>
+    <row r="252" ht="15.75" customHeight="1" s="19"/>
+    <row r="253" ht="15.75" customHeight="1" s="19"/>
+    <row r="254" ht="15.75" customHeight="1" s="19"/>
+    <row r="255" ht="15.75" customHeight="1" s="19"/>
+    <row r="256" ht="15.75" customHeight="1" s="19"/>
+    <row r="257" ht="15.75" customHeight="1" s="19"/>
+    <row r="258" ht="15.75" customHeight="1" s="19"/>
+    <row r="259" ht="15.75" customHeight="1" s="19"/>
+    <row r="260" ht="15.75" customHeight="1" s="19"/>
+    <row r="261" ht="15.75" customHeight="1" s="19"/>
+    <row r="262" ht="15.75" customHeight="1" s="19"/>
+    <row r="263" ht="15.75" customHeight="1" s="19"/>
+    <row r="264" ht="15.75" customHeight="1" s="19"/>
+    <row r="265" ht="15.75" customHeight="1" s="19"/>
+    <row r="266" ht="15.75" customHeight="1" s="19"/>
+    <row r="267" ht="15.75" customHeight="1" s="19"/>
+    <row r="268" ht="15.75" customHeight="1" s="19"/>
+    <row r="269" ht="15.75" customHeight="1" s="19"/>
+    <row r="270" ht="15.75" customHeight="1" s="19"/>
+    <row r="271" ht="15.75" customHeight="1" s="19"/>
+    <row r="272" ht="15.75" customHeight="1" s="19"/>
+    <row r="273" ht="15.75" customHeight="1" s="19"/>
+    <row r="274" ht="15.75" customHeight="1" s="19"/>
+    <row r="275" ht="15.75" customHeight="1" s="19"/>
+    <row r="276" ht="15.75" customHeight="1" s="19"/>
+    <row r="277" ht="15.75" customHeight="1" s="19"/>
+    <row r="278" ht="15.75" customHeight="1" s="19"/>
+    <row r="279" ht="15.75" customHeight="1" s="19"/>
+    <row r="280" ht="15.75" customHeight="1" s="19"/>
+    <row r="281" ht="15.75" customHeight="1" s="19"/>
+    <row r="282" ht="15.75" customHeight="1" s="19"/>
+    <row r="283" ht="15.75" customHeight="1" s="19"/>
+    <row r="284" ht="15.75" customHeight="1" s="19"/>
+    <row r="285" ht="15.75" customHeight="1" s="19"/>
+    <row r="286" ht="15.75" customHeight="1" s="19"/>
+    <row r="287" ht="15.75" customHeight="1" s="19"/>
+    <row r="288" ht="15.75" customHeight="1" s="19"/>
+    <row r="289" ht="15.75" customHeight="1" s="19"/>
+    <row r="290" ht="15.75" customHeight="1" s="19"/>
+    <row r="291" ht="15.75" customHeight="1" s="19"/>
+    <row r="292" ht="15.75" customHeight="1" s="19"/>
+    <row r="293" ht="15.75" customHeight="1" s="19"/>
+    <row r="294" ht="15.75" customHeight="1" s="19"/>
+    <row r="295" ht="15.75" customHeight="1" s="19"/>
+    <row r="296" ht="15.75" customHeight="1" s="19"/>
+    <row r="297" ht="15.75" customHeight="1" s="19"/>
+    <row r="298" ht="15.75" customHeight="1" s="19"/>
+    <row r="299" ht="15.75" customHeight="1" s="19"/>
+    <row r="300" ht="15.75" customHeight="1" s="19"/>
+    <row r="301" ht="15.75" customHeight="1" s="19"/>
+    <row r="302" ht="15.75" customHeight="1" s="19"/>
+    <row r="303" ht="15.75" customHeight="1" s="19"/>
+    <row r="304" ht="15.75" customHeight="1" s="19"/>
+    <row r="305" ht="15.75" customHeight="1" s="19"/>
+    <row r="306" ht="15.75" customHeight="1" s="19"/>
+    <row r="307" ht="15.75" customHeight="1" s="19"/>
+    <row r="308" ht="15.75" customHeight="1" s="19"/>
+    <row r="309" ht="15.75" customHeight="1" s="19"/>
+    <row r="310" ht="15.75" customHeight="1" s="19"/>
+    <row r="311" ht="15.75" customHeight="1" s="19"/>
+    <row r="312" ht="15.75" customHeight="1" s="19"/>
+    <row r="313" ht="15.75" customHeight="1" s="19"/>
+    <row r="314" ht="15.75" customHeight="1" s="19"/>
+    <row r="315" ht="15.75" customHeight="1" s="19"/>
+    <row r="316" ht="15.75" customHeight="1" s="19"/>
+    <row r="317" ht="15.75" customHeight="1" s="19"/>
+    <row r="318" ht="15.75" customHeight="1" s="19"/>
+    <row r="319" ht="15.75" customHeight="1" s="19"/>
+    <row r="320" ht="15.75" customHeight="1" s="19"/>
+    <row r="321" ht="15.75" customHeight="1" s="19"/>
+    <row r="322" ht="15.75" customHeight="1" s="19"/>
+    <row r="323" ht="15.75" customHeight="1" s="19"/>
+    <row r="324" ht="15.75" customHeight="1" s="19"/>
+    <row r="325" ht="15.75" customHeight="1" s="19"/>
+    <row r="326" ht="15.75" customHeight="1" s="19"/>
+    <row r="327" ht="15.75" customHeight="1" s="19"/>
+    <row r="328" ht="15.75" customHeight="1" s="19"/>
+    <row r="329" ht="15.75" customHeight="1" s="19"/>
+    <row r="330" ht="15.75" customHeight="1" s="19"/>
+    <row r="331" ht="15.75" customHeight="1" s="19"/>
+    <row r="332" ht="15.75" customHeight="1" s="19"/>
+    <row r="333" ht="15.75" customHeight="1" s="19"/>
+    <row r="334" ht="15.75" customHeight="1" s="19"/>
+    <row r="335" ht="15.75" customHeight="1" s="19"/>
+    <row r="336" ht="15.75" customHeight="1" s="19"/>
+    <row r="337" ht="15.75" customHeight="1" s="19"/>
+    <row r="338" ht="15.75" customHeight="1" s="19"/>
+    <row r="339" ht="15.75" customHeight="1" s="19"/>
+    <row r="340" ht="15.75" customHeight="1" s="19"/>
+    <row r="341" ht="15.75" customHeight="1" s="19"/>
+    <row r="342" ht="15.75" customHeight="1" s="19"/>
+    <row r="343" ht="15.75" customHeight="1" s="19"/>
+    <row r="344" ht="15.75" customHeight="1" s="19"/>
+    <row r="345" ht="15.75" customHeight="1" s="19"/>
+    <row r="346" ht="15.75" customHeight="1" s="19"/>
+    <row r="347" ht="15.75" customHeight="1" s="19"/>
+    <row r="348" ht="15.75" customHeight="1" s="19"/>
+    <row r="349" ht="15.75" customHeight="1" s="19"/>
+    <row r="350" ht="15.75" customHeight="1" s="19"/>
+    <row r="351" ht="15.75" customHeight="1" s="19"/>
+    <row r="352" ht="15.75" customHeight="1" s="19"/>
+    <row r="353" ht="15.75" customHeight="1" s="19"/>
+    <row r="354" ht="15.75" customHeight="1" s="19"/>
+    <row r="355" ht="15.75" customHeight="1" s="19"/>
+    <row r="356" ht="15.75" customHeight="1" s="19"/>
+    <row r="357" ht="15.75" customHeight="1" s="19"/>
+    <row r="358" ht="15.75" customHeight="1" s="19"/>
+    <row r="359" ht="15.75" customHeight="1" s="19"/>
+    <row r="360" ht="15.75" customHeight="1" s="19"/>
+    <row r="361" ht="15.75" customHeight="1" s="19"/>
+    <row r="362" ht="15.75" customHeight="1" s="19"/>
+    <row r="363" ht="15.75" customHeight="1" s="19"/>
+    <row r="364" ht="15.75" customHeight="1" s="19"/>
+    <row r="365" ht="15.75" customHeight="1" s="19"/>
+    <row r="366" ht="15.75" customHeight="1" s="19"/>
+    <row r="367" ht="15.75" customHeight="1" s="19"/>
+    <row r="368" ht="15.75" customHeight="1" s="19"/>
+    <row r="369" ht="15.75" customHeight="1" s="19"/>
+    <row r="370" ht="15.75" customHeight="1" s="19"/>
+    <row r="371" ht="15.75" customHeight="1" s="19"/>
+    <row r="372" ht="15.75" customHeight="1" s="19"/>
+    <row r="373" ht="15.75" customHeight="1" s="19"/>
+    <row r="374" ht="15.75" customHeight="1" s="19"/>
+    <row r="375" ht="15.75" customHeight="1" s="19"/>
+    <row r="376" ht="15.75" customHeight="1" s="19"/>
+    <row r="377" ht="15.75" customHeight="1" s="19"/>
+    <row r="378" ht="15.75" customHeight="1" s="19"/>
+    <row r="379" ht="15.75" customHeight="1" s="19"/>
+    <row r="380" ht="15.75" customHeight="1" s="19"/>
+    <row r="381" ht="15.75" customHeight="1" s="19"/>
+    <row r="382" ht="15.75" customHeight="1" s="19"/>
+    <row r="383" ht="15.75" customHeight="1" s="19"/>
+    <row r="384" ht="15.75" customHeight="1" s="19"/>
+    <row r="385" ht="15.75" customHeight="1" s="19"/>
+    <row r="386" ht="15.75" customHeight="1" s="19"/>
+    <row r="387" ht="15.75" customHeight="1" s="19"/>
+    <row r="388" ht="15.75" customHeight="1" s="19"/>
+    <row r="389" ht="15.75" customHeight="1" s="19"/>
+    <row r="390" ht="15.75" customHeight="1" s="19"/>
+    <row r="391" ht="15.75" customHeight="1" s="19"/>
+    <row r="392" ht="15.75" customHeight="1" s="19"/>
+    <row r="393" ht="15.75" customHeight="1" s="19"/>
+    <row r="394" ht="15.75" customHeight="1" s="19"/>
+    <row r="395" ht="15.75" customHeight="1" s="19"/>
+    <row r="396" ht="15.75" customHeight="1" s="19"/>
+    <row r="397" ht="15.75" customHeight="1" s="19"/>
+    <row r="398" ht="15.75" customHeight="1" s="19"/>
+    <row r="399" ht="15.75" customHeight="1" s="19"/>
+    <row r="400" ht="15.75" customHeight="1" s="19"/>
+    <row r="401" ht="15.75" customHeight="1" s="19"/>
+    <row r="402" ht="15.75" customHeight="1" s="19"/>
+    <row r="403" ht="15.75" customHeight="1" s="19"/>
+    <row r="404" ht="15.75" customHeight="1" s="19"/>
+    <row r="405" ht="15.75" customHeight="1" s="19"/>
+    <row r="406" ht="15.75" customHeight="1" s="19"/>
+    <row r="407" ht="15.75" customHeight="1" s="19"/>
+    <row r="408" ht="15.75" customHeight="1" s="19"/>
+    <row r="409" ht="15.75" customHeight="1" s="19"/>
+    <row r="410" ht="15.75" customHeight="1" s="19"/>
+    <row r="411" ht="15.75" customHeight="1" s="19"/>
+    <row r="412" ht="15.75" customHeight="1" s="19"/>
+    <row r="413" ht="15.75" customHeight="1" s="19"/>
+    <row r="414" ht="15.75" customHeight="1" s="19"/>
+    <row r="415" ht="15.75" customHeight="1" s="19"/>
+    <row r="416" ht="15.75" customHeight="1" s="19"/>
+    <row r="417" ht="15.75" customHeight="1" s="19"/>
+    <row r="418" ht="15.75" customHeight="1" s="19"/>
+    <row r="419" ht="15.75" customHeight="1" s="19"/>
+    <row r="420" ht="15.75" customHeight="1" s="19"/>
+    <row r="421" ht="15.75" customHeight="1" s="19"/>
+    <row r="422" ht="15.75" customHeight="1" s="19"/>
+    <row r="423" ht="15.75" customHeight="1" s="19"/>
+    <row r="424" ht="15.75" customHeight="1" s="19"/>
+    <row r="425" ht="15.75" customHeight="1" s="19"/>
+    <row r="426" ht="15.75" customHeight="1" s="19"/>
+    <row r="427" ht="15.75" customHeight="1" s="19"/>
+    <row r="428" ht="15.75" customHeight="1" s="19"/>
+    <row r="429" ht="15.75" customHeight="1" s="19"/>
+    <row r="430" ht="15.75" customHeight="1" s="19"/>
+    <row r="431" ht="15.75" customHeight="1" s="19"/>
+    <row r="432" ht="15.75" customHeight="1" s="19"/>
+    <row r="433" ht="15.75" customHeight="1" s="19"/>
+    <row r="434" ht="15.75" customHeight="1" s="19"/>
+    <row r="435" ht="15.75" customHeight="1" s="19"/>
+    <row r="436" ht="15.75" customHeight="1" s="19"/>
+    <row r="437" ht="15.75" customHeight="1" s="19"/>
+    <row r="438" ht="15.75" customHeight="1" s="19"/>
+    <row r="439" ht="15.75" customHeight="1" s="19"/>
+    <row r="440" ht="15.75" customHeight="1" s="19"/>
+    <row r="441" ht="15.75" customHeight="1" s="19"/>
+    <row r="442" ht="15.75" customHeight="1" s="19"/>
+    <row r="443" ht="15.75" customHeight="1" s="19"/>
+    <row r="444" ht="15.75" customHeight="1" s="19"/>
+    <row r="445" ht="15.75" customHeight="1" s="19"/>
+    <row r="446" ht="15.75" customHeight="1" s="19"/>
+    <row r="447" ht="15.75" customHeight="1" s="19"/>
+    <row r="448" ht="15.75" customHeight="1" s="19"/>
+    <row r="449" ht="15.75" customHeight="1" s="19"/>
+    <row r="450" ht="15.75" customHeight="1" s="19"/>
+    <row r="451" ht="15.75" customHeight="1" s="19"/>
+    <row r="452" ht="15.75" customHeight="1" s="19"/>
+    <row r="453" ht="15.75" customHeight="1" s="19"/>
+    <row r="454" ht="15.75" customHeight="1" s="19"/>
+    <row r="455" ht="15.75" customHeight="1" s="19"/>
+    <row r="456" ht="15.75" customHeight="1" s="19"/>
+    <row r="457" ht="15.75" customHeight="1" s="19"/>
+    <row r="458" ht="15.75" customHeight="1" s="19"/>
+    <row r="459" ht="15.75" customHeight="1" s="19"/>
+    <row r="460" ht="15.75" customHeight="1" s="19"/>
+    <row r="461" ht="15.75" customHeight="1" s="19"/>
+    <row r="462" ht="15.75" customHeight="1" s="19"/>
+    <row r="463" ht="15.75" customHeight="1" s="19"/>
+    <row r="464" ht="15.75" customHeight="1" s="19"/>
+    <row r="465" ht="15.75" customHeight="1" s="19"/>
+    <row r="466" ht="15.75" customHeight="1" s="19"/>
+    <row r="467" ht="15.75" customHeight="1" s="19"/>
+    <row r="468" ht="15.75" customHeight="1" s="19"/>
+    <row r="469" ht="15.75" customHeight="1" s="19"/>
+    <row r="470" ht="15.75" customHeight="1" s="19"/>
+    <row r="471" ht="15.75" customHeight="1" s="19"/>
+    <row r="472" ht="15.75" customHeight="1" s="19"/>
+    <row r="473" ht="15.75" customHeight="1" s="19"/>
+    <row r="474" ht="15.75" customHeight="1" s="19"/>
+    <row r="475" ht="15.75" customHeight="1" s="19"/>
+    <row r="476" ht="15.75" customHeight="1" s="19"/>
+    <row r="477" ht="15.75" customHeight="1" s="19"/>
+    <row r="478" ht="15.75" customHeight="1" s="19"/>
+    <row r="479" ht="15.75" customHeight="1" s="19"/>
+    <row r="480" ht="15.75" customHeight="1" s="19"/>
+    <row r="481" ht="15.75" customHeight="1" s="19"/>
+    <row r="482" ht="15.75" customHeight="1" s="19"/>
+    <row r="483" ht="15.75" customHeight="1" s="19"/>
+    <row r="484" ht="15.75" customHeight="1" s="19"/>
+    <row r="485" ht="15.75" customHeight="1" s="19"/>
+    <row r="486" ht="15.75" customHeight="1" s="19"/>
+    <row r="487" ht="15.75" customHeight="1" s="19"/>
+    <row r="488" ht="15.75" customHeight="1" s="19"/>
+    <row r="489" ht="15.75" customHeight="1" s="19"/>
+    <row r="490" ht="15.75" customHeight="1" s="19"/>
+    <row r="491" ht="15.75" customHeight="1" s="19"/>
+    <row r="492" ht="15.75" customHeight="1" s="19"/>
+    <row r="493" ht="15.75" customHeight="1" s="19"/>
+    <row r="494" ht="15.75" customHeight="1" s="19"/>
+    <row r="495" ht="15.75" customHeight="1" s="19"/>
+    <row r="496" ht="15.75" customHeight="1" s="19"/>
+    <row r="497" ht="15.75" customHeight="1" s="19"/>
+    <row r="498" ht="15.75" customHeight="1" s="19"/>
+    <row r="499" ht="15.75" customHeight="1" s="19"/>
+    <row r="500" ht="15.75" customHeight="1" s="19"/>
+    <row r="501" ht="15.75" customHeight="1" s="19"/>
+    <row r="502" ht="15.75" customHeight="1" s="19"/>
+    <row r="503" ht="15.75" customHeight="1" s="19"/>
+    <row r="504" ht="15.75" customHeight="1" s="19"/>
+    <row r="505" ht="15.75" customHeight="1" s="19"/>
+    <row r="506" ht="15.75" customHeight="1" s="19"/>
+    <row r="507" ht="15.75" customHeight="1" s="19"/>
+    <row r="508" ht="15.75" customHeight="1" s="19"/>
+    <row r="509" ht="15.75" customHeight="1" s="19"/>
+    <row r="510" ht="15.75" customHeight="1" s="19"/>
+    <row r="511" ht="15.75" customHeight="1" s="19"/>
+    <row r="512" ht="15.75" customHeight="1" s="19"/>
+    <row r="513" ht="15.75" customHeight="1" s="19"/>
+    <row r="514" ht="15.75" customHeight="1" s="19"/>
+    <row r="515" ht="15.75" customHeight="1" s="19"/>
+    <row r="516" ht="15.75" customHeight="1" s="19"/>
+    <row r="517" ht="15.75" customHeight="1" s="19"/>
+    <row r="518" ht="15.75" customHeight="1" s="19"/>
+    <row r="519" ht="15.75" customHeight="1" s="19"/>
+    <row r="520" ht="15.75" customHeight="1" s="19"/>
+    <row r="521" ht="15.75" customHeight="1" s="19"/>
+    <row r="522" ht="15.75" customHeight="1" s="19"/>
+    <row r="523" ht="15.75" customHeight="1" s="19"/>
+    <row r="524" ht="15.75" customHeight="1" s="19"/>
+    <row r="525" ht="15.75" customHeight="1" s="19"/>
+    <row r="526" ht="15.75" customHeight="1" s="19"/>
+    <row r="527" ht="15.75" customHeight="1" s="19"/>
+    <row r="528" ht="15.75" customHeight="1" s="19"/>
+    <row r="529" ht="15.75" customHeight="1" s="19"/>
+    <row r="530" ht="15.75" customHeight="1" s="19"/>
+    <row r="531" ht="15.75" customHeight="1" s="19"/>
+    <row r="532" ht="15.75" customHeight="1" s="19"/>
+    <row r="533" ht="15.75" customHeight="1" s="19"/>
+    <row r="534" ht="15.75" customHeight="1" s="19"/>
+    <row r="535" ht="15.75" customHeight="1" s="19"/>
+    <row r="536" ht="15.75" customHeight="1" s="19"/>
+    <row r="537" ht="15.75" customHeight="1" s="19"/>
+    <row r="538" ht="15.75" customHeight="1" s="19"/>
+    <row r="539" ht="15.75" customHeight="1" s="19"/>
+    <row r="540" ht="15.75" customHeight="1" s="19"/>
+    <row r="541" ht="15.75" customHeight="1" s="19"/>
+    <row r="542" ht="15.75" customHeight="1" s="19"/>
+    <row r="543" ht="15.75" customHeight="1" s="19"/>
+    <row r="544" ht="15.75" customHeight="1" s="19"/>
+    <row r="545" ht="15.75" customHeight="1" s="19"/>
+    <row r="546" ht="15.75" customHeight="1" s="19"/>
+    <row r="547" ht="15.75" customHeight="1" s="19"/>
+    <row r="548" ht="15.75" customHeight="1" s="19"/>
+    <row r="549" ht="15.75" customHeight="1" s="19"/>
+    <row r="550" ht="15.75" customHeight="1" s="19"/>
+    <row r="551" ht="15.75" customHeight="1" s="19"/>
+    <row r="552" ht="15.75" customHeight="1" s="19"/>
+    <row r="553" ht="15.75" customHeight="1" s="19"/>
+    <row r="554" ht="15.75" customHeight="1" s="19"/>
+    <row r="555" ht="15.75" customHeight="1" s="19"/>
+    <row r="556" ht="15.75" customHeight="1" s="19"/>
+    <row r="557" ht="15.75" customHeight="1" s="19"/>
+    <row r="558" ht="15.75" customHeight="1" s="19"/>
+    <row r="559" ht="15.75" customHeight="1" s="19"/>
+    <row r="560" ht="15.75" customHeight="1" s="19"/>
+    <row r="561" ht="15.75" customHeight="1" s="19"/>
+    <row r="562" ht="15.75" customHeight="1" s="19"/>
+    <row r="563" ht="15.75" customHeight="1" s="19"/>
+    <row r="564" ht="15.75" customHeight="1" s="19"/>
+    <row r="565" ht="15.75" customHeight="1" s="19"/>
+    <row r="566" ht="15.75" customHeight="1" s="19"/>
+    <row r="567" ht="15.75" customHeight="1" s="19"/>
+    <row r="568" ht="15.75" customHeight="1" s="19"/>
+    <row r="569" ht="15.75" customHeight="1" s="19"/>
+    <row r="570" ht="15.75" customHeight="1" s="19"/>
+    <row r="571" ht="15.75" customHeight="1" s="19"/>
+    <row r="572" ht="15.75" customHeight="1" s="19"/>
+    <row r="573" ht="15.75" customHeight="1" s="19"/>
+    <row r="574" ht="15.75" customHeight="1" s="19"/>
+    <row r="575" ht="15.75" customHeight="1" s="19"/>
+    <row r="576" ht="15.75" customHeight="1" s="19"/>
+    <row r="577" ht="15.75" customHeight="1" s="19"/>
+    <row r="578" ht="15.75" customHeight="1" s="19"/>
+    <row r="579" ht="15.75" customHeight="1" s="19"/>
+    <row r="580" ht="15.75" customHeight="1" s="19"/>
+    <row r="581" ht="15.75" customHeight="1" s="19"/>
+    <row r="582" ht="15.75" customHeight="1" s="19"/>
+    <row r="583" ht="15.75" customHeight="1" s="19"/>
+    <row r="584" ht="15.75" customHeight="1" s="19"/>
+    <row r="585" ht="15.75" customHeight="1" s="19"/>
+    <row r="586" ht="15.75" customHeight="1" s="19"/>
+    <row r="587" ht="15.75" customHeight="1" s="19"/>
+    <row r="588" ht="15.75" customHeight="1" s="19"/>
+    <row r="589" ht="15.75" customHeight="1" s="19"/>
+    <row r="590" ht="15.75" customHeight="1" s="19"/>
+    <row r="591" ht="15.75" customHeight="1" s="19"/>
+    <row r="592" ht="15.75" customHeight="1" s="19"/>
+    <row r="593" ht="15.75" customHeight="1" s="19"/>
+    <row r="594" ht="15.75" customHeight="1" s="19"/>
+    <row r="595" ht="15.75" customHeight="1" s="19"/>
+    <row r="596" ht="15.75" customHeight="1" s="19"/>
+    <row r="597" ht="15.75" customHeight="1" s="19"/>
+    <row r="598" ht="15.75" customHeight="1" s="19"/>
+    <row r="599" ht="15.75" customHeight="1" s="19"/>
+    <row r="600" ht="15.75" customHeight="1" s="19"/>
+    <row r="601" ht="15.75" customHeight="1" s="19"/>
+    <row r="602" ht="15.75" customHeight="1" s="19"/>
+    <row r="603" ht="15.75" customHeight="1" s="19"/>
+    <row r="604" ht="15.75" customHeight="1" s="19"/>
+    <row r="605" ht="15.75" customHeight="1" s="19"/>
+    <row r="606" ht="15.75" customHeight="1" s="19"/>
+    <row r="607" ht="15.75" customHeight="1" s="19"/>
+    <row r="608" ht="15.75" customHeight="1" s="19"/>
+    <row r="609" ht="15.75" customHeight="1" s="19"/>
+    <row r="610" ht="15.75" customHeight="1" s="19"/>
+    <row r="611" ht="15.75" customHeight="1" s="19"/>
+    <row r="612" ht="15.75" customHeight="1" s="19"/>
+    <row r="613" ht="15.75" customHeight="1" s="19"/>
+    <row r="614" ht="15.75" customHeight="1" s="19"/>
+    <row r="615" ht="15.75" customHeight="1" s="19"/>
+    <row r="616" ht="15.75" customHeight="1" s="19"/>
+    <row r="617" ht="15.75" customHeight="1" s="19"/>
+    <row r="618" ht="15.75" customHeight="1" s="19"/>
+    <row r="619" ht="15.75" customHeight="1" s="19"/>
+    <row r="620" ht="15.75" customHeight="1" s="19"/>
+    <row r="621" ht="15.75" customHeight="1" s="19"/>
+    <row r="622" ht="15.75" customHeight="1" s="19"/>
+    <row r="623" ht="15.75" customHeight="1" s="19"/>
+    <row r="624" ht="15.75" customHeight="1" s="19"/>
+    <row r="625" ht="15.75" customHeight="1" s="19"/>
+    <row r="626" ht="15.75" customHeight="1" s="19"/>
+    <row r="627" ht="15.75" customHeight="1" s="19"/>
+    <row r="628" ht="15.75" customHeight="1" s="19"/>
+    <row r="629" ht="15.75" customHeight="1" s="19"/>
+    <row r="630" ht="15.75" customHeight="1" s="19"/>
+    <row r="631" ht="15.75" customHeight="1" s="19"/>
+    <row r="632" ht="15.75" customHeight="1" s="19"/>
+    <row r="633" ht="15.75" customHeight="1" s="19"/>
+    <row r="634" ht="15.75" customHeight="1" s="19"/>
+    <row r="635" ht="15.75" customHeight="1" s="19"/>
+    <row r="636" ht="15.75" customHeight="1" s="19"/>
+    <row r="637" ht="15.75" customHeight="1" s="19"/>
+    <row r="638" ht="15.75" customHeight="1" s="19"/>
+    <row r="639" ht="15.75" customHeight="1" s="19"/>
+    <row r="640" ht="15.75" customHeight="1" s="19"/>
+    <row r="641" ht="15.75" customHeight="1" s="19"/>
+    <row r="642" ht="15.75" customHeight="1" s="19"/>
+    <row r="643" ht="15.75" customHeight="1" s="19"/>
+    <row r="644" ht="15.75" customHeight="1" s="19"/>
+    <row r="645" ht="15.75" customHeight="1" s="19"/>
+    <row r="646" ht="15.75" customHeight="1" s="19"/>
+    <row r="647" ht="15.75" customHeight="1" s="19"/>
+    <row r="648" ht="15.75" customHeight="1" s="19"/>
+    <row r="649" ht="15.75" customHeight="1" s="19"/>
+    <row r="650" ht="15.75" customHeight="1" s="19"/>
+    <row r="651" ht="15.75" customHeight="1" s="19"/>
+    <row r="652" ht="15.75" customHeight="1" s="19"/>
+    <row r="653" ht="15.75" customHeight="1" s="19"/>
+    <row r="654" ht="15.75" customHeight="1" s="19"/>
+    <row r="655" ht="15.75" customHeight="1" s="19"/>
+    <row r="656" ht="15.75" customHeight="1" s="19"/>
+    <row r="657" ht="15.75" customHeight="1" s="19"/>
+    <row r="658" ht="15.75" customHeight="1" s="19"/>
+    <row r="659" ht="15.75" customHeight="1" s="19"/>
+    <row r="660" ht="15.75" customHeight="1" s="19"/>
+    <row r="661" ht="15.75" customHeight="1" s="19"/>
+    <row r="662" ht="15.75" customHeight="1" s="19"/>
+    <row r="663" ht="15.75" customHeight="1" s="19"/>
+    <row r="664" ht="15.75" customHeight="1" s="19"/>
+    <row r="665" ht="15.75" customHeight="1" s="19"/>
+    <row r="666" ht="15.75" customHeight="1" s="19"/>
+    <row r="667" ht="15.75" customHeight="1" s="19"/>
+    <row r="668" ht="15.75" customHeight="1" s="19"/>
+    <row r="669" ht="15.75" customHeight="1" s="19"/>
+    <row r="670" ht="15.75" customHeight="1" s="19"/>
+    <row r="671" ht="15.75" customHeight="1" s="19"/>
+    <row r="672" ht="15.75" customHeight="1" s="19"/>
+    <row r="673" ht="15.75" customHeight="1" s="19"/>
+    <row r="674" ht="15.75" customHeight="1" s="19"/>
+    <row r="675" ht="15.75" customHeight="1" s="19"/>
+    <row r="676" ht="15.75" customHeight="1" s="19"/>
+    <row r="677" ht="15.75" customHeight="1" s="19"/>
+    <row r="678" ht="15.75" customHeight="1" s="19"/>
+    <row r="679" ht="15.75" customHeight="1" s="19"/>
+    <row r="680" ht="15.75" customHeight="1" s="19"/>
+    <row r="681" ht="15.75" customHeight="1" s="19"/>
+    <row r="682" ht="15.75" customHeight="1" s="19"/>
+    <row r="683" ht="15.75" customHeight="1" s="19"/>
+    <row r="684" ht="15.75" customHeight="1" s="19"/>
+    <row r="685" ht="15.75" customHeight="1" s="19"/>
+    <row r="686" ht="15.75" customHeight="1" s="19"/>
+    <row r="687" ht="15.75" customHeight="1" s="19"/>
+    <row r="688" ht="15.75" customHeight="1" s="19"/>
+    <row r="689" ht="15.75" customHeight="1" s="19"/>
+    <row r="690" ht="15.75" customHeight="1" s="19"/>
+    <row r="691" ht="15.75" customHeight="1" s="19"/>
+    <row r="692" ht="15.75" customHeight="1" s="19"/>
+    <row r="693" ht="15.75" customHeight="1" s="19"/>
+    <row r="694" ht="15.75" customHeight="1" s="19"/>
+    <row r="695" ht="15.75" customHeight="1" s="19"/>
+    <row r="696" ht="15.75" customHeight="1" s="19"/>
+    <row r="697" ht="15.75" customHeight="1" s="19"/>
+    <row r="698" ht="15.75" customHeight="1" s="19"/>
+    <row r="699" ht="15.75" customHeight="1" s="19"/>
+    <row r="700" ht="15.75" customHeight="1" s="19"/>
+    <row r="701" ht="15.75" customHeight="1" s="19"/>
+    <row r="702" ht="15.75" customHeight="1" s="19"/>
+    <row r="703" ht="15.75" customHeight="1" s="19"/>
+    <row r="704" ht="15.75" customHeight="1" s="19"/>
+    <row r="705" ht="15.75" customHeight="1" s="19"/>
+    <row r="706" ht="15.75" customHeight="1" s="19"/>
+    <row r="707" ht="15.75" customHeight="1" s="19"/>
+    <row r="708" ht="15.75" customHeight="1" s="19"/>
+    <row r="709" ht="15.75" customHeight="1" s="19"/>
+    <row r="710" ht="15.75" customHeight="1" s="19"/>
+    <row r="711" ht="15.75" customHeight="1" s="19"/>
+    <row r="712" ht="15.75" customHeight="1" s="19"/>
+    <row r="713" ht="15.75" customHeight="1" s="19"/>
+    <row r="714" ht="15.75" customHeight="1" s="19"/>
+    <row r="715" ht="15.75" customHeight="1" s="19"/>
+    <row r="716" ht="15.75" customHeight="1" s="19"/>
+    <row r="717" ht="15.75" customHeight="1" s="19"/>
+    <row r="718" ht="15.75" customHeight="1" s="19"/>
+    <row r="719" ht="15.75" customHeight="1" s="19"/>
+    <row r="720" ht="15.75" customHeight="1" s="19"/>
+    <row r="721" ht="15.75" customHeight="1" s="19"/>
+    <row r="722" ht="15.75" customHeight="1" s="19"/>
+    <row r="723" ht="15.75" customHeight="1" s="19"/>
+    <row r="724" ht="15.75" customHeight="1" s="19"/>
+    <row r="725" ht="15.75" customHeight="1" s="19"/>
+    <row r="726" ht="15.75" customHeight="1" s="19"/>
+    <row r="727" ht="15.75" customHeight="1" s="19"/>
+    <row r="728" ht="15.75" customHeight="1" s="19"/>
+    <row r="729" ht="15.75" customHeight="1" s="19"/>
+    <row r="730" ht="15.75" customHeight="1" s="19"/>
+    <row r="731" ht="15.75" customHeight="1" s="19"/>
+    <row r="732" ht="15.75" customHeight="1" s="19"/>
+    <row r="733" ht="15.75" customHeight="1" s="19"/>
+    <row r="734" ht="15.75" customHeight="1" s="19"/>
+    <row r="735" ht="15.75" customHeight="1" s="19"/>
+    <row r="736" ht="15.75" customHeight="1" s="19"/>
+    <row r="737" ht="15.75" customHeight="1" s="19"/>
+    <row r="738" ht="15.75" customHeight="1" s="19"/>
+    <row r="739" ht="15.75" customHeight="1" s="19"/>
+    <row r="740" ht="15.75" customHeight="1" s="19"/>
+    <row r="741" ht="15.75" customHeight="1" s="19"/>
+    <row r="742" ht="15.75" customHeight="1" s="19"/>
+    <row r="743" ht="15.75" customHeight="1" s="19"/>
+    <row r="744" ht="15.75" customHeight="1" s="19"/>
+    <row r="745" ht="15.75" customHeight="1" s="19"/>
+    <row r="746" ht="15.75" customHeight="1" s="19"/>
+    <row r="747" ht="15.75" customHeight="1" s="19"/>
+    <row r="748" ht="15.75" customHeight="1" s="19"/>
+    <row r="749" ht="15.75" customHeight="1" s="19"/>
+    <row r="750" ht="15.75" customHeight="1" s="19"/>
+    <row r="751" ht="15.75" customHeight="1" s="19"/>
+    <row r="752" ht="15.75" customHeight="1" s="19"/>
+    <row r="753" ht="15.75" customHeight="1" s="19"/>
+    <row r="754" ht="15.75" customHeight="1" s="19"/>
+    <row r="755" ht="15.75" customHeight="1" s="19"/>
+    <row r="756" ht="15.75" customHeight="1" s="19"/>
+    <row r="757" ht="15.75" customHeight="1" s="19"/>
+    <row r="758" ht="15.75" customHeight="1" s="19"/>
+    <row r="759" ht="15.75" customHeight="1" s="19"/>
+    <row r="760" ht="15.75" customHeight="1" s="19"/>
+    <row r="761" ht="15.75" customHeight="1" s="19"/>
+    <row r="762" ht="15.75" customHeight="1" s="19"/>
+    <row r="763" ht="15.75" customHeight="1" s="19"/>
+    <row r="764" ht="15.75" customHeight="1" s="19"/>
+    <row r="765" ht="15.75" customHeight="1" s="19"/>
+    <row r="766" ht="15.75" customHeight="1" s="19"/>
+    <row r="767" ht="15.75" customHeight="1" s="19"/>
+    <row r="768" ht="15.75" customHeight="1" s="19"/>
+    <row r="769" ht="15.75" customHeight="1" s="19"/>
+    <row r="770" ht="15.75" customHeight="1" s="19"/>
+    <row r="771" ht="15.75" customHeight="1" s="19"/>
+    <row r="772" ht="15.75" customHeight="1" s="19"/>
+    <row r="773" ht="15.75" customHeight="1" s="19"/>
+    <row r="774" ht="15.75" customHeight="1" s="19"/>
+    <row r="775" ht="15.75" customHeight="1" s="19"/>
+    <row r="776" ht="15.75" customHeight="1" s="19"/>
+    <row r="777" ht="15.75" customHeight="1" s="19"/>
+    <row r="778" ht="15.75" customHeight="1" s="19"/>
+    <row r="779" ht="15.75" customHeight="1" s="19"/>
+    <row r="780" ht="15.75" customHeight="1" s="19"/>
+    <row r="781" ht="15.75" customHeight="1" s="19"/>
+    <row r="782" ht="15.75" customHeight="1" s="19"/>
+    <row r="783" ht="15.75" customHeight="1" s="19"/>
+    <row r="784" ht="15.75" customHeight="1" s="19"/>
+    <row r="785" ht="15.75" customHeight="1" s="19"/>
+    <row r="786" ht="15.75" customHeight="1" s="19"/>
+    <row r="787" ht="15.75" customHeight="1" s="19"/>
+    <row r="788" ht="15.75" customHeight="1" s="19"/>
+    <row r="789" ht="15.75" customHeight="1" s="19"/>
+    <row r="790" ht="15.75" customHeight="1" s="19"/>
+    <row r="791" ht="15.75" customHeight="1" s="19"/>
+    <row r="792" ht="15.75" customHeight="1" s="19"/>
+    <row r="793" ht="15.75" customHeight="1" s="19"/>
+    <row r="794" ht="15.75" customHeight="1" s="19"/>
+    <row r="795" ht="15.75" customHeight="1" s="19"/>
+    <row r="796" ht="15.75" customHeight="1" s="19"/>
+    <row r="797" ht="15.75" customHeight="1" s="19"/>
+    <row r="798" ht="15.75" customHeight="1" s="19"/>
+    <row r="799" ht="15.75" customHeight="1" s="19"/>
+    <row r="800" ht="15.75" customHeight="1" s="19"/>
+    <row r="801" ht="15.75" customHeight="1" s="19"/>
+    <row r="802" ht="15.75" customHeight="1" s="19"/>
+    <row r="803" ht="15.75" customHeight="1" s="19"/>
+    <row r="804" ht="15.75" customHeight="1" s="19"/>
+    <row r="805" ht="15.75" customHeight="1" s="19"/>
+    <row r="806" ht="15.75" customHeight="1" s="19"/>
+    <row r="807" ht="15.75" customHeight="1" s="19"/>
+    <row r="808" ht="15.75" customHeight="1" s="19"/>
+    <row r="809" ht="15.75" customHeight="1" s="19"/>
+    <row r="810" ht="15.75" customHeight="1" s="19"/>
+    <row r="811" ht="15.75" customHeight="1" s="19"/>
+    <row r="812" ht="15.75" customHeight="1" s="19"/>
+    <row r="813" ht="15.75" customHeight="1" s="19"/>
+    <row r="814" ht="15.75" customHeight="1" s="19"/>
+    <row r="815" ht="15.75" customHeight="1" s="19"/>
+    <row r="816" ht="15.75" customHeight="1" s="19"/>
+    <row r="817" ht="15.75" customHeight="1" s="19"/>
+    <row r="818" ht="15.75" customHeight="1" s="19"/>
+    <row r="819" ht="15.75" customHeight="1" s="19"/>
+    <row r="820" ht="15.75" customHeight="1" s="19"/>
+    <row r="821" ht="15.75" customHeight="1" s="19"/>
+    <row r="822" ht="15.75" customHeight="1" s="19"/>
+    <row r="823" ht="15.75" customHeight="1" s="19"/>
+    <row r="824" ht="15.75" customHeight="1" s="19"/>
+    <row r="825" ht="15.75" customHeight="1" s="19"/>
+    <row r="826" ht="15.75" customHeight="1" s="19"/>
+    <row r="827" ht="15.75" customHeight="1" s="19"/>
+    <row r="828" ht="15.75" customHeight="1" s="19"/>
+    <row r="829" ht="15.75" customHeight="1" s="19"/>
+    <row r="830" ht="15.75" customHeight="1" s="19"/>
+    <row r="831" ht="15.75" customHeight="1" s="19"/>
+    <row r="832" ht="15.75" customHeight="1" s="19"/>
+    <row r="833" ht="15.75" customHeight="1" s="19"/>
+    <row r="834" ht="15.75" customHeight="1" s="19"/>
+    <row r="835" ht="15.75" customHeight="1" s="19"/>
+    <row r="836" ht="15.75" customHeight="1" s="19"/>
+    <row r="837" ht="15.75" customHeight="1" s="19"/>
+    <row r="838" ht="15.75" customHeight="1" s="19"/>
+    <row r="839" ht="15.75" customHeight="1" s="19"/>
+    <row r="840" ht="15.75" customHeight="1" s="19"/>
+    <row r="841" ht="15.75" customHeight="1" s="19"/>
+    <row r="842" ht="15.75" customHeight="1" s="19"/>
+    <row r="843" ht="15.75" customHeight="1" s="19"/>
+    <row r="844" ht="15.75" customHeight="1" s="19"/>
+    <row r="845" ht="15.75" customHeight="1" s="19"/>
+    <row r="846" ht="15.75" customHeight="1" s="19"/>
+    <row r="847" ht="15.75" customHeight="1" s="19"/>
+    <row r="848" ht="15.75" customHeight="1" s="19"/>
+    <row r="849" ht="15.75" customHeight="1" s="19"/>
+    <row r="850" ht="15.75" customHeight="1" s="19"/>
+    <row r="851" ht="15.75" customHeight="1" s="19"/>
+    <row r="852" ht="15.75" customHeight="1" s="19"/>
+    <row r="853" ht="15.75" customHeight="1" s="19"/>
+    <row r="854" ht="15.75" customHeight="1" s="19"/>
+    <row r="855" ht="15.75" customHeight="1" s="19"/>
+    <row r="856" ht="15.75" customHeight="1" s="19"/>
+    <row r="857" ht="15.75" customHeight="1" s="19"/>
+    <row r="858" ht="15.75" customHeight="1" s="19"/>
+    <row r="859" ht="15.75" customHeight="1" s="19"/>
+    <row r="860" ht="15.75" customHeight="1" s="19"/>
+    <row r="861" ht="15.75" customHeight="1" s="19"/>
+    <row r="862" ht="15.75" customHeight="1" s="19"/>
+    <row r="863" ht="15.75" customHeight="1" s="19"/>
+    <row r="864" ht="15.75" customHeight="1" s="19"/>
+    <row r="865" ht="15.75" customHeight="1" s="19"/>
+    <row r="866" ht="15.75" customHeight="1" s="19"/>
+    <row r="867" ht="15.75" customHeight="1" s="19"/>
+    <row r="868" ht="15.75" customHeight="1" s="19"/>
+    <row r="869" ht="15.75" customHeight="1" s="19"/>
+    <row r="870" ht="15.75" customHeight="1" s="19"/>
+    <row r="871" ht="15.75" customHeight="1" s="19"/>
+    <row r="872" ht="15.75" customHeight="1" s="19"/>
+    <row r="873" ht="15.75" customHeight="1" s="19"/>
+    <row r="874" ht="15.75" customHeight="1" s="19"/>
+    <row r="875" ht="15.75" customHeight="1" s="19"/>
+    <row r="876" ht="15.75" customHeight="1" s="19"/>
+    <row r="877" ht="15.75" customHeight="1" s="19"/>
+    <row r="878" ht="15.75" customHeight="1" s="19"/>
+    <row r="879" ht="15.75" customHeight="1" s="19"/>
+    <row r="880" ht="15.75" customHeight="1" s="19"/>
+    <row r="881" ht="15.75" customHeight="1" s="19"/>
+    <row r="882" ht="15.75" customHeight="1" s="19"/>
+    <row r="883" ht="15.75" customHeight="1" s="19"/>
+    <row r="884" ht="15.75" customHeight="1" s="19"/>
+    <row r="885" ht="15.75" customHeight="1" s="19"/>
+    <row r="886" ht="15.75" customHeight="1" s="19"/>
+    <row r="887" ht="15.75" customHeight="1" s="19"/>
+    <row r="888" ht="15.75" customHeight="1" s="19"/>
+    <row r="889" ht="15.75" customHeight="1" s="19"/>
+    <row r="890" ht="15.75" customHeight="1" s="19"/>
+    <row r="891" ht="15.75" customHeight="1" s="19"/>
+    <row r="892" ht="15.75" customHeight="1" s="19"/>
+    <row r="893" ht="15.75" customHeight="1" s="19"/>
+    <row r="894" ht="15.75" customHeight="1" s="19"/>
+    <row r="895" ht="15.75" customHeight="1" s="19"/>
+    <row r="896" ht="15.75" customHeight="1" s="19"/>
+    <row r="897" ht="15.75" customHeight="1" s="19"/>
+    <row r="898" ht="15.75" customHeight="1" s="19"/>
+    <row r="899" ht="15.75" customHeight="1" s="19"/>
+    <row r="900" ht="15.75" customHeight="1" s="19"/>
+    <row r="901" ht="15.75" customHeight="1" s="19"/>
+    <row r="902" ht="15.75" customHeight="1" s="19"/>
+    <row r="903" ht="15.75" customHeight="1" s="19"/>
+    <row r="904" ht="15.75" customHeight="1" s="19"/>
+    <row r="905" ht="15.75" customHeight="1" s="19"/>
+    <row r="906" ht="15.75" customHeight="1" s="19"/>
+    <row r="907" ht="15.75" customHeight="1" s="19"/>
+    <row r="908" ht="15.75" customHeight="1" s="19"/>
+    <row r="909" ht="15.75" customHeight="1" s="19"/>
+    <row r="910" ht="15.75" customHeight="1" s="19"/>
+    <row r="911" ht="15.75" customHeight="1" s="19"/>
+    <row r="912" ht="15.75" customHeight="1" s="19"/>
+    <row r="913" ht="15.75" customHeight="1" s="19"/>
+    <row r="914" ht="15.75" customHeight="1" s="19"/>
+    <row r="915" ht="15.75" customHeight="1" s="19"/>
+    <row r="916" ht="15.75" customHeight="1" s="19"/>
+    <row r="917" ht="15.75" customHeight="1" s="19"/>
+    <row r="918" ht="15.75" customHeight="1" s="19"/>
+    <row r="919" ht="15.75" customHeight="1" s="19"/>
+    <row r="920" ht="15.75" customHeight="1" s="19"/>
+    <row r="921" ht="15.75" customHeight="1" s="19"/>
+    <row r="922" ht="15.75" customHeight="1" s="19"/>
+    <row r="923" ht="15.75" customHeight="1" s="19"/>
+    <row r="924" ht="15.75" customHeight="1" s="19"/>
+    <row r="925" ht="15.75" customHeight="1" s="19"/>
+    <row r="926" ht="15.75" customHeight="1" s="19"/>
+    <row r="927" ht="15.75" customHeight="1" s="19"/>
+    <row r="928" ht="15.75" customHeight="1" s="19"/>
+    <row r="929" ht="15.75" customHeight="1" s="19"/>
+    <row r="930" ht="15.75" customHeight="1" s="19"/>
+    <row r="931" ht="15.75" customHeight="1" s="19"/>
+    <row r="932" ht="15.75" customHeight="1" s="19"/>
+    <row r="933" ht="15.75" customHeight="1" s="19"/>
+    <row r="934" ht="15.75" customHeight="1" s="19"/>
+    <row r="935" ht="15.75" customHeight="1" s="19"/>
+    <row r="936" ht="15.75" customHeight="1" s="19"/>
+    <row r="937" ht="15.75" customHeight="1" s="19"/>
+    <row r="938" ht="15.75" customHeight="1" s="19"/>
+    <row r="939" ht="15.75" customHeight="1" s="19"/>
+    <row r="940" ht="15.75" customHeight="1" s="19"/>
+    <row r="941" ht="15.75" customHeight="1" s="19"/>
+    <row r="942" ht="15.75" customHeight="1" s="19"/>
+    <row r="943" ht="15.75" customHeight="1" s="19"/>
+    <row r="944" ht="15.75" customHeight="1" s="19"/>
+    <row r="945" ht="15.75" customHeight="1" s="19"/>
+    <row r="946" ht="15.75" customHeight="1" s="19"/>
+    <row r="947" ht="15.75" customHeight="1" s="19"/>
+    <row r="948" ht="15.75" customHeight="1" s="19"/>
+    <row r="949" ht="15.75" customHeight="1" s="19"/>
+    <row r="950" ht="15.75" customHeight="1" s="19"/>
+    <row r="951" ht="15.75" customHeight="1" s="19"/>
+    <row r="952" ht="15.75" customHeight="1" s="19"/>
+    <row r="953" ht="15.75" customHeight="1" s="19"/>
+    <row r="954" ht="15.75" customHeight="1" s="19"/>
+    <row r="955" ht="15.75" customHeight="1" s="19"/>
+    <row r="956" ht="15.75" customHeight="1" s="19"/>
+    <row r="957" ht="15.75" customHeight="1" s="19"/>
+    <row r="958" ht="15.75" customHeight="1" s="19"/>
+    <row r="959" ht="15.75" customHeight="1" s="19"/>
+    <row r="960" ht="15.75" customHeight="1" s="19"/>
+    <row r="961" ht="15.75" customHeight="1" s="19"/>
+    <row r="962" ht="15.75" customHeight="1" s="19"/>
+    <row r="963" ht="15.75" customHeight="1" s="19"/>
+    <row r="964" ht="15.75" customHeight="1" s="19"/>
+    <row r="965" ht="15.75" customHeight="1" s="19"/>
+    <row r="966" ht="15.75" customHeight="1" s="19"/>
+    <row r="967" ht="15.75" customHeight="1" s="19"/>
+    <row r="968" ht="15.75" customHeight="1" s="19"/>
+    <row r="969" ht="15.75" customHeight="1" s="19"/>
+    <row r="970" ht="15.75" customHeight="1" s="19"/>
+    <row r="971" ht="15.75" customHeight="1" s="19"/>
+    <row r="972" ht="15.75" customHeight="1" s="19"/>
+    <row r="973" ht="15.75" customHeight="1" s="19"/>
+    <row r="974" ht="15.75" customHeight="1" s="19"/>
+    <row r="975" ht="15.75" customHeight="1" s="19"/>
+    <row r="976" ht="15.75" customHeight="1" s="19"/>
+    <row r="977" ht="15.75" customHeight="1" s="19"/>
+    <row r="978" ht="15.75" customHeight="1" s="19"/>
+    <row r="979" ht="15.75" customHeight="1" s="19"/>
+    <row r="980" ht="15.75" customHeight="1" s="19"/>
+    <row r="981" ht="15.75" customHeight="1" s="19"/>
+    <row r="982" ht="15.75" customHeight="1" s="19"/>
+    <row r="983" ht="15.75" customHeight="1" s="19"/>
+    <row r="984" ht="15.75" customHeight="1" s="19"/>
+    <row r="985" ht="15.75" customHeight="1" s="19"/>
+    <row r="986" ht="15.75" customHeight="1" s="19"/>
+    <row r="987" ht="15.75" customHeight="1" s="19"/>
+    <row r="988" ht="15.75" customHeight="1" s="19"/>
+    <row r="989" ht="15.75" customHeight="1" s="19"/>
+    <row r="990" ht="15.75" customHeight="1" s="19"/>
+    <row r="991" ht="15.75" customHeight="1" s="19"/>
+    <row r="992" ht="15.75" customHeight="1" s="19"/>
+    <row r="993" ht="15.75" customHeight="1" s="19"/>
+    <row r="994" ht="15.75" customHeight="1" s="19"/>
+    <row r="995" ht="15.75" customHeight="1" s="19"/>
+    <row r="996" ht="15.75" customHeight="1" s="19"/>
+    <row r="997" ht="15.75" customHeight="1" s="19"/>
+    <row r="998" ht="15.75" customHeight="1" s="19"/>
+    <row r="999" ht="15.75" customHeight="1" s="19"/>
+    <row r="1000" ht="15.75" customHeight="1" s="19"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col width="24.75" customWidth="1" style="19" min="1" max="1"/>
+    <col width="56.75" customWidth="1" style="19" min="2" max="2"/>
+    <col width="12.63" customWidth="1" style="19" min="3" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1" s="19">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="n"/>
+    </row>
+    <row r="2" ht="17.25" customHeight="1" s="19">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>SPM-87-TC12</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30.75" customHeight="1" s="19">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>The assigned Coordinator is notified of the decision with the changes required</t>
         </is>
@@ -6094,7 +7352,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>npm run fixtures:spm87 has been run; 'SPM87 Lakeside Conference' is in Safety review, assigned to Daniel Tan. Logged in as Hana Yusof (hana.yusof@connectsphere.com / password123). This case changes the event - run npm run fixtures:spm87 afterwards.</t>
         </is>
@@ -6106,7 +7364,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>1. Click 'Safety Checks' in the sidebar
 2. Click 'SPM87 Lakeside Conference' in the list
@@ -6123,7 +7381,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Event: SPM87 Lakeside Conference
 Coordinator: daniel.tan@connectsphere.com</t>
@@ -6136,7 +7394,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Step 3: The message 'Changes requested. The event is back in Planning and the coordinator has been notified.' is shown.
 Step 6: The Notifications list has a new notification titled 'Safety check: changes requested' for 'SPM87 Lakeside Conference', which includes 'Add a second fire marshal at the east exit.'</t>
@@ -6149,7 +7407,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -6181,7 +7439,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>Step 3: The message 'Changes requested. The event is back in Planning and the coordinator has been notified.' is shown.
 Step 6: The Notifications list has a new notification titled 'Safety check: changes requested' for 'SPM87 Lakeside Conference', which includes 'Add a second fire marshal at the east exit.'</t>
@@ -6218,7 +7476,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -6248,7 +7506,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Step 3: The message 'Changes requested. The event is back in Planning and the coordinator has been notified.' is shown.
 Step 6: The Notifications list has a new notification titled 'Safety check: changes requested' for 'SPM87 Lakeside Conference', which includes 'Add a second fire marshal at the east exit.'</t>
@@ -6285,7 +7543,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>Kayalvizhi</t>
         </is>
@@ -7288,1236 +8546,69 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24.75" customWidth="1" style="19" min="1" max="1"/>
-    <col width="56.75" customWidth="1" style="19" min="2" max="2"/>
-    <col width="12.63" customWidth="1" style="19" min="3" max="6"/>
+    <col width="5" customWidth="1" style="19" min="1" max="1"/>
+    <col width="75" customWidth="1" style="19" min="2" max="2"/>
+    <col width="40" customWidth="1" style="19" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="19">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B1" s="9" t="n"/>
-    </row>
-    <row r="2" ht="17.25" customHeight="1" s="19">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" s="17" t="inlineStr">
-        <is>
-          <t>SPM-87-TC01</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30.75" customHeight="1" s="19">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>Summary</t>
-        </is>
-      </c>
-      <c r="B3" s="17" t="inlineStr">
-        <is>
-          <t>The Safety Checks list shows events awaiting a check, earliest event date first</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="111.75" customHeight="1" s="19">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>Pre-conditions</t>
-        </is>
-      </c>
-      <c r="B4" s="17" t="inlineStr">
-        <is>
-          <t>npm run fixtures:spm87 has been run. Five SPM87 events are in Safety review: 'SPM87 Hillside Workshop' (8 Oct 2027), 'SPM87 Lakeside Conference' (12 Oct 2027), 'SPM87 Waterfront Gala' (18 Oct 2027), 'SPM87 Rooftop Launch Party' (20 Oct 2027) and 'SPM87 Twin Tab Briefing' (22 Oct 2027). They were submitted in the reverse order, newest event first. 'SPM87 Unsubmitted Planning Day' is in Planning. Other stories' events may also be listed; only the SPM87 ones are checked here.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30.75" customHeight="1" s="19">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>Test Steps</t>
-        </is>
-      </c>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t>1. Log in as hana.yusof@connectsphere.com with password123
-2. Click 'Safety Checks' in the sidebar</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="44.25" customHeight="1" s="19">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>Test Data</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>Safety Officer: hana.yusof@connectsphere.com (Hana Yusof)
-SPM87 events in Safety review dated 8, 12, 18, 20 and 22 Oct 2027</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="84.75" customHeight="1" s="19">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>Step 2: The Safety Checks page lists the five SPM87 events in Safety review in this order: SPM87 Hillside Workshop, SPM87 Lakeside Conference, SPM87 Waterfront Gala, SPM87 Rooftop Launch Party, SPM87 Twin Tab Briefing - by event date, not by when they were submitted. 'SPM87 Unsubmitted Planning Day' is not listed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="17.25" customHeight="1" s="19">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>Janelle</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="15.75" customHeight="1" s="19">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>Creation Date</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="n">
-        <v>46308</v>
-      </c>
-    </row>
-    <row r="10" ht="15.75" customHeight="1" s="19"/>
-    <row r="11" ht="15.75" customHeight="1" s="19">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="n"/>
-      <c r="C11" s="14" t="n"/>
-    </row>
-    <row r="12" ht="15.75" customHeight="1" s="19">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>Step 2: The Safety Checks page lists the five SPM87 events in Safety review in this order: SPM87 Hillside Workshop, SPM87 Lakeside Conference, SPM87 Waterfront Gala, SPM87 Rooftop Launch Party, SPM87 Twin Tab Briefing - by event date, not by when they were submitted. 'SPM87 Unsubmitted Planning Day' is not listed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="15.75" customHeight="1" s="19">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="15.75" customHeight="1" s="19">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="15.75" customHeight="1" s="19">
-      <c r="A15" s="16" t="inlineStr">
-        <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>Janelle</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="15.75" customHeight="1" s="19">
-      <c r="A16" s="16" t="inlineStr">
-        <is>
-          <t>Date of Execution</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="n">
-        <v>46308</v>
-      </c>
-    </row>
-    <row r="17" ht="15.75" customHeight="1" s="19">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="n"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1" s="19">
-      <c r="A18" s="16" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>Step 2: The Safety Checks page lists the five SPM87 events in Safety review in this order: SPM87 Hillside Workshop, SPM87 Lakeside Conference, SPM87 Waterfront Gala, SPM87 Rooftop Launch Party, SPM87 Twin Tab Briefing - by event date, not by when they were submitted. 'SPM87 Unsubmitted Planning Day' is not listed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15.75" customHeight="1" s="19">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15.75" customHeight="1" s="19">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1" s="19">
-      <c r="A21" s="16" t="inlineStr">
-        <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>Kayalvizhi</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1" s="19">
-      <c r="A22" s="16" t="inlineStr">
-        <is>
-          <t>Date of Execution</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1" s="19"/>
-    <row r="24" ht="15.75" customHeight="1" s="19"/>
-    <row r="25" ht="15.75" customHeight="1" s="19"/>
-    <row r="26" ht="15.75" customHeight="1" s="19"/>
-    <row r="27" ht="15.75" customHeight="1" s="19"/>
-    <row r="28" ht="15.75" customHeight="1" s="19"/>
-    <row r="29" ht="15.75" customHeight="1" s="19"/>
-    <row r="30" ht="15.75" customHeight="1" s="19"/>
-    <row r="31" ht="15.75" customHeight="1" s="19"/>
-    <row r="32" ht="15.75" customHeight="1" s="19"/>
-    <row r="33" ht="15.75" customHeight="1" s="19"/>
-    <row r="34" ht="15.75" customHeight="1" s="19"/>
-    <row r="35" ht="15.75" customHeight="1" s="19"/>
-    <row r="36" ht="15.75" customHeight="1" s="19"/>
-    <row r="37" ht="15.75" customHeight="1" s="19"/>
-    <row r="38" ht="15.75" customHeight="1" s="19"/>
-    <row r="39" ht="15.75" customHeight="1" s="19"/>
-    <row r="40" ht="15.75" customHeight="1" s="19"/>
-    <row r="41" ht="15.75" customHeight="1" s="19"/>
-    <row r="42" ht="15.75" customHeight="1" s="19"/>
-    <row r="43" ht="15.75" customHeight="1" s="19"/>
-    <row r="44" ht="15.75" customHeight="1" s="19"/>
-    <row r="45" ht="15.75" customHeight="1" s="19"/>
-    <row r="46" ht="15.75" customHeight="1" s="19"/>
-    <row r="47" ht="15.75" customHeight="1" s="19"/>
-    <row r="48" ht="15.75" customHeight="1" s="19"/>
-    <row r="49" ht="15.75" customHeight="1" s="19"/>
-    <row r="50" ht="15.75" customHeight="1" s="19"/>
-    <row r="51" ht="15.75" customHeight="1" s="19"/>
-    <row r="52" ht="15.75" customHeight="1" s="19"/>
-    <row r="53" ht="15.75" customHeight="1" s="19"/>
-    <row r="54" ht="15.75" customHeight="1" s="19"/>
-    <row r="55" ht="15.75" customHeight="1" s="19"/>
-    <row r="56" ht="15.75" customHeight="1" s="19"/>
-    <row r="57" ht="15.75" customHeight="1" s="19"/>
-    <row r="58" ht="15.75" customHeight="1" s="19"/>
-    <row r="59" ht="15.75" customHeight="1" s="19"/>
-    <row r="60" ht="15.75" customHeight="1" s="19"/>
-    <row r="61" ht="15.75" customHeight="1" s="19"/>
-    <row r="62" ht="15.75" customHeight="1" s="19"/>
-    <row r="63" ht="15.75" customHeight="1" s="19"/>
-    <row r="64" ht="15.75" customHeight="1" s="19"/>
-    <row r="65" ht="15.75" customHeight="1" s="19"/>
-    <row r="66" ht="15.75" customHeight="1" s="19"/>
-    <row r="67" ht="15.75" customHeight="1" s="19"/>
-    <row r="68" ht="15.75" customHeight="1" s="19"/>
-    <row r="69" ht="15.75" customHeight="1" s="19"/>
-    <row r="70" ht="15.75" customHeight="1" s="19"/>
-    <row r="71" ht="15.75" customHeight="1" s="19"/>
-    <row r="72" ht="15.75" customHeight="1" s="19"/>
-    <row r="73" ht="15.75" customHeight="1" s="19"/>
-    <row r="74" ht="15.75" customHeight="1" s="19"/>
-    <row r="75" ht="15.75" customHeight="1" s="19"/>
-    <row r="76" ht="15.75" customHeight="1" s="19"/>
-    <row r="77" ht="15.75" customHeight="1" s="19"/>
-    <row r="78" ht="15.75" customHeight="1" s="19"/>
-    <row r="79" ht="15.75" customHeight="1" s="19"/>
-    <row r="80" ht="15.75" customHeight="1" s="19"/>
-    <row r="81" ht="15.75" customHeight="1" s="19"/>
-    <row r="82" ht="15.75" customHeight="1" s="19"/>
-    <row r="83" ht="15.75" customHeight="1" s="19"/>
-    <row r="84" ht="15.75" customHeight="1" s="19"/>
-    <row r="85" ht="15.75" customHeight="1" s="19"/>
-    <row r="86" ht="15.75" customHeight="1" s="19"/>
-    <row r="87" ht="15.75" customHeight="1" s="19"/>
-    <row r="88" ht="15.75" customHeight="1" s="19"/>
-    <row r="89" ht="15.75" customHeight="1" s="19"/>
-    <row r="90" ht="15.75" customHeight="1" s="19"/>
-    <row r="91" ht="15.75" customHeight="1" s="19"/>
-    <row r="92" ht="15.75" customHeight="1" s="19"/>
-    <row r="93" ht="15.75" customHeight="1" s="19"/>
-    <row r="94" ht="15.75" customHeight="1" s="19"/>
-    <row r="95" ht="15.75" customHeight="1" s="19"/>
-    <row r="96" ht="15.75" customHeight="1" s="19"/>
-    <row r="97" ht="15.75" customHeight="1" s="19"/>
-    <row r="98" ht="15.75" customHeight="1" s="19"/>
-    <row r="99" ht="15.75" customHeight="1" s="19"/>
-    <row r="100" ht="15.75" customHeight="1" s="19"/>
-    <row r="101" ht="15.75" customHeight="1" s="19"/>
-    <row r="102" ht="15.75" customHeight="1" s="19"/>
-    <row r="103" ht="15.75" customHeight="1" s="19"/>
-    <row r="104" ht="15.75" customHeight="1" s="19"/>
-    <row r="105" ht="15.75" customHeight="1" s="19"/>
-    <row r="106" ht="15.75" customHeight="1" s="19"/>
-    <row r="107" ht="15.75" customHeight="1" s="19"/>
-    <row r="108" ht="15.75" customHeight="1" s="19"/>
-    <row r="109" ht="15.75" customHeight="1" s="19"/>
-    <row r="110" ht="15.75" customHeight="1" s="19"/>
-    <row r="111" ht="15.75" customHeight="1" s="19"/>
-    <row r="112" ht="15.75" customHeight="1" s="19"/>
-    <row r="113" ht="15.75" customHeight="1" s="19"/>
-    <row r="114" ht="15.75" customHeight="1" s="19"/>
-    <row r="115" ht="15.75" customHeight="1" s="19"/>
-    <row r="116" ht="15.75" customHeight="1" s="19"/>
-    <row r="117" ht="15.75" customHeight="1" s="19"/>
-    <row r="118" ht="15.75" customHeight="1" s="19"/>
-    <row r="119" ht="15.75" customHeight="1" s="19"/>
-    <row r="120" ht="15.75" customHeight="1" s="19"/>
-    <row r="121" ht="15.75" customHeight="1" s="19"/>
-    <row r="122" ht="15.75" customHeight="1" s="19"/>
-    <row r="123" ht="15.75" customHeight="1" s="19"/>
-    <row r="124" ht="15.75" customHeight="1" s="19"/>
-    <row r="125" ht="15.75" customHeight="1" s="19"/>
-    <row r="126" ht="15.75" customHeight="1" s="19"/>
-    <row r="127" ht="15.75" customHeight="1" s="19"/>
-    <row r="128" ht="15.75" customHeight="1" s="19"/>
-    <row r="129" ht="15.75" customHeight="1" s="19"/>
-    <row r="130" ht="15.75" customHeight="1" s="19"/>
-    <row r="131" ht="15.75" customHeight="1" s="19"/>
-    <row r="132" ht="15.75" customHeight="1" s="19"/>
-    <row r="133" ht="15.75" customHeight="1" s="19"/>
-    <row r="134" ht="15.75" customHeight="1" s="19"/>
-    <row r="135" ht="15.75" customHeight="1" s="19"/>
-    <row r="136" ht="15.75" customHeight="1" s="19"/>
-    <row r="137" ht="15.75" customHeight="1" s="19"/>
-    <row r="138" ht="15.75" customHeight="1" s="19"/>
-    <row r="139" ht="15.75" customHeight="1" s="19"/>
-    <row r="140" ht="15.75" customHeight="1" s="19"/>
-    <row r="141" ht="15.75" customHeight="1" s="19"/>
-    <row r="142" ht="15.75" customHeight="1" s="19"/>
-    <row r="143" ht="15.75" customHeight="1" s="19"/>
-    <row r="144" ht="15.75" customHeight="1" s="19"/>
-    <row r="145" ht="15.75" customHeight="1" s="19"/>
-    <row r="146" ht="15.75" customHeight="1" s="19"/>
-    <row r="147" ht="15.75" customHeight="1" s="19"/>
-    <row r="148" ht="15.75" customHeight="1" s="19"/>
-    <row r="149" ht="15.75" customHeight="1" s="19"/>
-    <row r="150" ht="15.75" customHeight="1" s="19"/>
-    <row r="151" ht="15.75" customHeight="1" s="19"/>
-    <row r="152" ht="15.75" customHeight="1" s="19"/>
-    <row r="153" ht="15.75" customHeight="1" s="19"/>
-    <row r="154" ht="15.75" customHeight="1" s="19"/>
-    <row r="155" ht="15.75" customHeight="1" s="19"/>
-    <row r="156" ht="15.75" customHeight="1" s="19"/>
-    <row r="157" ht="15.75" customHeight="1" s="19"/>
-    <row r="158" ht="15.75" customHeight="1" s="19"/>
-    <row r="159" ht="15.75" customHeight="1" s="19"/>
-    <row r="160" ht="15.75" customHeight="1" s="19"/>
-    <row r="161" ht="15.75" customHeight="1" s="19"/>
-    <row r="162" ht="15.75" customHeight="1" s="19"/>
-    <row r="163" ht="15.75" customHeight="1" s="19"/>
-    <row r="164" ht="15.75" customHeight="1" s="19"/>
-    <row r="165" ht="15.75" customHeight="1" s="19"/>
-    <row r="166" ht="15.75" customHeight="1" s="19"/>
-    <row r="167" ht="15.75" customHeight="1" s="19"/>
-    <row r="168" ht="15.75" customHeight="1" s="19"/>
-    <row r="169" ht="15.75" customHeight="1" s="19"/>
-    <row r="170" ht="15.75" customHeight="1" s="19"/>
-    <row r="171" ht="15.75" customHeight="1" s="19"/>
-    <row r="172" ht="15.75" customHeight="1" s="19"/>
-    <row r="173" ht="15.75" customHeight="1" s="19"/>
-    <row r="174" ht="15.75" customHeight="1" s="19"/>
-    <row r="175" ht="15.75" customHeight="1" s="19"/>
-    <row r="176" ht="15.75" customHeight="1" s="19"/>
-    <row r="177" ht="15.75" customHeight="1" s="19"/>
-    <row r="178" ht="15.75" customHeight="1" s="19"/>
-    <row r="179" ht="15.75" customHeight="1" s="19"/>
-    <row r="180" ht="15.75" customHeight="1" s="19"/>
-    <row r="181" ht="15.75" customHeight="1" s="19"/>
-    <row r="182" ht="15.75" customHeight="1" s="19"/>
-    <row r="183" ht="15.75" customHeight="1" s="19"/>
-    <row r="184" ht="15.75" customHeight="1" s="19"/>
-    <row r="185" ht="15.75" customHeight="1" s="19"/>
-    <row r="186" ht="15.75" customHeight="1" s="19"/>
-    <row r="187" ht="15.75" customHeight="1" s="19"/>
-    <row r="188" ht="15.75" customHeight="1" s="19"/>
-    <row r="189" ht="15.75" customHeight="1" s="19"/>
-    <row r="190" ht="15.75" customHeight="1" s="19"/>
-    <row r="191" ht="15.75" customHeight="1" s="19"/>
-    <row r="192" ht="15.75" customHeight="1" s="19"/>
-    <row r="193" ht="15.75" customHeight="1" s="19"/>
-    <row r="194" ht="15.75" customHeight="1" s="19"/>
-    <row r="195" ht="15.75" customHeight="1" s="19"/>
-    <row r="196" ht="15.75" customHeight="1" s="19"/>
-    <row r="197" ht="15.75" customHeight="1" s="19"/>
-    <row r="198" ht="15.75" customHeight="1" s="19"/>
-    <row r="199" ht="15.75" customHeight="1" s="19"/>
-    <row r="200" ht="15.75" customHeight="1" s="19"/>
-    <row r="201" ht="15.75" customHeight="1" s="19"/>
-    <row r="202" ht="15.75" customHeight="1" s="19"/>
-    <row r="203" ht="15.75" customHeight="1" s="19"/>
-    <row r="204" ht="15.75" customHeight="1" s="19"/>
-    <row r="205" ht="15.75" customHeight="1" s="19"/>
-    <row r="206" ht="15.75" customHeight="1" s="19"/>
-    <row r="207" ht="15.75" customHeight="1" s="19"/>
-    <row r="208" ht="15.75" customHeight="1" s="19"/>
-    <row r="209" ht="15.75" customHeight="1" s="19"/>
-    <row r="210" ht="15.75" customHeight="1" s="19"/>
-    <row r="211" ht="15.75" customHeight="1" s="19"/>
-    <row r="212" ht="15.75" customHeight="1" s="19"/>
-    <row r="213" ht="15.75" customHeight="1" s="19"/>
-    <row r="214" ht="15.75" customHeight="1" s="19"/>
-    <row r="215" ht="15.75" customHeight="1" s="19"/>
-    <row r="216" ht="15.75" customHeight="1" s="19"/>
-    <row r="217" ht="15.75" customHeight="1" s="19"/>
-    <row r="218" ht="15.75" customHeight="1" s="19"/>
-    <row r="219" ht="15.75" customHeight="1" s="19"/>
-    <row r="220" ht="15.75" customHeight="1" s="19"/>
-    <row r="221" ht="15.75" customHeight="1" s="19"/>
-    <row r="222" ht="15.75" customHeight="1" s="19"/>
-    <row r="223" ht="15.75" customHeight="1" s="19"/>
-    <row r="224" ht="15.75" customHeight="1" s="19"/>
-    <row r="225" ht="15.75" customHeight="1" s="19"/>
-    <row r="226" ht="15.75" customHeight="1" s="19"/>
-    <row r="227" ht="15.75" customHeight="1" s="19"/>
-    <row r="228" ht="15.75" customHeight="1" s="19"/>
-    <row r="229" ht="15.75" customHeight="1" s="19"/>
-    <row r="230" ht="15.75" customHeight="1" s="19"/>
-    <row r="231" ht="15.75" customHeight="1" s="19"/>
-    <row r="232" ht="15.75" customHeight="1" s="19"/>
-    <row r="233" ht="15.75" customHeight="1" s="19"/>
-    <row r="234" ht="15.75" customHeight="1" s="19"/>
-    <row r="235" ht="15.75" customHeight="1" s="19"/>
-    <row r="236" ht="15.75" customHeight="1" s="19"/>
-    <row r="237" ht="15.75" customHeight="1" s="19"/>
-    <row r="238" ht="15.75" customHeight="1" s="19"/>
-    <row r="239" ht="15.75" customHeight="1" s="19"/>
-    <row r="240" ht="15.75" customHeight="1" s="19"/>
-    <row r="241" ht="15.75" customHeight="1" s="19"/>
-    <row r="242" ht="15.75" customHeight="1" s="19"/>
-    <row r="243" ht="15.75" customHeight="1" s="19"/>
-    <row r="244" ht="15.75" customHeight="1" s="19"/>
-    <row r="245" ht="15.75" customHeight="1" s="19"/>
-    <row r="246" ht="15.75" customHeight="1" s="19"/>
-    <row r="247" ht="15.75" customHeight="1" s="19"/>
-    <row r="248" ht="15.75" customHeight="1" s="19"/>
-    <row r="249" ht="15.75" customHeight="1" s="19"/>
-    <row r="250" ht="15.75" customHeight="1" s="19"/>
-    <row r="251" ht="15.75" customHeight="1" s="19"/>
-    <row r="252" ht="15.75" customHeight="1" s="19"/>
-    <row r="253" ht="15.75" customHeight="1" s="19"/>
-    <row r="254" ht="15.75" customHeight="1" s="19"/>
-    <row r="255" ht="15.75" customHeight="1" s="19"/>
-    <row r="256" ht="15.75" customHeight="1" s="19"/>
-    <row r="257" ht="15.75" customHeight="1" s="19"/>
-    <row r="258" ht="15.75" customHeight="1" s="19"/>
-    <row r="259" ht="15.75" customHeight="1" s="19"/>
-    <row r="260" ht="15.75" customHeight="1" s="19"/>
-    <row r="261" ht="15.75" customHeight="1" s="19"/>
-    <row r="262" ht="15.75" customHeight="1" s="19"/>
-    <row r="263" ht="15.75" customHeight="1" s="19"/>
-    <row r="264" ht="15.75" customHeight="1" s="19"/>
-    <row r="265" ht="15.75" customHeight="1" s="19"/>
-    <row r="266" ht="15.75" customHeight="1" s="19"/>
-    <row r="267" ht="15.75" customHeight="1" s="19"/>
-    <row r="268" ht="15.75" customHeight="1" s="19"/>
-    <row r="269" ht="15.75" customHeight="1" s="19"/>
-    <row r="270" ht="15.75" customHeight="1" s="19"/>
-    <row r="271" ht="15.75" customHeight="1" s="19"/>
-    <row r="272" ht="15.75" customHeight="1" s="19"/>
-    <row r="273" ht="15.75" customHeight="1" s="19"/>
-    <row r="274" ht="15.75" customHeight="1" s="19"/>
-    <row r="275" ht="15.75" customHeight="1" s="19"/>
-    <row r="276" ht="15.75" customHeight="1" s="19"/>
-    <row r="277" ht="15.75" customHeight="1" s="19"/>
-    <row r="278" ht="15.75" customHeight="1" s="19"/>
-    <row r="279" ht="15.75" customHeight="1" s="19"/>
-    <row r="280" ht="15.75" customHeight="1" s="19"/>
-    <row r="281" ht="15.75" customHeight="1" s="19"/>
-    <row r="282" ht="15.75" customHeight="1" s="19"/>
-    <row r="283" ht="15.75" customHeight="1" s="19"/>
-    <row r="284" ht="15.75" customHeight="1" s="19"/>
-    <row r="285" ht="15.75" customHeight="1" s="19"/>
-    <row r="286" ht="15.75" customHeight="1" s="19"/>
-    <row r="287" ht="15.75" customHeight="1" s="19"/>
-    <row r="288" ht="15.75" customHeight="1" s="19"/>
-    <row r="289" ht="15.75" customHeight="1" s="19"/>
-    <row r="290" ht="15.75" customHeight="1" s="19"/>
-    <row r="291" ht="15.75" customHeight="1" s="19"/>
-    <row r="292" ht="15.75" customHeight="1" s="19"/>
-    <row r="293" ht="15.75" customHeight="1" s="19"/>
-    <row r="294" ht="15.75" customHeight="1" s="19"/>
-    <row r="295" ht="15.75" customHeight="1" s="19"/>
-    <row r="296" ht="15.75" customHeight="1" s="19"/>
-    <row r="297" ht="15.75" customHeight="1" s="19"/>
-    <row r="298" ht="15.75" customHeight="1" s="19"/>
-    <row r="299" ht="15.75" customHeight="1" s="19"/>
-    <row r="300" ht="15.75" customHeight="1" s="19"/>
-    <row r="301" ht="15.75" customHeight="1" s="19"/>
-    <row r="302" ht="15.75" customHeight="1" s="19"/>
-    <row r="303" ht="15.75" customHeight="1" s="19"/>
-    <row r="304" ht="15.75" customHeight="1" s="19"/>
-    <row r="305" ht="15.75" customHeight="1" s="19"/>
-    <row r="306" ht="15.75" customHeight="1" s="19"/>
-    <row r="307" ht="15.75" customHeight="1" s="19"/>
-    <row r="308" ht="15.75" customHeight="1" s="19"/>
-    <row r="309" ht="15.75" customHeight="1" s="19"/>
-    <row r="310" ht="15.75" customHeight="1" s="19"/>
-    <row r="311" ht="15.75" customHeight="1" s="19"/>
-    <row r="312" ht="15.75" customHeight="1" s="19"/>
-    <row r="313" ht="15.75" customHeight="1" s="19"/>
-    <row r="314" ht="15.75" customHeight="1" s="19"/>
-    <row r="315" ht="15.75" customHeight="1" s="19"/>
-    <row r="316" ht="15.75" customHeight="1" s="19"/>
-    <row r="317" ht="15.75" customHeight="1" s="19"/>
-    <row r="318" ht="15.75" customHeight="1" s="19"/>
-    <row r="319" ht="15.75" customHeight="1" s="19"/>
-    <row r="320" ht="15.75" customHeight="1" s="19"/>
-    <row r="321" ht="15.75" customHeight="1" s="19"/>
-    <row r="322" ht="15.75" customHeight="1" s="19"/>
-    <row r="323" ht="15.75" customHeight="1" s="19"/>
-    <row r="324" ht="15.75" customHeight="1" s="19"/>
-    <row r="325" ht="15.75" customHeight="1" s="19"/>
-    <row r="326" ht="15.75" customHeight="1" s="19"/>
-    <row r="327" ht="15.75" customHeight="1" s="19"/>
-    <row r="328" ht="15.75" customHeight="1" s="19"/>
-    <row r="329" ht="15.75" customHeight="1" s="19"/>
-    <row r="330" ht="15.75" customHeight="1" s="19"/>
-    <row r="331" ht="15.75" customHeight="1" s="19"/>
-    <row r="332" ht="15.75" customHeight="1" s="19"/>
-    <row r="333" ht="15.75" customHeight="1" s="19"/>
-    <row r="334" ht="15.75" customHeight="1" s="19"/>
-    <row r="335" ht="15.75" customHeight="1" s="19"/>
-    <row r="336" ht="15.75" customHeight="1" s="19"/>
-    <row r="337" ht="15.75" customHeight="1" s="19"/>
-    <row r="338" ht="15.75" customHeight="1" s="19"/>
-    <row r="339" ht="15.75" customHeight="1" s="19"/>
-    <row r="340" ht="15.75" customHeight="1" s="19"/>
-    <row r="341" ht="15.75" customHeight="1" s="19"/>
-    <row r="342" ht="15.75" customHeight="1" s="19"/>
-    <row r="343" ht="15.75" customHeight="1" s="19"/>
-    <row r="344" ht="15.75" customHeight="1" s="19"/>
-    <row r="345" ht="15.75" customHeight="1" s="19"/>
-    <row r="346" ht="15.75" customHeight="1" s="19"/>
-    <row r="347" ht="15.75" customHeight="1" s="19"/>
-    <row r="348" ht="15.75" customHeight="1" s="19"/>
-    <row r="349" ht="15.75" customHeight="1" s="19"/>
-    <row r="350" ht="15.75" customHeight="1" s="19"/>
-    <row r="351" ht="15.75" customHeight="1" s="19"/>
-    <row r="352" ht="15.75" customHeight="1" s="19"/>
-    <row r="353" ht="15.75" customHeight="1" s="19"/>
-    <row r="354" ht="15.75" customHeight="1" s="19"/>
-    <row r="355" ht="15.75" customHeight="1" s="19"/>
-    <row r="356" ht="15.75" customHeight="1" s="19"/>
-    <row r="357" ht="15.75" customHeight="1" s="19"/>
-    <row r="358" ht="15.75" customHeight="1" s="19"/>
-    <row r="359" ht="15.75" customHeight="1" s="19"/>
-    <row r="360" ht="15.75" customHeight="1" s="19"/>
-    <row r="361" ht="15.75" customHeight="1" s="19"/>
-    <row r="362" ht="15.75" customHeight="1" s="19"/>
-    <row r="363" ht="15.75" customHeight="1" s="19"/>
-    <row r="364" ht="15.75" customHeight="1" s="19"/>
-    <row r="365" ht="15.75" customHeight="1" s="19"/>
-    <row r="366" ht="15.75" customHeight="1" s="19"/>
-    <row r="367" ht="15.75" customHeight="1" s="19"/>
-    <row r="368" ht="15.75" customHeight="1" s="19"/>
-    <row r="369" ht="15.75" customHeight="1" s="19"/>
-    <row r="370" ht="15.75" customHeight="1" s="19"/>
-    <row r="371" ht="15.75" customHeight="1" s="19"/>
-    <row r="372" ht="15.75" customHeight="1" s="19"/>
-    <row r="373" ht="15.75" customHeight="1" s="19"/>
-    <row r="374" ht="15.75" customHeight="1" s="19"/>
-    <row r="375" ht="15.75" customHeight="1" s="19"/>
-    <row r="376" ht="15.75" customHeight="1" s="19"/>
-    <row r="377" ht="15.75" customHeight="1" s="19"/>
-    <row r="378" ht="15.75" customHeight="1" s="19"/>
-    <row r="379" ht="15.75" customHeight="1" s="19"/>
-    <row r="380" ht="15.75" customHeight="1" s="19"/>
-    <row r="381" ht="15.75" customHeight="1" s="19"/>
-    <row r="382" ht="15.75" customHeight="1" s="19"/>
-    <row r="383" ht="15.75" customHeight="1" s="19"/>
-    <row r="384" ht="15.75" customHeight="1" s="19"/>
-    <row r="385" ht="15.75" customHeight="1" s="19"/>
-    <row r="386" ht="15.75" customHeight="1" s="19"/>
-    <row r="387" ht="15.75" customHeight="1" s="19"/>
-    <row r="388" ht="15.75" customHeight="1" s="19"/>
-    <row r="389" ht="15.75" customHeight="1" s="19"/>
-    <row r="390" ht="15.75" customHeight="1" s="19"/>
-    <row r="391" ht="15.75" customHeight="1" s="19"/>
-    <row r="392" ht="15.75" customHeight="1" s="19"/>
-    <row r="393" ht="15.75" customHeight="1" s="19"/>
-    <row r="394" ht="15.75" customHeight="1" s="19"/>
-    <row r="395" ht="15.75" customHeight="1" s="19"/>
-    <row r="396" ht="15.75" customHeight="1" s="19"/>
-    <row r="397" ht="15.75" customHeight="1" s="19"/>
-    <row r="398" ht="15.75" customHeight="1" s="19"/>
-    <row r="399" ht="15.75" customHeight="1" s="19"/>
-    <row r="400" ht="15.75" customHeight="1" s="19"/>
-    <row r="401" ht="15.75" customHeight="1" s="19"/>
-    <row r="402" ht="15.75" customHeight="1" s="19"/>
-    <row r="403" ht="15.75" customHeight="1" s="19"/>
-    <row r="404" ht="15.75" customHeight="1" s="19"/>
-    <row r="405" ht="15.75" customHeight="1" s="19"/>
-    <row r="406" ht="15.75" customHeight="1" s="19"/>
-    <row r="407" ht="15.75" customHeight="1" s="19"/>
-    <row r="408" ht="15.75" customHeight="1" s="19"/>
-    <row r="409" ht="15.75" customHeight="1" s="19"/>
-    <row r="410" ht="15.75" customHeight="1" s="19"/>
-    <row r="411" ht="15.75" customHeight="1" s="19"/>
-    <row r="412" ht="15.75" customHeight="1" s="19"/>
-    <row r="413" ht="15.75" customHeight="1" s="19"/>
-    <row r="414" ht="15.75" customHeight="1" s="19"/>
-    <row r="415" ht="15.75" customHeight="1" s="19"/>
-    <row r="416" ht="15.75" customHeight="1" s="19"/>
-    <row r="417" ht="15.75" customHeight="1" s="19"/>
-    <row r="418" ht="15.75" customHeight="1" s="19"/>
-    <row r="419" ht="15.75" customHeight="1" s="19"/>
-    <row r="420" ht="15.75" customHeight="1" s="19"/>
-    <row r="421" ht="15.75" customHeight="1" s="19"/>
-    <row r="422" ht="15.75" customHeight="1" s="19"/>
-    <row r="423" ht="15.75" customHeight="1" s="19"/>
-    <row r="424" ht="15.75" customHeight="1" s="19"/>
-    <row r="425" ht="15.75" customHeight="1" s="19"/>
-    <row r="426" ht="15.75" customHeight="1" s="19"/>
-    <row r="427" ht="15.75" customHeight="1" s="19"/>
-    <row r="428" ht="15.75" customHeight="1" s="19"/>
-    <row r="429" ht="15.75" customHeight="1" s="19"/>
-    <row r="430" ht="15.75" customHeight="1" s="19"/>
-    <row r="431" ht="15.75" customHeight="1" s="19"/>
-    <row r="432" ht="15.75" customHeight="1" s="19"/>
-    <row r="433" ht="15.75" customHeight="1" s="19"/>
-    <row r="434" ht="15.75" customHeight="1" s="19"/>
-    <row r="435" ht="15.75" customHeight="1" s="19"/>
-    <row r="436" ht="15.75" customHeight="1" s="19"/>
-    <row r="437" ht="15.75" customHeight="1" s="19"/>
-    <row r="438" ht="15.75" customHeight="1" s="19"/>
-    <row r="439" ht="15.75" customHeight="1" s="19"/>
-    <row r="440" ht="15.75" customHeight="1" s="19"/>
-    <row r="441" ht="15.75" customHeight="1" s="19"/>
-    <row r="442" ht="15.75" customHeight="1" s="19"/>
-    <row r="443" ht="15.75" customHeight="1" s="19"/>
-    <row r="444" ht="15.75" customHeight="1" s="19"/>
-    <row r="445" ht="15.75" customHeight="1" s="19"/>
-    <row r="446" ht="15.75" customHeight="1" s="19"/>
-    <row r="447" ht="15.75" customHeight="1" s="19"/>
-    <row r="448" ht="15.75" customHeight="1" s="19"/>
-    <row r="449" ht="15.75" customHeight="1" s="19"/>
-    <row r="450" ht="15.75" customHeight="1" s="19"/>
-    <row r="451" ht="15.75" customHeight="1" s="19"/>
-    <row r="452" ht="15.75" customHeight="1" s="19"/>
-    <row r="453" ht="15.75" customHeight="1" s="19"/>
-    <row r="454" ht="15.75" customHeight="1" s="19"/>
-    <row r="455" ht="15.75" customHeight="1" s="19"/>
-    <row r="456" ht="15.75" customHeight="1" s="19"/>
-    <row r="457" ht="15.75" customHeight="1" s="19"/>
-    <row r="458" ht="15.75" customHeight="1" s="19"/>
-    <row r="459" ht="15.75" customHeight="1" s="19"/>
-    <row r="460" ht="15.75" customHeight="1" s="19"/>
-    <row r="461" ht="15.75" customHeight="1" s="19"/>
-    <row r="462" ht="15.75" customHeight="1" s="19"/>
-    <row r="463" ht="15.75" customHeight="1" s="19"/>
-    <row r="464" ht="15.75" customHeight="1" s="19"/>
-    <row r="465" ht="15.75" customHeight="1" s="19"/>
-    <row r="466" ht="15.75" customHeight="1" s="19"/>
-    <row r="467" ht="15.75" customHeight="1" s="19"/>
-    <row r="468" ht="15.75" customHeight="1" s="19"/>
-    <row r="469" ht="15.75" customHeight="1" s="19"/>
-    <row r="470" ht="15.75" customHeight="1" s="19"/>
-    <row r="471" ht="15.75" customHeight="1" s="19"/>
-    <row r="472" ht="15.75" customHeight="1" s="19"/>
-    <row r="473" ht="15.75" customHeight="1" s="19"/>
-    <row r="474" ht="15.75" customHeight="1" s="19"/>
-    <row r="475" ht="15.75" customHeight="1" s="19"/>
-    <row r="476" ht="15.75" customHeight="1" s="19"/>
-    <row r="477" ht="15.75" customHeight="1" s="19"/>
-    <row r="478" ht="15.75" customHeight="1" s="19"/>
-    <row r="479" ht="15.75" customHeight="1" s="19"/>
-    <row r="480" ht="15.75" customHeight="1" s="19"/>
-    <row r="481" ht="15.75" customHeight="1" s="19"/>
-    <row r="482" ht="15.75" customHeight="1" s="19"/>
-    <row r="483" ht="15.75" customHeight="1" s="19"/>
-    <row r="484" ht="15.75" customHeight="1" s="19"/>
-    <row r="485" ht="15.75" customHeight="1" s="19"/>
-    <row r="486" ht="15.75" customHeight="1" s="19"/>
-    <row r="487" ht="15.75" customHeight="1" s="19"/>
-    <row r="488" ht="15.75" customHeight="1" s="19"/>
-    <row r="489" ht="15.75" customHeight="1" s="19"/>
-    <row r="490" ht="15.75" customHeight="1" s="19"/>
-    <row r="491" ht="15.75" customHeight="1" s="19"/>
-    <row r="492" ht="15.75" customHeight="1" s="19"/>
-    <row r="493" ht="15.75" customHeight="1" s="19"/>
-    <row r="494" ht="15.75" customHeight="1" s="19"/>
-    <row r="495" ht="15.75" customHeight="1" s="19"/>
-    <row r="496" ht="15.75" customHeight="1" s="19"/>
-    <row r="497" ht="15.75" customHeight="1" s="19"/>
-    <row r="498" ht="15.75" customHeight="1" s="19"/>
-    <row r="499" ht="15.75" customHeight="1" s="19"/>
-    <row r="500" ht="15.75" customHeight="1" s="19"/>
-    <row r="501" ht="15.75" customHeight="1" s="19"/>
-    <row r="502" ht="15.75" customHeight="1" s="19"/>
-    <row r="503" ht="15.75" customHeight="1" s="19"/>
-    <row r="504" ht="15.75" customHeight="1" s="19"/>
-    <row r="505" ht="15.75" customHeight="1" s="19"/>
-    <row r="506" ht="15.75" customHeight="1" s="19"/>
-    <row r="507" ht="15.75" customHeight="1" s="19"/>
-    <row r="508" ht="15.75" customHeight="1" s="19"/>
-    <row r="509" ht="15.75" customHeight="1" s="19"/>
-    <row r="510" ht="15.75" customHeight="1" s="19"/>
-    <row r="511" ht="15.75" customHeight="1" s="19"/>
-    <row r="512" ht="15.75" customHeight="1" s="19"/>
-    <row r="513" ht="15.75" customHeight="1" s="19"/>
-    <row r="514" ht="15.75" customHeight="1" s="19"/>
-    <row r="515" ht="15.75" customHeight="1" s="19"/>
-    <row r="516" ht="15.75" customHeight="1" s="19"/>
-    <row r="517" ht="15.75" customHeight="1" s="19"/>
-    <row r="518" ht="15.75" customHeight="1" s="19"/>
-    <row r="519" ht="15.75" customHeight="1" s="19"/>
-    <row r="520" ht="15.75" customHeight="1" s="19"/>
-    <row r="521" ht="15.75" customHeight="1" s="19"/>
-    <row r="522" ht="15.75" customHeight="1" s="19"/>
-    <row r="523" ht="15.75" customHeight="1" s="19"/>
-    <row r="524" ht="15.75" customHeight="1" s="19"/>
-    <row r="525" ht="15.75" customHeight="1" s="19"/>
-    <row r="526" ht="15.75" customHeight="1" s="19"/>
-    <row r="527" ht="15.75" customHeight="1" s="19"/>
-    <row r="528" ht="15.75" customHeight="1" s="19"/>
-    <row r="529" ht="15.75" customHeight="1" s="19"/>
-    <row r="530" ht="15.75" customHeight="1" s="19"/>
-    <row r="531" ht="15.75" customHeight="1" s="19"/>
-    <row r="532" ht="15.75" customHeight="1" s="19"/>
-    <row r="533" ht="15.75" customHeight="1" s="19"/>
-    <row r="534" ht="15.75" customHeight="1" s="19"/>
-    <row r="535" ht="15.75" customHeight="1" s="19"/>
-    <row r="536" ht="15.75" customHeight="1" s="19"/>
-    <row r="537" ht="15.75" customHeight="1" s="19"/>
-    <row r="538" ht="15.75" customHeight="1" s="19"/>
-    <row r="539" ht="15.75" customHeight="1" s="19"/>
-    <row r="540" ht="15.75" customHeight="1" s="19"/>
-    <row r="541" ht="15.75" customHeight="1" s="19"/>
-    <row r="542" ht="15.75" customHeight="1" s="19"/>
-    <row r="543" ht="15.75" customHeight="1" s="19"/>
-    <row r="544" ht="15.75" customHeight="1" s="19"/>
-    <row r="545" ht="15.75" customHeight="1" s="19"/>
-    <row r="546" ht="15.75" customHeight="1" s="19"/>
-    <row r="547" ht="15.75" customHeight="1" s="19"/>
-    <row r="548" ht="15.75" customHeight="1" s="19"/>
-    <row r="549" ht="15.75" customHeight="1" s="19"/>
-    <row r="550" ht="15.75" customHeight="1" s="19"/>
-    <row r="551" ht="15.75" customHeight="1" s="19"/>
-    <row r="552" ht="15.75" customHeight="1" s="19"/>
-    <row r="553" ht="15.75" customHeight="1" s="19"/>
-    <row r="554" ht="15.75" customHeight="1" s="19"/>
-    <row r="555" ht="15.75" customHeight="1" s="19"/>
-    <row r="556" ht="15.75" customHeight="1" s="19"/>
-    <row r="557" ht="15.75" customHeight="1" s="19"/>
-    <row r="558" ht="15.75" customHeight="1" s="19"/>
-    <row r="559" ht="15.75" customHeight="1" s="19"/>
-    <row r="560" ht="15.75" customHeight="1" s="19"/>
-    <row r="561" ht="15.75" customHeight="1" s="19"/>
-    <row r="562" ht="15.75" customHeight="1" s="19"/>
-    <row r="563" ht="15.75" customHeight="1" s="19"/>
-    <row r="564" ht="15.75" customHeight="1" s="19"/>
-    <row r="565" ht="15.75" customHeight="1" s="19"/>
-    <row r="566" ht="15.75" customHeight="1" s="19"/>
-    <row r="567" ht="15.75" customHeight="1" s="19"/>
-    <row r="568" ht="15.75" customHeight="1" s="19"/>
-    <row r="569" ht="15.75" customHeight="1" s="19"/>
-    <row r="570" ht="15.75" customHeight="1" s="19"/>
-    <row r="571" ht="15.75" customHeight="1" s="19"/>
-    <row r="572" ht="15.75" customHeight="1" s="19"/>
-    <row r="573" ht="15.75" customHeight="1" s="19"/>
-    <row r="574" ht="15.75" customHeight="1" s="19"/>
-    <row r="575" ht="15.75" customHeight="1" s="19"/>
-    <row r="576" ht="15.75" customHeight="1" s="19"/>
-    <row r="577" ht="15.75" customHeight="1" s="19"/>
-    <row r="578" ht="15.75" customHeight="1" s="19"/>
-    <row r="579" ht="15.75" customHeight="1" s="19"/>
-    <row r="580" ht="15.75" customHeight="1" s="19"/>
-    <row r="581" ht="15.75" customHeight="1" s="19"/>
-    <row r="582" ht="15.75" customHeight="1" s="19"/>
-    <row r="583" ht="15.75" customHeight="1" s="19"/>
-    <row r="584" ht="15.75" customHeight="1" s="19"/>
-    <row r="585" ht="15.75" customHeight="1" s="19"/>
-    <row r="586" ht="15.75" customHeight="1" s="19"/>
-    <row r="587" ht="15.75" customHeight="1" s="19"/>
-    <row r="588" ht="15.75" customHeight="1" s="19"/>
-    <row r="589" ht="15.75" customHeight="1" s="19"/>
-    <row r="590" ht="15.75" customHeight="1" s="19"/>
-    <row r="591" ht="15.75" customHeight="1" s="19"/>
-    <row r="592" ht="15.75" customHeight="1" s="19"/>
-    <row r="593" ht="15.75" customHeight="1" s="19"/>
-    <row r="594" ht="15.75" customHeight="1" s="19"/>
-    <row r="595" ht="15.75" customHeight="1" s="19"/>
-    <row r="596" ht="15.75" customHeight="1" s="19"/>
-    <row r="597" ht="15.75" customHeight="1" s="19"/>
-    <row r="598" ht="15.75" customHeight="1" s="19"/>
-    <row r="599" ht="15.75" customHeight="1" s="19"/>
-    <row r="600" ht="15.75" customHeight="1" s="19"/>
-    <row r="601" ht="15.75" customHeight="1" s="19"/>
-    <row r="602" ht="15.75" customHeight="1" s="19"/>
-    <row r="603" ht="15.75" customHeight="1" s="19"/>
-    <row r="604" ht="15.75" customHeight="1" s="19"/>
-    <row r="605" ht="15.75" customHeight="1" s="19"/>
-    <row r="606" ht="15.75" customHeight="1" s="19"/>
-    <row r="607" ht="15.75" customHeight="1" s="19"/>
-    <row r="608" ht="15.75" customHeight="1" s="19"/>
-    <row r="609" ht="15.75" customHeight="1" s="19"/>
-    <row r="610" ht="15.75" customHeight="1" s="19"/>
-    <row r="611" ht="15.75" customHeight="1" s="19"/>
-    <row r="612" ht="15.75" customHeight="1" s="19"/>
-    <row r="613" ht="15.75" customHeight="1" s="19"/>
-    <row r="614" ht="15.75" customHeight="1" s="19"/>
-    <row r="615" ht="15.75" customHeight="1" s="19"/>
-    <row r="616" ht="15.75" customHeight="1" s="19"/>
-    <row r="617" ht="15.75" customHeight="1" s="19"/>
-    <row r="618" ht="15.75" customHeight="1" s="19"/>
-    <row r="619" ht="15.75" customHeight="1" s="19"/>
-    <row r="620" ht="15.75" customHeight="1" s="19"/>
-    <row r="621" ht="15.75" customHeight="1" s="19"/>
-    <row r="622" ht="15.75" customHeight="1" s="19"/>
-    <row r="623" ht="15.75" customHeight="1" s="19"/>
-    <row r="624" ht="15.75" customHeight="1" s="19"/>
-    <row r="625" ht="15.75" customHeight="1" s="19"/>
-    <row r="626" ht="15.75" customHeight="1" s="19"/>
-    <row r="627" ht="15.75" customHeight="1" s="19"/>
-    <row r="628" ht="15.75" customHeight="1" s="19"/>
-    <row r="629" ht="15.75" customHeight="1" s="19"/>
-    <row r="630" ht="15.75" customHeight="1" s="19"/>
-    <row r="631" ht="15.75" customHeight="1" s="19"/>
-    <row r="632" ht="15.75" customHeight="1" s="19"/>
-    <row r="633" ht="15.75" customHeight="1" s="19"/>
-    <row r="634" ht="15.75" customHeight="1" s="19"/>
-    <row r="635" ht="15.75" customHeight="1" s="19"/>
-    <row r="636" ht="15.75" customHeight="1" s="19"/>
-    <row r="637" ht="15.75" customHeight="1" s="19"/>
-    <row r="638" ht="15.75" customHeight="1" s="19"/>
-    <row r="639" ht="15.75" customHeight="1" s="19"/>
-    <row r="640" ht="15.75" customHeight="1" s="19"/>
-    <row r="641" ht="15.75" customHeight="1" s="19"/>
-    <row r="642" ht="15.75" customHeight="1" s="19"/>
-    <row r="643" ht="15.75" customHeight="1" s="19"/>
-    <row r="644" ht="15.75" customHeight="1" s="19"/>
-    <row r="645" ht="15.75" customHeight="1" s="19"/>
-    <row r="646" ht="15.75" customHeight="1" s="19"/>
-    <row r="647" ht="15.75" customHeight="1" s="19"/>
-    <row r="648" ht="15.75" customHeight="1" s="19"/>
-    <row r="649" ht="15.75" customHeight="1" s="19"/>
-    <row r="650" ht="15.75" customHeight="1" s="19"/>
-    <row r="651" ht="15.75" customHeight="1" s="19"/>
-    <row r="652" ht="15.75" customHeight="1" s="19"/>
-    <row r="653" ht="15.75" customHeight="1" s="19"/>
-    <row r="654" ht="15.75" customHeight="1" s="19"/>
-    <row r="655" ht="15.75" customHeight="1" s="19"/>
-    <row r="656" ht="15.75" customHeight="1" s="19"/>
-    <row r="657" ht="15.75" customHeight="1" s="19"/>
-    <row r="658" ht="15.75" customHeight="1" s="19"/>
-    <row r="659" ht="15.75" customHeight="1" s="19"/>
-    <row r="660" ht="15.75" customHeight="1" s="19"/>
-    <row r="661" ht="15.75" customHeight="1" s="19"/>
-    <row r="662" ht="15.75" customHeight="1" s="19"/>
-    <row r="663" ht="15.75" customHeight="1" s="19"/>
-    <row r="664" ht="15.75" customHeight="1" s="19"/>
-    <row r="665" ht="15.75" customHeight="1" s="19"/>
-    <row r="666" ht="15.75" customHeight="1" s="19"/>
-    <row r="667" ht="15.75" customHeight="1" s="19"/>
-    <row r="668" ht="15.75" customHeight="1" s="19"/>
-    <row r="669" ht="15.75" customHeight="1" s="19"/>
-    <row r="670" ht="15.75" customHeight="1" s="19"/>
-    <row r="671" ht="15.75" customHeight="1" s="19"/>
-    <row r="672" ht="15.75" customHeight="1" s="19"/>
-    <row r="673" ht="15.75" customHeight="1" s="19"/>
-    <row r="674" ht="15.75" customHeight="1" s="19"/>
-    <row r="675" ht="15.75" customHeight="1" s="19"/>
-    <row r="676" ht="15.75" customHeight="1" s="19"/>
-    <row r="677" ht="15.75" customHeight="1" s="19"/>
-    <row r="678" ht="15.75" customHeight="1" s="19"/>
-    <row r="679" ht="15.75" customHeight="1" s="19"/>
-    <row r="680" ht="15.75" customHeight="1" s="19"/>
-    <row r="681" ht="15.75" customHeight="1" s="19"/>
-    <row r="682" ht="15.75" customHeight="1" s="19"/>
-    <row r="683" ht="15.75" customHeight="1" s="19"/>
-    <row r="684" ht="15.75" customHeight="1" s="19"/>
-    <row r="685" ht="15.75" customHeight="1" s="19"/>
-    <row r="686" ht="15.75" customHeight="1" s="19"/>
-    <row r="687" ht="15.75" customHeight="1" s="19"/>
-    <row r="688" ht="15.75" customHeight="1" s="19"/>
-    <row r="689" ht="15.75" customHeight="1" s="19"/>
-    <row r="690" ht="15.75" customHeight="1" s="19"/>
-    <row r="691" ht="15.75" customHeight="1" s="19"/>
-    <row r="692" ht="15.75" customHeight="1" s="19"/>
-    <row r="693" ht="15.75" customHeight="1" s="19"/>
-    <row r="694" ht="15.75" customHeight="1" s="19"/>
-    <row r="695" ht="15.75" customHeight="1" s="19"/>
-    <row r="696" ht="15.75" customHeight="1" s="19"/>
-    <row r="697" ht="15.75" customHeight="1" s="19"/>
-    <row r="698" ht="15.75" customHeight="1" s="19"/>
-    <row r="699" ht="15.75" customHeight="1" s="19"/>
-    <row r="700" ht="15.75" customHeight="1" s="19"/>
-    <row r="701" ht="15.75" customHeight="1" s="19"/>
-    <row r="702" ht="15.75" customHeight="1" s="19"/>
-    <row r="703" ht="15.75" customHeight="1" s="19"/>
-    <row r="704" ht="15.75" customHeight="1" s="19"/>
-    <row r="705" ht="15.75" customHeight="1" s="19"/>
-    <row r="706" ht="15.75" customHeight="1" s="19"/>
-    <row r="707" ht="15.75" customHeight="1" s="19"/>
-    <row r="708" ht="15.75" customHeight="1" s="19"/>
-    <row r="709" ht="15.75" customHeight="1" s="19"/>
-    <row r="710" ht="15.75" customHeight="1" s="19"/>
-    <row r="711" ht="15.75" customHeight="1" s="19"/>
-    <row r="712" ht="15.75" customHeight="1" s="19"/>
-    <row r="713" ht="15.75" customHeight="1" s="19"/>
-    <row r="714" ht="15.75" customHeight="1" s="19"/>
-    <row r="715" ht="15.75" customHeight="1" s="19"/>
-    <row r="716" ht="15.75" customHeight="1" s="19"/>
-    <row r="717" ht="15.75" customHeight="1" s="19"/>
-    <row r="718" ht="15.75" customHeight="1" s="19"/>
-    <row r="719" ht="15.75" customHeight="1" s="19"/>
-    <row r="720" ht="15.75" customHeight="1" s="19"/>
-    <row r="721" ht="15.75" customHeight="1" s="19"/>
-    <row r="722" ht="15.75" customHeight="1" s="19"/>
-    <row r="723" ht="15.75" customHeight="1" s="19"/>
-    <row r="724" ht="15.75" customHeight="1" s="19"/>
-    <row r="725" ht="15.75" customHeight="1" s="19"/>
-    <row r="726" ht="15.75" customHeight="1" s="19"/>
-    <row r="727" ht="15.75" customHeight="1" s="19"/>
-    <row r="728" ht="15.75" customHeight="1" s="19"/>
-    <row r="729" ht="15.75" customHeight="1" s="19"/>
-    <row r="730" ht="15.75" customHeight="1" s="19"/>
-    <row r="731" ht="15.75" customHeight="1" s="19"/>
-    <row r="732" ht="15.75" customHeight="1" s="19"/>
-    <row r="733" ht="15.75" customHeight="1" s="19"/>
-    <row r="734" ht="15.75" customHeight="1" s="19"/>
-    <row r="735" ht="15.75" customHeight="1" s="19"/>
-    <row r="736" ht="15.75" customHeight="1" s="19"/>
-    <row r="737" ht="15.75" customHeight="1" s="19"/>
-    <row r="738" ht="15.75" customHeight="1" s="19"/>
-    <row r="739" ht="15.75" customHeight="1" s="19"/>
-    <row r="740" ht="15.75" customHeight="1" s="19"/>
-    <row r="741" ht="15.75" customHeight="1" s="19"/>
-    <row r="742" ht="15.75" customHeight="1" s="19"/>
-    <row r="743" ht="15.75" customHeight="1" s="19"/>
-    <row r="744" ht="15.75" customHeight="1" s="19"/>
-    <row r="745" ht="15.75" customHeight="1" s="19"/>
-    <row r="746" ht="15.75" customHeight="1" s="19"/>
-    <row r="747" ht="15.75" customHeight="1" s="19"/>
-    <row r="748" ht="15.75" customHeight="1" s="19"/>
-    <row r="749" ht="15.75" customHeight="1" s="19"/>
-    <row r="750" ht="15.75" customHeight="1" s="19"/>
-    <row r="751" ht="15.75" customHeight="1" s="19"/>
-    <row r="752" ht="15.75" customHeight="1" s="19"/>
-    <row r="753" ht="15.75" customHeight="1" s="19"/>
-    <row r="754" ht="15.75" customHeight="1" s="19"/>
-    <row r="755" ht="15.75" customHeight="1" s="19"/>
-    <row r="756" ht="15.75" customHeight="1" s="19"/>
-    <row r="757" ht="15.75" customHeight="1" s="19"/>
-    <row r="758" ht="15.75" customHeight="1" s="19"/>
-    <row r="759" ht="15.75" customHeight="1" s="19"/>
-    <row r="760" ht="15.75" customHeight="1" s="19"/>
-    <row r="761" ht="15.75" customHeight="1" s="19"/>
-    <row r="762" ht="15.75" customHeight="1" s="19"/>
-    <row r="763" ht="15.75" customHeight="1" s="19"/>
-    <row r="764" ht="15.75" customHeight="1" s="19"/>
-    <row r="765" ht="15.75" customHeight="1" s="19"/>
-    <row r="766" ht="15.75" customHeight="1" s="19"/>
-    <row r="767" ht="15.75" customHeight="1" s="19"/>
-    <row r="768" ht="15.75" customHeight="1" s="19"/>
-    <row r="769" ht="15.75" customHeight="1" s="19"/>
-    <row r="770" ht="15.75" customHeight="1" s="19"/>
-    <row r="771" ht="15.75" customHeight="1" s="19"/>
-    <row r="772" ht="15.75" customHeight="1" s="19"/>
-    <row r="773" ht="15.75" customHeight="1" s="19"/>
-    <row r="774" ht="15.75" customHeight="1" s="19"/>
-    <row r="775" ht="15.75" customHeight="1" s="19"/>
-    <row r="776" ht="15.75" customHeight="1" s="19"/>
-    <row r="777" ht="15.75" customHeight="1" s="19"/>
-    <row r="778" ht="15.75" customHeight="1" s="19"/>
-    <row r="779" ht="15.75" customHeight="1" s="19"/>
-    <row r="780" ht="15.75" customHeight="1" s="19"/>
-    <row r="781" ht="15.75" customHeight="1" s="19"/>
-    <row r="782" ht="15.75" customHeight="1" s="19"/>
-    <row r="783" ht="15.75" customHeight="1" s="19"/>
-    <row r="784" ht="15.75" customHeight="1" s="19"/>
-    <row r="785" ht="15.75" customHeight="1" s="19"/>
-    <row r="786" ht="15.75" customHeight="1" s="19"/>
-    <row r="787" ht="15.75" customHeight="1" s="19"/>
-    <row r="788" ht="15.75" customHeight="1" s="19"/>
-    <row r="789" ht="15.75" customHeight="1" s="19"/>
-    <row r="790" ht="15.75" customHeight="1" s="19"/>
-    <row r="791" ht="15.75" customHeight="1" s="19"/>
-    <row r="792" ht="15.75" customHeight="1" s="19"/>
-    <row r="793" ht="15.75" customHeight="1" s="19"/>
-    <row r="794" ht="15.75" customHeight="1" s="19"/>
-    <row r="795" ht="15.75" customHeight="1" s="19"/>
-    <row r="796" ht="15.75" customHeight="1" s="19"/>
-    <row r="797" ht="15.75" customHeight="1" s="19"/>
-    <row r="798" ht="15.75" customHeight="1" s="19"/>
-    <row r="799" ht="15.75" customHeight="1" s="19"/>
-    <row r="800" ht="15.75" customHeight="1" s="19"/>
-    <row r="801" ht="15.75" customHeight="1" s="19"/>
-    <row r="802" ht="15.75" customHeight="1" s="19"/>
-    <row r="803" ht="15.75" customHeight="1" s="19"/>
-    <row r="804" ht="15.75" customHeight="1" s="19"/>
-    <row r="805" ht="15.75" customHeight="1" s="19"/>
-    <row r="806" ht="15.75" customHeight="1" s="19"/>
-    <row r="807" ht="15.75" customHeight="1" s="19"/>
-    <row r="808" ht="15.75" customHeight="1" s="19"/>
-    <row r="809" ht="15.75" customHeight="1" s="19"/>
-    <row r="810" ht="15.75" customHeight="1" s="19"/>
-    <row r="811" ht="15.75" customHeight="1" s="19"/>
-    <row r="812" ht="15.75" customHeight="1" s="19"/>
-    <row r="813" ht="15.75" customHeight="1" s="19"/>
-    <row r="814" ht="15.75" customHeight="1" s="19"/>
-    <row r="815" ht="15.75" customHeight="1" s="19"/>
-    <row r="816" ht="15.75" customHeight="1" s="19"/>
-    <row r="817" ht="15.75" customHeight="1" s="19"/>
-    <row r="818" ht="15.75" customHeight="1" s="19"/>
-    <row r="819" ht="15.75" customHeight="1" s="19"/>
-    <row r="820" ht="15.75" customHeight="1" s="19"/>
-    <row r="821" ht="15.75" customHeight="1" s="19"/>
-    <row r="822" ht="15.75" customHeight="1" s="19"/>
-    <row r="823" ht="15.75" customHeight="1" s="19"/>
-    <row r="824" ht="15.75" customHeight="1" s="19"/>
-    <row r="825" ht="15.75" customHeight="1" s="19"/>
-    <row r="826" ht="15.75" customHeight="1" s="19"/>
-    <row r="827" ht="15.75" customHeight="1" s="19"/>
-    <row r="828" ht="15.75" customHeight="1" s="19"/>
-    <row r="829" ht="15.75" customHeight="1" s="19"/>
-    <row r="830" ht="15.75" customHeight="1" s="19"/>
-    <row r="831" ht="15.75" customHeight="1" s="19"/>
-    <row r="832" ht="15.75" customHeight="1" s="19"/>
-    <row r="833" ht="15.75" customHeight="1" s="19"/>
-    <row r="834" ht="15.75" customHeight="1" s="19"/>
-    <row r="835" ht="15.75" customHeight="1" s="19"/>
-    <row r="836" ht="15.75" customHeight="1" s="19"/>
-    <row r="837" ht="15.75" customHeight="1" s="19"/>
-    <row r="838" ht="15.75" customHeight="1" s="19"/>
-    <row r="839" ht="15.75" customHeight="1" s="19"/>
-    <row r="840" ht="15.75" customHeight="1" s="19"/>
-    <row r="841" ht="15.75" customHeight="1" s="19"/>
-    <row r="842" ht="15.75" customHeight="1" s="19"/>
-    <row r="843" ht="15.75" customHeight="1" s="19"/>
-    <row r="844" ht="15.75" customHeight="1" s="19"/>
-    <row r="845" ht="15.75" customHeight="1" s="19"/>
-    <row r="846" ht="15.75" customHeight="1" s="19"/>
-    <row r="847" ht="15.75" customHeight="1" s="19"/>
-    <row r="848" ht="15.75" customHeight="1" s="19"/>
-    <row r="849" ht="15.75" customHeight="1" s="19"/>
-    <row r="850" ht="15.75" customHeight="1" s="19"/>
-    <row r="851" ht="15.75" customHeight="1" s="19"/>
-    <row r="852" ht="15.75" customHeight="1" s="19"/>
-    <row r="853" ht="15.75" customHeight="1" s="19"/>
-    <row r="854" ht="15.75" customHeight="1" s="19"/>
-    <row r="855" ht="15.75" customHeight="1" s="19"/>
-    <row r="856" ht="15.75" customHeight="1" s="19"/>
-    <row r="857" ht="15.75" customHeight="1" s="19"/>
-    <row r="858" ht="15.75" customHeight="1" s="19"/>
-    <row r="859" ht="15.75" customHeight="1" s="19"/>
-    <row r="860" ht="15.75" customHeight="1" s="19"/>
-    <row r="861" ht="15.75" customHeight="1" s="19"/>
-    <row r="862" ht="15.75" customHeight="1" s="19"/>
-    <row r="863" ht="15.75" customHeight="1" s="19"/>
-    <row r="864" ht="15.75" customHeight="1" s="19"/>
-    <row r="865" ht="15.75" customHeight="1" s="19"/>
-    <row r="866" ht="15.75" customHeight="1" s="19"/>
-    <row r="867" ht="15.75" customHeight="1" s="19"/>
-    <row r="868" ht="15.75" customHeight="1" s="19"/>
-    <row r="869" ht="15.75" customHeight="1" s="19"/>
-    <row r="870" ht="15.75" customHeight="1" s="19"/>
-    <row r="871" ht="15.75" customHeight="1" s="19"/>
-    <row r="872" ht="15.75" customHeight="1" s="19"/>
-    <row r="873" ht="15.75" customHeight="1" s="19"/>
-    <row r="874" ht="15.75" customHeight="1" s="19"/>
-    <row r="875" ht="15.75" customHeight="1" s="19"/>
-    <row r="876" ht="15.75" customHeight="1" s="19"/>
-    <row r="877" ht="15.75" customHeight="1" s="19"/>
-    <row r="878" ht="15.75" customHeight="1" s="19"/>
-    <row r="879" ht="15.75" customHeight="1" s="19"/>
-    <row r="880" ht="15.75" customHeight="1" s="19"/>
-    <row r="881" ht="15.75" customHeight="1" s="19"/>
-    <row r="882" ht="15.75" customHeight="1" s="19"/>
-    <row r="883" ht="15.75" customHeight="1" s="19"/>
-    <row r="884" ht="15.75" customHeight="1" s="19"/>
-    <row r="885" ht="15.75" customHeight="1" s="19"/>
-    <row r="886" ht="15.75" customHeight="1" s="19"/>
-    <row r="887" ht="15.75" customHeight="1" s="19"/>
-    <row r="888" ht="15.75" customHeight="1" s="19"/>
-    <row r="889" ht="15.75" customHeight="1" s="19"/>
-    <row r="890" ht="15.75" customHeight="1" s="19"/>
-    <row r="891" ht="15.75" customHeight="1" s="19"/>
-    <row r="892" ht="15.75" customHeight="1" s="19"/>
-    <row r="893" ht="15.75" customHeight="1" s="19"/>
-    <row r="894" ht="15.75" customHeight="1" s="19"/>
-    <row r="895" ht="15.75" customHeight="1" s="19"/>
-    <row r="896" ht="15.75" customHeight="1" s="19"/>
-    <row r="897" ht="15.75" customHeight="1" s="19"/>
-    <row r="898" ht="15.75" customHeight="1" s="19"/>
-    <row r="899" ht="15.75" customHeight="1" s="19"/>
-    <row r="900" ht="15.75" customHeight="1" s="19"/>
-    <row r="901" ht="15.75" customHeight="1" s="19"/>
-    <row r="902" ht="15.75" customHeight="1" s="19"/>
-    <row r="903" ht="15.75" customHeight="1" s="19"/>
-    <row r="904" ht="15.75" customHeight="1" s="19"/>
-    <row r="905" ht="15.75" customHeight="1" s="19"/>
-    <row r="906" ht="15.75" customHeight="1" s="19"/>
-    <row r="907" ht="15.75" customHeight="1" s="19"/>
-    <row r="908" ht="15.75" customHeight="1" s="19"/>
-    <row r="909" ht="15.75" customHeight="1" s="19"/>
-    <row r="910" ht="15.75" customHeight="1" s="19"/>
-    <row r="911" ht="15.75" customHeight="1" s="19"/>
-    <row r="912" ht="15.75" customHeight="1" s="19"/>
-    <row r="913" ht="15.75" customHeight="1" s="19"/>
-    <row r="914" ht="15.75" customHeight="1" s="19"/>
-    <row r="915" ht="15.75" customHeight="1" s="19"/>
-    <row r="916" ht="15.75" customHeight="1" s="19"/>
-    <row r="917" ht="15.75" customHeight="1" s="19"/>
-    <row r="918" ht="15.75" customHeight="1" s="19"/>
-    <row r="919" ht="15.75" customHeight="1" s="19"/>
-    <row r="920" ht="15.75" customHeight="1" s="19"/>
-    <row r="921" ht="15.75" customHeight="1" s="19"/>
-    <row r="922" ht="15.75" customHeight="1" s="19"/>
-    <row r="923" ht="15.75" customHeight="1" s="19"/>
-    <row r="924" ht="15.75" customHeight="1" s="19"/>
-    <row r="925" ht="15.75" customHeight="1" s="19"/>
-    <row r="926" ht="15.75" customHeight="1" s="19"/>
-    <row r="927" ht="15.75" customHeight="1" s="19"/>
-    <row r="928" ht="15.75" customHeight="1" s="19"/>
-    <row r="929" ht="15.75" customHeight="1" s="19"/>
-    <row r="930" ht="15.75" customHeight="1" s="19"/>
-    <row r="931" ht="15.75" customHeight="1" s="19"/>
-    <row r="932" ht="15.75" customHeight="1" s="19"/>
-    <row r="933" ht="15.75" customHeight="1" s="19"/>
-    <row r="934" ht="15.75" customHeight="1" s="19"/>
-    <row r="935" ht="15.75" customHeight="1" s="19"/>
-    <row r="936" ht="15.75" customHeight="1" s="19"/>
-    <row r="937" ht="15.75" customHeight="1" s="19"/>
-    <row r="938" ht="15.75" customHeight="1" s="19"/>
-    <row r="939" ht="15.75" customHeight="1" s="19"/>
-    <row r="940" ht="15.75" customHeight="1" s="19"/>
-    <row r="941" ht="15.75" customHeight="1" s="19"/>
-    <row r="942" ht="15.75" customHeight="1" s="19"/>
-    <row r="943" ht="15.75" customHeight="1" s="19"/>
-    <row r="944" ht="15.75" customHeight="1" s="19"/>
-    <row r="945" ht="15.75" customHeight="1" s="19"/>
-    <row r="946" ht="15.75" customHeight="1" s="19"/>
-    <row r="947" ht="15.75" customHeight="1" s="19"/>
-    <row r="948" ht="15.75" customHeight="1" s="19"/>
-    <row r="949" ht="15.75" customHeight="1" s="19"/>
-    <row r="950" ht="15.75" customHeight="1" s="19"/>
-    <row r="951" ht="15.75" customHeight="1" s="19"/>
-    <row r="952" ht="15.75" customHeight="1" s="19"/>
-    <row r="953" ht="15.75" customHeight="1" s="19"/>
-    <row r="954" ht="15.75" customHeight="1" s="19"/>
-    <row r="955" ht="15.75" customHeight="1" s="19"/>
-    <row r="956" ht="15.75" customHeight="1" s="19"/>
-    <row r="957" ht="15.75" customHeight="1" s="19"/>
-    <row r="958" ht="15.75" customHeight="1" s="19"/>
-    <row r="959" ht="15.75" customHeight="1" s="19"/>
-    <row r="960" ht="15.75" customHeight="1" s="19"/>
-    <row r="961" ht="15.75" customHeight="1" s="19"/>
-    <row r="962" ht="15.75" customHeight="1" s="19"/>
-    <row r="963" ht="15.75" customHeight="1" s="19"/>
-    <row r="964" ht="15.75" customHeight="1" s="19"/>
-    <row r="965" ht="15.75" customHeight="1" s="19"/>
-    <row r="966" ht="15.75" customHeight="1" s="19"/>
-    <row r="967" ht="15.75" customHeight="1" s="19"/>
-    <row r="968" ht="15.75" customHeight="1" s="19"/>
-    <row r="969" ht="15.75" customHeight="1" s="19"/>
-    <row r="970" ht="15.75" customHeight="1" s="19"/>
-    <row r="971" ht="15.75" customHeight="1" s="19"/>
-    <row r="972" ht="15.75" customHeight="1" s="19"/>
-    <row r="973" ht="15.75" customHeight="1" s="19"/>
-    <row r="974" ht="15.75" customHeight="1" s="19"/>
-    <row r="975" ht="15.75" customHeight="1" s="19"/>
-    <row r="976" ht="15.75" customHeight="1" s="19"/>
-    <row r="977" ht="15.75" customHeight="1" s="19"/>
-    <row r="978" ht="15.75" customHeight="1" s="19"/>
-    <row r="979" ht="15.75" customHeight="1" s="19"/>
-    <row r="980" ht="15.75" customHeight="1" s="19"/>
-    <row r="981" ht="15.75" customHeight="1" s="19"/>
-    <row r="982" ht="15.75" customHeight="1" s="19"/>
-    <row r="983" ht="15.75" customHeight="1" s="19"/>
-    <row r="984" ht="15.75" customHeight="1" s="19"/>
-    <row r="985" ht="15.75" customHeight="1" s="19"/>
-    <row r="986" ht="15.75" customHeight="1" s="19"/>
-    <row r="987" ht="15.75" customHeight="1" s="19"/>
-    <row r="988" ht="15.75" customHeight="1" s="19"/>
-    <row r="989" ht="15.75" customHeight="1" s="19"/>
-    <row r="990" ht="15.75" customHeight="1" s="19"/>
-    <row r="991" ht="15.75" customHeight="1" s="19"/>
-    <row r="992" ht="15.75" customHeight="1" s="19"/>
-    <row r="993" ht="15.75" customHeight="1" s="19"/>
-    <row r="994" ht="15.75" customHeight="1" s="19"/>
-    <row r="995" ht="15.75" customHeight="1" s="19"/>
-    <row r="996" ht="15.75" customHeight="1" s="19"/>
-    <row r="997" ht="15.75" customHeight="1" s="19"/>
-    <row r="998" ht="15.75" customHeight="1" s="19"/>
-    <row r="999" ht="15.75" customHeight="1" s="19"/>
-    <row r="1000" ht="15.75" customHeight="1" s="19"/>
+    <row r="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="24" t="inlineStr">
+        <is>
+          <t>Question / ambiguity for the PO or developer</t>
+        </is>
+      </c>
+      <c r="C1" s="24" t="inlineStr">
+        <is>
+          <t>Answer</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="206.5" customHeight="1" s="19">
+      <c r="A2" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="25" t="inlineStr">
+        <is>
+          <t>DECIDED 2026-10-13: Wording - button 'Record safety decision'; dialog 'Record safety decision' with the choices 'Approve', 'Request changes', 'Reject'; box 'Changes required' or 'Reason for rejecting' (none for Approve); button 'Record decision' / 'Cancel'. Messages: 'Safety check approved. The coordinator has been notified.'; 'Changes requested. The event is back in Planning and the coordinator has been notified.'; 'Safety arrangement rejected. The event is back in Planning and the coordinator has been notified.'; 'Give a reason for rejecting.'; 'Describe the changes required.'; 'This safety check has already been decided.'. Safety check row: '&lt;Approved | Changes requested | Rejected&gt; · decided by &lt;name&gt;, &lt;date and time&gt;', followed by '. Changes required: …' or '. Reason: …'. Notification titles: 'Safety check: approved' / 'Safety check: changes requested' / 'Safety check: rejected'. Venue bookings card: opening hours '08:00–22:00' and 'Unavailable &lt;date&gt;, &lt;from&gt;–&lt;to&gt; (&lt;reason&gt;)'.</t>
+        </is>
+      </c>
+      <c r="C2" s="25" t="n"/>
+    </row>
+    <row r="3" ht="71.5" customHeight="1" s="19">
+      <c r="A3" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="25" t="inlineStr">
+        <is>
+          <t>DECIDED 2026-10-13: 'Safety approved' badge (status safety_cleared) is added wherever Safety review was: a 'Safety approved' list on the organiser's and coordinator's Dashboard after 'Safety review', Venue Staff and Technical Support 'Upcoming events', the status filter, Technical Support's equipment view, and reassigning the coordinator.</t>
+        </is>
+      </c>
+      <c r="C3" s="25" t="n"/>
+    </row>
+    <row r="4" ht="166" customHeight="1" s="19">
+      <c r="A4" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>DECIDED 2026-10-13: Fixtures (scripts/seed-spm87.ts, npm run fixtures:spm87) - a dedicated venue 'SPM87 Hillside Studio' (SPM87-STU, Theatre seats 60, open 08:00-22:00, maintenance 8 Oct 2027 07:00-09:00) so no other venue gains an unavailable period; events in Safety review, each with a pending SafetyCheck submitted by Daniel Tan in reverse date order, an approved booking and a reserved Handheld Wireless Mic: 'SPM87 Hillside Workshop' (8 Oct 2027 10:00-13:00, 50 people, at SPM87 Hillside Studio, accessibility notes), 'SPM87 Lakeside Conference' (12 Oct), 'SPM87 Waterfront Gala' (18 Oct), 'SPM87 Rooftop Launch Party' (20 Oct, 300 people), 'SPM87 Twin Tab Briefing' (22 Oct); and 'SPM87 Unsubmitted Planning Day' in Planning. Organiser Rachel Ng, coordinator Daniel Tan.</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="n"/>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -8549,21 +8640,21 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
-        <is>
-          <t>SPM-87-TC02</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="44.25" customHeight="1" s="19">
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>SPM-87-TC01</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30.75" customHeight="1" s="19">
       <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Summary</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
-        <is>
-          <t>The review shows attendance, each venue with its capacity, layout, opening hours and unavailable periods, accessibility needs and equipment</t>
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>The Safety Checks list shows events awaiting a check, earliest event date first</t>
         </is>
       </c>
     </row>
@@ -8573,50 +8664,47 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
-        <is>
-          <t>npm run fixtures:spm87 has been run. 'SPM87 Hillside Workshop' (8 Oct 2027, 10:00-13:00, 50 attendees, accessibility: 'Two attendees use wheelchairs; step-free route needed') is in Safety review with an approved booking at SPM87 Hillside Studio (Theatre, seats 60, open 08:00-22:00), which is unavailable for maintenance on 8 Oct 2027 from 07:00 to 09:00, and a Reserved Handheld Wireless Mic. Logged in as Hana Yusof (hana.yusof@connectsphere.com / password123).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="44.25" customHeight="1" s="19">
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>npm run fixtures:spm87 has been run. Five SPM87 events are in Safety review: 'SPM87 Hillside Workshop' (8 Oct 2027), 'SPM87 Lakeside Conference' (12 Oct 2027), 'SPM87 Waterfront Gala' (18 Oct 2027), 'SPM87 Rooftop Launch Party' (20 Oct 2027) and 'SPM87 Twin Tab Briefing' (22 Oct 2027). They were submitted in the reverse order, newest event first. 'SPM87 Unsubmitted Planning Day' is in Planning. Other stories' events may also be listed; only the SPM87 ones are checked here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30.75" customHeight="1" s="19">
       <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t>1. Click 'Safety Checks' in the sidebar
-2. Click 'SPM87 Hillside Workshop' in the list
-3. Click the 'Equipment' tab</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="57.75" customHeight="1" s="19">
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>1. Log in as hana.yusof@connectsphere.com with password123
+2. Click 'Safety Checks' in the sidebar</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44.25" customHeight="1" s="19">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>Event: SPM87 Hillside Workshop (Safety review)
-Venue: SPM87 Hillside Studio, Theatre, seats 60, open 08:00-22:00, maintenance 8 Oct 2027 07:00-09:00
-Equipment: Handheld Wireless Mic, Reserved</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="111.75" customHeight="1" s="19">
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Safety Officer: hana.yusof@connectsphere.com (Hana Yusof)
+SPM87 events in Safety review dated 8, 12, 18, 20 and 22 Oct 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="84.75" customHeight="1" s="19">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>Step 2: The event opens with the status 'Safety review'. Expected attendance reads 50, the accessibility notes read 'Two attendees use wheelchairs; step-free route needed', and the 'Venue bookings' card shows 'SPM87 Hillside Studio (SPM87-STU) · Theatre · seats 60', its opening hours '08:00–22:00', and 'Unavailable 8 Oct 2027, 07:00–09:00 (Maintenance)'.
-Step 3: The Equipment tab lists Handheld Wireless Mic with its quantity and the status 'Reserved'.</t>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>Step 2: The Safety Checks page lists the five SPM87 events in Safety review in this order: SPM87 Hillside Workshop, SPM87 Lakeside Conference, SPM87 Waterfront Gala, SPM87 Rooftop Launch Party, SPM87 Twin Tab Briefing - by event date, not by when they were submitted. 'SPM87 Unsubmitted Planning Day' is not listed.</t>
         </is>
       </c>
     </row>
@@ -8626,7 +8714,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -8658,10 +8746,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>Step 2: The event opens with the status 'Safety review'. Expected attendance reads 50, the accessibility notes read 'Two attendees use wheelchairs; step-free route needed', and the 'Venue bookings' card shows 'SPM87 Hillside Studio (SPM87-STU) · Theatre · seats 60', its opening hours '08:00–22:00', and 'Unavailable 8 Oct 2027, 07:00–09:00 (Maintenance)'.
-Step 3: The Equipment tab lists Handheld Wireless Mic with its quantity and the status 'Reserved'.</t>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>Step 2: The Safety Checks page lists the five SPM87 events in Safety review in this order: SPM87 Hillside Workshop, SPM87 Lakeside Conference, SPM87 Waterfront Gala, SPM87 Rooftop Launch Party, SPM87 Twin Tab Briefing - by event date, not by when they were submitted. 'SPM87 Unsubmitted Planning Day' is not listed.</t>
         </is>
       </c>
     </row>
@@ -8695,7 +8782,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -8725,10 +8812,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>Step 2: The event opens with the status 'Safety review'. Expected attendance reads 50, the accessibility notes read 'Two attendees use wheelchairs; step-free route needed', and the 'Venue bookings' card shows 'SPM87 Hillside Studio (SPM87-STU) · Theatre · seats 60', its opening hours '08:00–22:00', and 'Unavailable 8 Oct 2027, 07:00–09:00 (Maintenance)'.
-Step 3: The Equipment tab lists Handheld Wireless Mic with its quantity and the status 'Reserved'.</t>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>Step 2: The Safety Checks page lists the five SPM87 events in Safety review in this order: SPM87 Hillside Workshop, SPM87 Lakeside Conference, SPM87 Waterfront Gala, SPM87 Rooftop Launch Party, SPM87 Twin Tab Briefing - by event date, not by when they were submitted. 'SPM87 Unsubmitted Planning Day' is not listed.</t>
         </is>
       </c>
     </row>
@@ -8762,7 +8848,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>Kayalvizhi</t>
         </is>
@@ -9790,62 +9876,61 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
-        <is>
-          <t>SPM-87-TC03</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30.75" customHeight="1" s="19">
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>SPM-87-TC02</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="44.25" customHeight="1" s="19">
       <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Summary</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
-        <is>
-          <t>The Safety Officer approves an event, which becomes Safety approved with the decision recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="84.75" customHeight="1" s="19">
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>The review shows attendance, each venue with its capacity, layout, opening hours and unavailable periods, accessibility needs and equipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="111.75" customHeight="1" s="19">
       <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
-        <is>
-          <t>npm run fixtures:spm87 has been run. 'SPM87 Waterfront Gala' is in Safety review, submitted by Daniel Tan. Logged in as Hana Yusof (hana.yusof@connectsphere.com / password123). Note the date and time of step 5. This case changes the event - SPM-87-TC04 and TC05 read the result, so go straight to those and run npm run fixtures:spm87 after TC05.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="71.25" customHeight="1" s="19">
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>npm run fixtures:spm87 has been run. 'SPM87 Hillside Workshop' (8 Oct 2027, 10:00-13:00, 50 attendees, accessibility: 'Two attendees use wheelchairs; step-free route needed') is in Safety review with an approved booking at SPM87 Hillside Studio (Theatre, seats 60, open 08:00-22:00), which is unavailable for maintenance on 8 Oct 2027 from 07:00 to 09:00, and a Reserved Handheld Wireless Mic. Logged in as Hana Yusof (hana.yusof@connectsphere.com / password123).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44.25" customHeight="1" s="19">
       <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>1. Click 'Safety Checks' in the sidebar
-2. Click 'SPM87 Waterfront Gala' in the list
-3. Click 'Record safety decision'
-4. Choose 'Approve'
-5. Click 'Record decision'</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30.75" customHeight="1" s="19">
+2. Click 'SPM87 Hillside Workshop' in the list
+3. Click the 'Equipment' tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="57.75" customHeight="1" s="19">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>Event: SPM87 Waterfront Gala (Safety review)
-Decision: Approve (no reason needed)</t>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Event: SPM87 Hillside Workshop (Safety review)
+Venue: SPM87 Hillside Studio, Theatre, seats 60, open 08:00-22:00, maintenance 8 Oct 2027 07:00-09:00
+Equipment: Handheld Wireless Mic, Reserved</t>
         </is>
       </c>
     </row>
@@ -9855,11 +9940,10 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>Step 3: A dialog headed 'Record safety decision' opens with the choices 'Approve', 'Request changes' and 'Reject'.
-Step 4: No reason box is shown for Approve.
-Step 5: The message 'Safety check approved. The coordinator has been notified.' is shown. The status badge changes to 'Safety approved', the 'Safety check' row reads 'Approved · decided by Hana Yusof, &lt;date and time of step 5&gt;', and the 'Record safety decision' button is gone.</t>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>Step 2: The event opens with the status 'Safety review'. Expected attendance reads 50, the accessibility notes read 'Two attendees use wheelchairs; step-free route needed', and the 'Venue bookings' card shows 'SPM87 Hillside Studio (SPM87-STU) · Theatre · seats 60', its opening hours '08:00–22:00', and 'Unavailable 8 Oct 2027, 07:00–09:00 (Maintenance)'.
+Step 3: The Equipment tab lists Handheld Wireless Mic with its quantity and the status 'Reserved'.</t>
         </is>
       </c>
     </row>
@@ -9869,7 +9953,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -9901,11 +9985,10 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>Step 3: A dialog headed 'Record safety decision' opens with the choices 'Approve', 'Request changes' and 'Reject'.
-Step 4: No reason box is shown for Approve.
-Step 5: The message 'Safety check approved. The coordinator has been notified.' is shown. The status badge changes to 'Safety approved', the 'Safety check' row reads 'Approved · decided by Hana Yusof, &lt;date and time of step 5&gt;', and the 'Record safety decision' button is gone.</t>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>Step 2: The event opens with the status 'Safety review'. Expected attendance reads 50, the accessibility notes read 'Two attendees use wheelchairs; step-free route needed', and the 'Venue bookings' card shows 'SPM87 Hillside Studio (SPM87-STU) · Theatre · seats 60', its opening hours '08:00–22:00', and 'Unavailable 8 Oct 2027, 07:00–09:00 (Maintenance)'.
+Step 3: The Equipment tab lists Handheld Wireless Mic with its quantity and the status 'Reserved'.</t>
         </is>
       </c>
     </row>
@@ -9939,7 +10022,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -9969,11 +10052,10 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>Step 3: A dialog headed 'Record safety decision' opens with the choices 'Approve', 'Request changes' and 'Reject'.
-Step 4: No reason box is shown for Approve.
-Step 5: The message 'Safety check approved. The coordinator has been notified.' is shown. The status badge changes to 'Safety approved', the 'Safety check' row reads 'Approved · decided by Hana Yusof, &lt;date and time of step 5&gt;', and the 'Record safety decision' button is gone.</t>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>Step 2: The event opens with the status 'Safety review'. Expected attendance reads 50, the accessibility notes read 'Two attendees use wheelchairs; step-free route needed', and the 'Venue bookings' card shows 'SPM87 Hillside Studio (SPM87-STU) · Theatre · seats 60', its opening hours '08:00–22:00', and 'Unavailable 8 Oct 2027, 07:00–09:00 (Maintenance)'.
+Step 3: The Equipment tab lists Handheld Wireless Mic with its quantity and the status 'Reserved'.</t>
         </is>
       </c>
     </row>
@@ -10007,7 +10089,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>Kayalvizhi</t>
         </is>
@@ -11035,9 +11117,9 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
-        <is>
-          <t>SPM-87-TC04</t>
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>SPM-87-TC03</t>
         </is>
       </c>
     </row>
@@ -11047,36 +11129,37 @@
           <t>Summary</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
-        <is>
-          <t>After approval the assigned Coordinator sees the decision and can go on to confirm the event</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="44.25" customHeight="1" s="19">
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>The Safety Officer approves an event, which becomes Safety approved with the decision recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="84.75" customHeight="1" s="19">
       <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
-        <is>
-          <t>SPM-87-TC03 has just been run (so 'SPM87 Waterfront Gala' is Safety approved) and the fixtures have NOT been reset since.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="57.75" customHeight="1" s="19">
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>npm run fixtures:spm87 has been run. 'SPM87 Waterfront Gala' is in Safety review, submitted by Daniel Tan. Logged in as Hana Yusof (hana.yusof@connectsphere.com / password123). Note the date and time of step 5. This case changes the event - SPM-87-TC04 and TC05 read the result, so go straight to those and run npm run fixtures:spm87 after TC05.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="71.25" customHeight="1" s="19">
       <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t>1. Click 'Log out' in the top bar
-2. Log in as daniel.tan@connectsphere.com with password123
-3. Click 'All Events' in the sidebar
-4. Click 'SPM87 Waterfront Gala' in the list</t>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>1. Click 'Safety Checks' in the sidebar
+2. Click 'SPM87 Waterfront Gala' in the list
+3. Click 'Record safety decision'
+4. Choose 'Approve'
+5. Click 'Record decision'</t>
         </is>
       </c>
     </row>
@@ -11086,23 +11169,24 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>Coordinator: daniel.tan@connectsphere.com
-Event: SPM87 Waterfront Gala (Safety approved)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="98.25" customHeight="1" s="19">
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Event: SPM87 Waterfront Gala (Safety review)
+Decision: Approve (no reason needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="111.75" customHeight="1" s="19">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>Step 3: 'SPM87 Waterfront Gala' is listed with the status 'Safety approved'.
-Step 4: The event shows the status 'Safety approved', the 'Safety check' row 'Approved · decided by Hana Yusof, &lt;date and time of TC03 step 5&gt;', and a 'Confirm event' button - the event is back with the Coordinator to proceed. There is no 'Submit for safety check' button.</t>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>Step 3: A dialog headed 'Record safety decision' opens with the choices 'Approve', 'Request changes' and 'Reject'.
+Step 4: No reason box is shown for Approve.
+Step 5: The message 'Safety check approved. The coordinator has been notified.' is shown. The status badge changes to 'Safety approved', the 'Safety check' row reads 'Approved · decided by Hana Yusof, &lt;date and time of step 5&gt;', and the 'Record safety decision' button is gone.</t>
         </is>
       </c>
     </row>
@@ -11112,7 +11196,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -11144,10 +11228,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>Step 3: 'SPM87 Waterfront Gala' is listed with the status 'Safety approved'.
-Step 4: The event shows the status 'Safety approved', the 'Safety check' row 'Approved · decided by Hana Yusof, &lt;date and time of TC03 step 5&gt;', and a 'Confirm event' button - the event is back with the Coordinator to proceed. There is no 'Submit for safety check' button.</t>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>Step 3: A dialog headed 'Record safety decision' opens with the choices 'Approve', 'Request changes' and 'Reject'.
+Step 4: No reason box is shown for Approve.
+Step 5: The message 'Safety check approved. The coordinator has been notified.' is shown. The status badge changes to 'Safety approved', the 'Safety check' row reads 'Approved · decided by Hana Yusof, &lt;date and time of step 5&gt;', and the 'Record safety decision' button is gone.</t>
         </is>
       </c>
     </row>
@@ -11181,7 +11266,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -11211,10 +11296,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>Step 3: 'SPM87 Waterfront Gala' is listed with the status 'Safety approved'.
-Step 4: The event shows the status 'Safety approved', the 'Safety check' row 'Approved · decided by Hana Yusof, &lt;date and time of TC03 step 5&gt;', and a 'Confirm event' button - the event is back with the Coordinator to proceed. There is no 'Submit for safety check' button.</t>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>Step 3: A dialog headed 'Record safety decision' opens with the choices 'Approve', 'Request changes' and 'Reject'.
+Step 4: No reason box is shown for Approve.
+Step 5: The message 'Safety check approved. The coordinator has been notified.' is shown. The status badge changes to 'Safety approved', the 'Safety check' row reads 'Approved · decided by Hana Yusof, &lt;date and time of step 5&gt;', and the 'Record safety decision' button is gone.</t>
         </is>
       </c>
     </row>
@@ -11248,7 +11334,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>Kayalvizhi</t>
         </is>
@@ -12276,9 +12362,9 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
-        <is>
-          <t>SPM-87-TC05</t>
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>SPM-87-TC04</t>
         </is>
       </c>
     </row>
@@ -12288,21 +12374,21 @@
           <t>Summary</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
-        <is>
-          <t>The Event Organiser sees that their event is Safety approved but not the safety details</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="57.75" customHeight="1" s="19">
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>After approval the assigned Coordinator sees the decision and can go on to confirm the event</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="44.25" customHeight="1" s="19">
       <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
-        <is>
-          <t>SPM-87-TC04 has just been run (so 'SPM87 Waterfront Gala' is Safety approved) and the fixtures have NOT been reset since. Rachel Ng (rachel.ng@meridianfina.com / password123) raised the event. Run npm run fixtures:spm87 after this case.</t>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>SPM-87-TC03 has just been run (so 'SPM87 Waterfront Gala' is Safety approved) and the fixtures have NOT been reset since.</t>
         </is>
       </c>
     </row>
@@ -12312,11 +12398,11 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>1. Click 'Log out' in the top bar
-2. Log in as rachel.ng@meridianfina.com with password123
-3. Click 'My Events' in the sidebar
+2. Log in as daniel.tan@connectsphere.com with password123
+3. Click 'All Events' in the sidebar
 4. Click 'SPM87 Waterfront Gala' in the list</t>
         </is>
       </c>
@@ -12327,9 +12413,9 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>Organiser: rachel.ng@meridianfina.com
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Coordinator: daniel.tan@connectsphere.com
 Event: SPM87 Waterfront Gala (Safety approved)</t>
         </is>
       </c>
@@ -12340,11 +12426,10 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>Step 2: The Dashboard lists 'SPM87 Waterfront Gala' under a 'Safety approved' heading.
-Step 3: 'SPM87 Waterfront Gala' is listed with the status 'Safety approved'.
-Step 4: The event shows the status 'Safety approved'. There is no 'Safety check' row and no decision details - those are for internal staff only.</t>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>Step 3: 'SPM87 Waterfront Gala' is listed with the status 'Safety approved'.
+Step 4: The event shows the status 'Safety approved', the 'Safety check' row 'Approved · decided by Hana Yusof, &lt;date and time of TC03 step 5&gt;', and a 'Confirm event' button - the event is back with the Coordinator to proceed. There is no 'Submit for safety check' button.</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12439,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -12386,11 +12471,10 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>Step 2: The Dashboard lists 'SPM87 Waterfront Gala' under a 'Safety approved' heading.
-Step 3: 'SPM87 Waterfront Gala' is listed with the status 'Safety approved'.
-Step 4: The event shows the status 'Safety approved'. There is no 'Safety check' row and no decision details - those are for internal staff only.</t>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>Step 3: 'SPM87 Waterfront Gala' is listed with the status 'Safety approved'.
+Step 4: The event shows the status 'Safety approved', the 'Safety check' row 'Approved · decided by Hana Yusof, &lt;date and time of TC03 step 5&gt;', and a 'Confirm event' button - the event is back with the Coordinator to proceed. There is no 'Submit for safety check' button.</t>
         </is>
       </c>
     </row>
@@ -12424,7 +12508,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -12454,11 +12538,10 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>Step 2: The Dashboard lists 'SPM87 Waterfront Gala' under a 'Safety approved' heading.
-Step 3: 'SPM87 Waterfront Gala' is listed with the status 'Safety approved'.
-Step 4: The event shows the status 'Safety approved'. There is no 'Safety check' row and no decision details - those are for internal staff only.</t>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>Step 3: 'SPM87 Waterfront Gala' is listed with the status 'Safety approved'.
+Step 4: The event shows the status 'Safety approved', the 'Safety check' row 'Approved · decided by Hana Yusof, &lt;date and time of TC03 step 5&gt;', and a 'Confirm event' button - the event is back with the Coordinator to proceed. There is no 'Submit for safety check' button.</t>
         </is>
       </c>
     </row>
@@ -12492,7 +12575,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>Kayalvizhi</t>
         </is>
@@ -13520,9 +13603,9 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
-        <is>
-          <t>SPM-87-TC06</t>
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>SPM-87-TC05</t>
         </is>
       </c>
     </row>
@@ -13532,70 +13615,63 @@
           <t>Summary</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
-        <is>
-          <t>Requesting changes returns the event to Planning with the changes required recorded for the Coordinator</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="71.25" customHeight="1" s="19">
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>The Event Organiser sees that their event is Safety approved but not the safety details</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="57.75" customHeight="1" s="19">
       <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
-        <is>
-          <t>npm run fixtures:spm87 has been run. 'SPM87 Lakeside Conference' is in Safety review, assigned to Daniel Tan. Logged in as Hana Yusof (hana.yusof@connectsphere.com / password123). Note the date and time of step 6. This case changes the event - run npm run fixtures:spm87 afterwards.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="152.25" customHeight="1" s="19">
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>SPM-87-TC04 has just been run (so 'SPM87 Waterfront Gala' is Safety approved) and the fixtures have NOT been reset since. Rachel Ng (rachel.ng@meridianfina.com / password123) raised the event. Run npm run fixtures:spm87 after this case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="57.75" customHeight="1" s="19">
       <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t>1. Click 'Safety Checks' in the sidebar
-2. Click 'SPM87 Lakeside Conference' in the list
-3. Click 'Record safety decision'
-4. Choose 'Request changes'
-5. Type 'Add a second fire marshal at the east exit.' in 'Changes required'
-6. Click 'Record decision'
-7. Click 'Log out' in the top bar
-8. Log in as daniel.tan@connectsphere.com with password123
-9. Click 'All Events' in the sidebar
-10. Click 'SPM87 Lakeside Conference' in the list</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="57.75" customHeight="1" s="19">
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>1. Click 'Log out' in the top bar
+2. Log in as rachel.ng@meridianfina.com with password123
+3. Click 'My Events' in the sidebar
+4. Click 'SPM87 Waterfront Gala' in the list</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30.75" customHeight="1" s="19">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>Event: SPM87 Lakeside Conference (Safety review)
-Decision: Request changes
-Changes required: Add a second fire marshal at the east exit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="111.75" customHeight="1" s="19">
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Organiser: rachel.ng@meridianfina.com
+Event: SPM87 Waterfront Gala (Safety approved)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="98.25" customHeight="1" s="19">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>Step 4: A box labelled 'Changes required' appears.
-Step 6: The message 'Changes requested. The event is back in Planning and the coordinator has been notified.' is shown, and the status badge changes to 'Planning'.
-Step 10: Daniel sees the status 'Planning' and the 'Safety check' row 'Changes requested · decided by Hana Yusof, &lt;date and time of step 6&gt;. Changes required: Add a second fire marshal at the east exit.'</t>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>Step 2: The Dashboard lists 'SPM87 Waterfront Gala' under a 'Safety approved' heading.
+Step 3: 'SPM87 Waterfront Gala' is listed with the status 'Safety approved'.
+Step 4: The event shows the status 'Safety approved'. There is no 'Safety check' row and no decision details - those are for internal staff only.</t>
         </is>
       </c>
     </row>
@@ -13605,7 +13681,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -13637,11 +13713,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>Step 4: A box labelled 'Changes required' appears.
-Step 6: The message 'Changes requested. The event is back in Planning and the coordinator has been notified.' is shown, and the status badge changes to 'Planning'.
-Step 10: Daniel sees the status 'Planning' and the 'Safety check' row 'Changes requested · decided by Hana Yusof, &lt;date and time of step 6&gt;. Changes required: Add a second fire marshal at the east exit.'</t>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>Step 2: The Dashboard lists 'SPM87 Waterfront Gala' under a 'Safety approved' heading.
+Step 3: 'SPM87 Waterfront Gala' is listed with the status 'Safety approved'.
+Step 4: The event shows the status 'Safety approved'. There is no 'Safety check' row and no decision details - those are for internal staff only.</t>
         </is>
       </c>
     </row>
@@ -13675,7 +13751,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -13705,11 +13781,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>Step 4: A box labelled 'Changes required' appears.
-Step 6: The message 'Changes requested. The event is back in Planning and the coordinator has been notified.' is shown, and the status badge changes to 'Planning'.
-Step 10: Daniel sees the status 'Planning' and the 'Safety check' row 'Changes requested · decided by Hana Yusof, &lt;date and time of step 6&gt;. Changes required: Add a second fire marshal at the east exit.'</t>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>Step 2: The Dashboard lists 'SPM87 Waterfront Gala' under a 'Safety approved' heading.
+Step 3: 'SPM87 Waterfront Gala' is listed with the status 'Safety approved'.
+Step 4: The event shows the status 'Safety approved'. There is no 'Safety check' row and no decision details - those are for internal staff only.</t>
         </is>
       </c>
     </row>
@@ -13743,7 +13819,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>Kayalvizhi</t>
         </is>
@@ -14771,9 +14847,9 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
-        <is>
-          <t>SPM-87-TC07</t>
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>SPM-87-TC06</t>
         </is>
       </c>
     </row>
@@ -14783,9 +14859,9 @@
           <t>Summary</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
-        <is>
-          <t>Rejecting the safety arrangement returns the event to Planning with the reason recorded for the Coordinator</t>
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>Requesting changes returns the event to Planning with the changes required recorded for the Coordinator</t>
         </is>
       </c>
     </row>
@@ -14795,9 +14871,9 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
-        <is>
-          <t>npm run fixtures:spm87 has been run. 'SPM87 Rooftop Launch Party' is in Safety review, assigned to Daniel Tan. Logged in as Hana Yusof (hana.yusof@connectsphere.com / password123). Note the date and time of step 6. This case changes the event - run npm run fixtures:spm87 afterwards.</t>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>npm run fixtures:spm87 has been run. 'SPM87 Lakeside Conference' is in Safety review, assigned to Daniel Tan. Logged in as Hana Yusof (hana.yusof@connectsphere.com / password123). Note the date and time of step 6. This case changes the event - run npm run fixtures:spm87 afterwards.</t>
         </is>
       </c>
     </row>
@@ -14807,18 +14883,18 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>1. Click 'Safety Checks' in the sidebar
-2. Click 'SPM87 Rooftop Launch Party' in the list
+2. Click 'SPM87 Lakeside Conference' in the list
 3. Click 'Record safety decision'
-4. Choose 'Reject'
-5. Type 'A single stairway cannot evacuate 300 people from the rooftop.' in 'Reason for rejecting'
+4. Choose 'Request changes'
+5. Type 'Add a second fire marshal at the east exit.' in 'Changes required'
 6. Click 'Record decision'
 7. Click 'Log out' in the top bar
 8. Log in as daniel.tan@connectsphere.com with password123
 9. Click 'All Events' in the sidebar
-10. Click 'SPM87 Rooftop Launch Party' in the list</t>
+10. Click 'SPM87 Lakeside Conference' in the list</t>
         </is>
       </c>
     </row>
@@ -14828,11 +14904,11 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>Event: SPM87 Rooftop Launch Party (Safety review)
-Decision: Reject
-Reason: A single stairway cannot evacuate 300 people from the rooftop.</t>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Event: SPM87 Lakeside Conference (Safety review)
+Decision: Request changes
+Changes required: Add a second fire marshal at the east exit.</t>
         </is>
       </c>
     </row>
@@ -14842,11 +14918,11 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>Step 4: A box labelled 'Reason for rejecting' appears.
-Step 6: The message 'Safety arrangement rejected. The event is back in Planning and the coordinator has been notified.' is shown, and the status badge changes to 'Planning'.
-Step 10: Daniel sees the status 'Planning' and the 'Safety check' row 'Rejected · decided by Hana Yusof, &lt;date and time of step 6&gt;. Reason: A single stairway cannot evacuate 300 people from the rooftop.'</t>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>Step 4: A box labelled 'Changes required' appears.
+Step 6: The message 'Changes requested. The event is back in Planning and the coordinator has been notified.' is shown, and the status badge changes to 'Planning'.
+Step 10: Daniel sees the status 'Planning' and the 'Safety check' row 'Changes requested · decided by Hana Yusof, &lt;date and time of step 6&gt;. Changes required: Add a second fire marshal at the east exit.'</t>
         </is>
       </c>
     </row>
@@ -14856,7 +14932,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -14888,11 +14964,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>Step 4: A box labelled 'Reason for rejecting' appears.
-Step 6: The message 'Safety arrangement rejected. The event is back in Planning and the coordinator has been notified.' is shown, and the status badge changes to 'Planning'.
-Step 10: Daniel sees the status 'Planning' and the 'Safety check' row 'Rejected · decided by Hana Yusof, &lt;date and time of step 6&gt;. Reason: A single stairway cannot evacuate 300 people from the rooftop.</t>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>Step 4: A box labelled 'Changes required' appears.
+Step 6: The message 'Changes requested. The event is back in Planning and the coordinator has been notified.' is shown, and the status badge changes to 'Planning'.
+Step 10: Daniel sees the status 'Planning' and the 'Safety check' row 'Changes requested · decided by Hana Yusof, &lt;date and time of step 6&gt;. Changes required: Add a second fire marshal at the east exit.'</t>
         </is>
       </c>
     </row>
@@ -14926,7 +15002,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -14956,11 +15032,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>Step 4: A box labelled 'Reason for rejecting' appears.
-Step 6: The message 'Safety arrangement rejected. The event is back in Planning and the coordinator has been notified.' is shown, and the status badge changes to 'Planning'.
-Step 10: Daniel sees the status 'Planning' and the 'Safety check' row 'Rejected · decided by Hana Yusof, &lt;date and time of step 6&gt;. Reason: A single stairway cannot evacuate 300 people from the rooftop.'</t>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>Step 4: A box labelled 'Changes required' appears.
+Step 6: The message 'Changes requested. The event is back in Planning and the coordinator has been notified.' is shown, and the status badge changes to 'Planning'.
+Step 10: Daniel sees the status 'Planning' and the 'Safety check' row 'Changes requested · decided by Hana Yusof, &lt;date and time of step 6&gt;. Changes required: Add a second fire marshal at the east exit.'</t>
         </is>
       </c>
     </row>
@@ -14994,7 +15070,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>Kayalvizhi</t>
         </is>
@@ -16022,9 +16098,9 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
-        <is>
-          <t>SPM-87-TC08</t>
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>SPM-87-TC07</t>
         </is>
       </c>
     </row>
@@ -16034,69 +16110,70 @@
           <t>Summary</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
-        <is>
-          <t>Rejecting or requesting changes without a reason is not saved and a reason is asked for</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="44.25" customHeight="1" s="19">
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>Rejecting the safety arrangement returns the event to Planning with the reason recorded for the Coordinator</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="71.25" customHeight="1" s="19">
       <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
-        <is>
-          <t>npm run fixtures:spm87 has been run. 'SPM87 Hillside Workshop' is in Safety review. Logged in as Hana Yusof (hana.yusof@connectsphere.com / password123).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="138.75" customHeight="1" s="19">
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>npm run fixtures:spm87 has been run. 'SPM87 Rooftop Launch Party' is in Safety review, assigned to Daniel Tan. Logged in as Hana Yusof (hana.yusof@connectsphere.com / password123). Note the date and time of step 6. This case changes the event - run npm run fixtures:spm87 afterwards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="152.25" customHeight="1" s="19">
       <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>1. Click 'Safety Checks' in the sidebar
-2. Click 'SPM87 Hillside Workshop' in the list
+2. Click 'SPM87 Rooftop Launch Party' in the list
 3. Click 'Record safety decision'
 4. Choose 'Reject'
-5. Leave 'Reason for rejecting' empty
+5. Type 'A single stairway cannot evacuate 300 people from the rooftop.' in 'Reason for rejecting'
 6. Click 'Record decision'
-7. Choose 'Request changes'
-8. Type three spaces in 'Changes required'
-9. Click 'Record decision'
-10. Click 'Cancel' in the dialog</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30.75" customHeight="1" s="19">
+7. Click 'Log out' in the top bar
+8. Log in as daniel.tan@connectsphere.com with password123
+9. Click 'All Events' in the sidebar
+10. Click 'SPM87 Rooftop Launch Party' in the list</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="57.75" customHeight="1" s="19">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>Event: SPM87 Hillside Workshop (Safety review)
-Reject with no reason; Request changes with only spaces</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="84.75" customHeight="1" s="19">
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Event: SPM87 Rooftop Launch Party (Safety review)
+Decision: Reject
+Reason: A single stairway cannot evacuate 300 people from the rooftop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="111.75" customHeight="1" s="19">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>Step 6: Nothing is saved. 'Give a reason for rejecting.' is shown under the reason box and the dialog stays open.
-Step 9: Nothing is saved. 'Describe the changes required.' is shown under the box and the dialog stays open.
-Step 10: The status is still 'Safety review' and the 'Record safety decision' button is still there.</t>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>Step 4: A box labelled 'Reason for rejecting' appears.
+Step 6: The message 'Safety arrangement rejected. The event is back in Planning and the coordinator has been notified.' is shown, and the status badge changes to 'Planning'.
+Step 10: Daniel sees the status 'Planning' and the 'Safety check' row 'Rejected · decided by Hana Yusof, &lt;date and time of step 6&gt;. Reason: A single stairway cannot evacuate 300 people from the rooftop.'</t>
         </is>
       </c>
     </row>
@@ -16106,7 +16183,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -16138,11 +16215,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>Step 6: Nothing is saved. 'Give a reason for rejecting.' is shown under the reason box and the dialog stays open.
-Step 9: Nothing is saved. 'Describe the changes required.' is shown under the box and the dialog stays open.
-Step 10: The status is still 'Safety review' and the 'Record safety decision' button is still there.</t>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>Step 4: A box labelled 'Reason for rejecting' appears.
+Step 6: The message 'Safety arrangement rejected. The event is back in Planning and the coordinator has been notified.' is shown, and the status badge changes to 'Planning'.
+Step 10: Daniel sees the status 'Planning' and the 'Safety check' row 'Rejected · decided by Hana Yusof, &lt;date and time of step 6&gt;. Reason: A single stairway cannot evacuate 300 people from the rooftop.</t>
         </is>
       </c>
     </row>
@@ -16176,7 +16253,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -16206,11 +16283,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>Step 6: Nothing is saved. 'Give a reason for rejecting.' is shown under the reason box and the dialog stays open.
-Step 9: Nothing is saved. 'Describe the changes required.' is shown under the box and the dialog stays open.
-Step 10: The status is still 'Safety review' and the 'Record safety decision' button is still there.</t>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>Step 4: A box labelled 'Reason for rejecting' appears.
+Step 6: The message 'Safety arrangement rejected. The event is back in Planning and the coordinator has been notified.' is shown, and the status badge changes to 'Planning'.
+Step 10: Daniel sees the status 'Planning' and the 'Safety check' row 'Rejected · decided by Hana Yusof, &lt;date and time of step 6&gt;. Reason: A single stairway cannot evacuate 300 people from the rooftop.'</t>
         </is>
       </c>
     </row>
@@ -16244,7 +16321,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>Kayalvizhi</t>
         </is>

--- a/docs/test-cases/SPM-87_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-87_Test_Cases.xlsx
@@ -28,7 +28,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -52,6 +52,9 @@
       <name val="Arial"/>
       <color theme="1"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
     </font>
   </fonts>
   <fills count="4">
@@ -137,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -191,6 +194,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -968,11 +974,15 @@
       </c>
       <c r="G14" s="23" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Updated</t>
         </is>
       </c>
       <c r="H14" s="23" t="n"/>
-      <c r="I14" s="23" t="n"/>
+      <c r="I14" s="23" t="inlineStr">
+        <is>
+          <t>Week 7 #5</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -6062,7 +6072,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="24.75" customWidth="1" style="19" min="1" max="1"/>
@@ -6070,57 +6080,64 @@
     <col width="12.63" customWidth="1" style="19" min="3" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="19">
-      <c r="A1" s="8" t="inlineStr">
+    <row r="1" ht="90" customHeight="1" s="19">
+      <c r="A1" s="26" t="inlineStr">
+        <is>
+          <t>v2 (2026-10-20): The Event Operations Manager is now shown as the 'Event Coordinator Lead' (SPM-84 AC1, forum #129, Week 7 Change #5) - the same role, accounts, permissions and pages. Read 'Operations Manager', 'Event Operations Manager' or 'Ops Manager' in this case as 'Event Coordinator Lead'; on screen the role is shown under its new name, and refusals say 'Assigning coordinators is the Event Coordinator Lead's role.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="17.25" customHeight="1" s="19">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B1" s="9" t="n"/>
-    </row>
-    <row r="2" ht="17.25" customHeight="1" s="19">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" s="23" t="inlineStr">
-        <is>
-          <t>SPM-87-TC11</t>
-        </is>
-      </c>
+      <c r="B2" s="9" t="n"/>
     </row>
     <row r="3" ht="30.75" customHeight="1" s="19">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Summary</t>
+          <t>Test Case ID</t>
         </is>
       </c>
       <c r="B3" s="23" t="inlineStr">
         <is>
-          <t>The assigned Coordinator and the Operations Manager cannot record a safety decision</t>
+          <t>SPM-87-TC11</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30.75" customHeight="1" s="19">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>Pre-conditions</t>
+          <t>Summary</t>
         </is>
       </c>
       <c r="B4" s="23" t="inlineStr">
         <is>
-          <t>npm run fixtures:spm87 has been run. 'SPM87 Hillside Workshop' is in Safety review, assigned to Daniel Tan.</t>
+          <t>The assigned Coordinator and the Operations Manager cannot record a safety decision</t>
         </is>
       </c>
     </row>
     <row r="5" ht="98.25" customHeight="1" s="19">
       <c r="A5" s="10" t="inlineStr">
         <is>
+          <t>Pre-conditions</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>npm run fixtures:spm87 has been run. 'SPM87 Hillside Workshop' is in Safety review, assigned to Daniel Tan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30.75" customHeight="1" s="19">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>1. Log in as daniel.tan@connectsphere.com with password123
 2. Click 'All Events' in the sidebar
@@ -6132,191 +6149,190 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="30.75" customHeight="1" s="19">
-      <c r="A6" s="10" t="inlineStr">
+    <row r="7" ht="71.25" customHeight="1" s="19">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Coordinator: daniel.tan@connectsphere.com (assigned)
 Operations Manager: grace.lim@connectsphere.com</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="71.25" customHeight="1" s="19">
-      <c r="A7" s="10" t="inlineStr">
+    <row r="8" ht="17.25" customHeight="1" s="19">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>Step 3: Daniel Tan sees the event in 'Safety review' with no 'Record safety decision' button - only the Safety Officer decides.
 Step 7: Grace Lim sees the event with no 'Record safety decision' button either.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="17.25" customHeight="1" s="19">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B8" s="23" t="inlineStr">
-        <is>
-          <t>Janelle</t>
-        </is>
-      </c>
-    </row>
     <row r="9" ht="15.75" customHeight="1" s="19">
       <c r="A9" s="10" t="inlineStr">
         <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>Janelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15.75" customHeight="1" s="19">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B9" s="18" t="n">
+      <c r="B10" s="18" t="n">
         <v>46308</v>
       </c>
     </row>
-    <row r="10" ht="15.75" customHeight="1" s="19"/>
-    <row r="11" ht="15.75" customHeight="1" s="19">
-      <c r="A11" s="12" t="inlineStr">
+    <row r="11" ht="15.75" customHeight="1" s="19"/>
+    <row r="12" ht="15.75" customHeight="1" s="19">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n"/>
-      <c r="C11" s="14" t="n"/>
-    </row>
-    <row r="12" ht="15.75" customHeight="1" s="19">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="B12" s="13" t="n"/>
+      <c r="C12" s="14" t="n"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1" s="19">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>Step 3: Daniel Tan sees the event in 'Safety review' with no 'Record safety decision' button - only the Safety Officer decides.
 Step 7: Grace Lim sees the event with no 'Record safety decision' button either.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15.75" customHeight="1" s="19">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="14" ht="15.75" customHeight="1" s="19">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="19">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B15" s="23" t="inlineStr">
-        <is>
-          <t>Janelle</t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" s="19">
       <c r="A16" s="16" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>Janelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1" s="19">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B16" s="18" t="n">
+      <c r="B17" s="18" t="n">
         <v>46308</v>
       </c>
     </row>
-    <row r="17" ht="15.75" customHeight="1" s="19">
-      <c r="A17" s="12" t="inlineStr">
+    <row r="18" ht="15.75" customHeight="1" s="19">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1" s="19">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="B18" s="13" t="n"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1" s="19">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>Step 3: Daniel Tan sees the event in 'Safety review' with no 'Record safety decision' button - only the Safety Officer decides.
 Step 7: Grace Lim sees the event with no 'Record safety decision' button either.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15.75" customHeight="1" s="19">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="20" ht="15.75" customHeight="1" s="19">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="19">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B21" s="23" t="inlineStr">
-        <is>
-          <t>Kayalvizhi</t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="19">
       <c r="A22" s="16" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>Kayalvizhi</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" s="19">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B22" s="18" t="n">
+      <c r="B23" s="18" t="n">
         <v>46309</v>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1" s="19"/>
     <row r="24" ht="15.75" customHeight="1" s="19"/>
     <row r="25" ht="15.75" customHeight="1" s="19"/>
     <row r="26" ht="15.75" customHeight="1" s="19"/>
@@ -7295,6 +7311,9 @@
     <row r="999" ht="15.75" customHeight="1" s="19"/>
     <row r="1000" ht="15.75" customHeight="1" s="19"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
